--- a/research/traditional_assets/database/data/cyprus/cyprus_oil_gas_distribution.xlsx
+++ b/research/traditional_assets/database/data/cyprus/cyprus_oil_gas_distribution.xlsx
@@ -587,74 +587,56 @@
           <t>Oil/Gas Distribution</t>
         </is>
       </c>
-      <c r="G2">
-        <v>1352.173913043478</v>
-      </c>
-      <c r="H2">
-        <v>1352.173913043478</v>
-      </c>
-      <c r="I2">
-        <v>-197.8260869565217</v>
-      </c>
-      <c r="J2">
-        <v>-197.8260869565217</v>
-      </c>
       <c r="K2">
-        <v>-0.549</v>
-      </c>
-      <c r="L2">
-        <v>-23.86956521739131</v>
+        <v>-0.214</v>
       </c>
       <c r="M2">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>12.88056206088993</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>-100.1821493624772</v>
+        <v>-0</v>
       </c>
       <c r="P2">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>12.88056206088993</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>-100.1821493624772</v>
+        <v>-0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
       <c r="U2">
-        <v>5.02</v>
+        <v>4.69</v>
       </c>
       <c r="V2">
-        <v>1.175644028103044</v>
+        <v>0.3326241134751773</v>
       </c>
       <c r="W2">
-        <v>-0.009119601328903654</v>
+        <v>-0.003835125448028674</v>
       </c>
       <c r="X2">
-        <v>0.06334816368708154</v>
+        <v>0.1048305442879964</v>
       </c>
       <c r="Y2">
-        <v>-0.0724677650159852</v>
+        <v>-0.1086656697360251</v>
       </c>
       <c r="Z2">
-        <v>0.0004811715481171548</v>
+        <v>0</v>
       </c>
       <c r="AA2">
-        <v>-0.09518828451882845</v>
+        <v>-2.330000000000132</v>
       </c>
       <c r="AB2">
-        <v>0.06334816368708154</v>
+        <v>0.1048305442879964</v>
       </c>
       <c r="AC2">
-        <v>-0.15853644820591</v>
+        <v>-2.434830544288129</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -666,7 +648,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-5.02</v>
+        <v>-4.69</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -675,28 +657,28 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>6.693333333333332</v>
+        <v>-0.4984059511158342</v>
       </c>
       <c r="AK2">
-        <v>9.65384615384616</v>
+        <v>78.16666666666603</v>
       </c>
       <c r="AL2">
-        <v>0.577</v>
+        <v>0.045</v>
       </c>
       <c r="AM2">
-        <v>0.577</v>
+        <v>-0.019</v>
       </c>
       <c r="AN2">
         <v>0</v>
       </c>
       <c r="AO2">
-        <v>-7.885615251299827</v>
+        <v>-5.177777777777778</v>
       </c>
       <c r="AP2">
-        <v>-0.6857923497267758</v>
+        <v>-0.3448529411764706</v>
       </c>
       <c r="AQ2">
-        <v>-7.885615251299827</v>
+        <v>12.26315789473684</v>
       </c>
     </row>
     <row r="3">
@@ -715,74 +697,56 @@
           <t>Oil/Gas Distribution</t>
         </is>
       </c>
-      <c r="G3">
-        <v>1352.173913043478</v>
-      </c>
-      <c r="H3">
-        <v>1352.173913043478</v>
-      </c>
-      <c r="I3">
-        <v>-197.8260869565217</v>
-      </c>
-      <c r="J3">
-        <v>-197.8260869565217</v>
-      </c>
       <c r="K3">
-        <v>-0.549</v>
-      </c>
-      <c r="L3">
-        <v>-23.86956521739131</v>
+        <v>-0.214</v>
       </c>
       <c r="M3">
-        <v>55</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>12.88056206088993</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>-100.1821493624772</v>
+        <v>0</v>
       </c>
       <c r="P3">
-        <v>55</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>12.88056206088993</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>-100.1821493624772</v>
+        <v>0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>5.02</v>
+        <v>4.69</v>
       </c>
       <c r="V3">
-        <v>1.175644028103044</v>
+        <v>0.3326241134751773</v>
       </c>
       <c r="W3">
-        <v>-0.009119601328903654</v>
+        <v>-0.003835125448028674</v>
       </c>
       <c r="X3">
-        <v>0.06334816368708154</v>
+        <v>0.1048305442879964</v>
       </c>
       <c r="Y3">
-        <v>-0.0724677650159852</v>
+        <v>-0.1086656697360251</v>
       </c>
       <c r="Z3">
-        <v>0.0004811715481171548</v>
+        <v>0</v>
       </c>
       <c r="AA3">
-        <v>-0.09518828451882845</v>
+        <v>-2.330000000000132</v>
       </c>
       <c r="AB3">
-        <v>0.06334816368708154</v>
+        <v>0.1048305442879964</v>
       </c>
       <c r="AC3">
-        <v>-0.15853644820591</v>
+        <v>-2.434830544288129</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -794,7 +758,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-5.02</v>
+        <v>-4.69</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -803,28 +767,28 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>6.693333333333332</v>
+        <v>-0.4984059511158342</v>
       </c>
       <c r="AK3">
-        <v>9.65384615384616</v>
+        <v>78.16666666666603</v>
       </c>
       <c r="AL3">
-        <v>0.577</v>
+        <v>0.045</v>
       </c>
       <c r="AM3">
-        <v>0.577</v>
+        <v>-0.019</v>
       </c>
       <c r="AN3">
         <v>0</v>
       </c>
       <c r="AO3">
-        <v>-7.885615251299827</v>
+        <v>-5.177777777777778</v>
       </c>
       <c r="AP3">
-        <v>-0.6857923497267758</v>
+        <v>-0.3448529411764706</v>
       </c>
       <c r="AQ3">
-        <v>-7.885615251299827</v>
+        <v>12.26315789473684</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/cyprus/cyprus_oil_gas_distribution.xlsx
+++ b/research/traditional_assets/database/data/cyprus/cyprus_oil_gas_distribution.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="nyse_fro" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -351,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -587,98 +589,113 @@
           <t>Oil/Gas Distribution</t>
         </is>
       </c>
+      <c r="D2">
+        <v>0.222</v>
+      </c>
+      <c r="G2">
+        <v>0.310626176067387</v>
+      </c>
+      <c r="H2">
+        <v>0.310626176067387</v>
+      </c>
+      <c r="I2">
+        <v>0.4318102446220165</v>
+      </c>
+      <c r="J2">
+        <v>0.4303700223930852</v>
+      </c>
       <c r="K2">
-        <v>-0.214</v>
+        <v>779.4200000000001</v>
+      </c>
+      <c r="L2">
+        <v>0.4062716643992348</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>605.5549999999999</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.1352379569868459</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0.7769302814913652</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>605.5</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.13522567389508</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0.776859716199225</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.055</v>
+      </c>
+      <c r="T2">
+        <v>9.082577139979029e-05</v>
       </c>
       <c r="U2">
-        <v>4.69</v>
+        <v>294.8</v>
       </c>
       <c r="V2">
-        <v>0.3326241134751773</v>
+        <v>0.06583737186501996</v>
       </c>
       <c r="W2">
-        <v>-0.003835125448028674</v>
+        <v>0.4426655063457983</v>
       </c>
       <c r="X2">
-        <v>0.1048305442879964</v>
+        <v>0.1045151350885101</v>
       </c>
       <c r="Y2">
-        <v>-0.1086656697360251</v>
+        <v>0.3381503712572881</v>
       </c>
       <c r="Z2">
-        <v>0</v>
-      </c>
-      <c r="AA2">
-        <v>-2.330000000000132</v>
+        <v>0.4636785498489426</v>
       </c>
       <c r="AB2">
-        <v>0.1048305442879964</v>
-      </c>
-      <c r="AC2">
-        <v>-2.434830544288129</v>
+        <v>0.08674456225255785</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>2269.2</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>2269.2</v>
       </c>
       <c r="AG2">
-        <v>-4.69</v>
+        <v>1974.4</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>0.336332241473862</v>
       </c>
       <c r="AI2">
-        <v>0</v>
+        <v>0.502825234328259</v>
       </c>
       <c r="AJ2">
-        <v>-0.4984059511158342</v>
+        <v>0.3060088963283272</v>
       </c>
       <c r="AK2">
-        <v>78.16666666666603</v>
+        <v>0.4680780446172448</v>
       </c>
       <c r="AL2">
-        <v>0.045</v>
+        <v>150.095</v>
       </c>
       <c r="AM2">
-        <v>-0.019</v>
+        <v>99.773</v>
       </c>
       <c r="AN2">
-        <v>0</v>
+        <v>2.189776795622763</v>
       </c>
       <c r="AO2">
-        <v>-5.177777777777778</v>
+        <v>5.519271128285419</v>
       </c>
       <c r="AP2">
-        <v>-0.3448529411764706</v>
+        <v>1.905294952087777</v>
       </c>
       <c r="AQ2">
-        <v>12.26315789473684</v>
+        <v>8.302997805017389</v>
       </c>
     </row>
     <row r="3">
@@ -689,106 +706,9018 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Frontline plc (NYSE:FRO)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Oil/Gas Distribution</t>
+        </is>
+      </c>
+      <c r="D3">
+        <v>0.222</v>
+      </c>
+      <c r="G3">
+        <v>0.3111667449016847</v>
+      </c>
+      <c r="H3">
+        <v>0.3111667449016847</v>
+      </c>
+      <c r="I3">
+        <v>0.4321180827204923</v>
+      </c>
+      <c r="J3">
+        <v>0.4320174608589558</v>
+      </c>
+      <c r="K3">
+        <v>777.1</v>
+      </c>
+      <c r="L3">
+        <v>0.4053095498878632</v>
+      </c>
+      <c r="M3">
+        <v>605.5</v>
+      </c>
+      <c r="N3">
+        <v>0.1356528362756519</v>
+      </c>
+      <c r="O3">
+        <v>0.7791789988418478</v>
+      </c>
+      <c r="P3">
+        <v>605.5</v>
+      </c>
+      <c r="Q3">
+        <v>0.1356528362756519</v>
+      </c>
+      <c r="R3">
+        <v>0.7791789988418478</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>285.4</v>
+      </c>
+      <c r="V3">
+        <v>0.06393942109508019</v>
+      </c>
+      <c r="W3">
+        <v>0.3831665105270943</v>
+      </c>
+      <c r="X3">
+        <v>0.09910917753539944</v>
+      </c>
+      <c r="Y3">
+        <v>0.2840573329916949</v>
+      </c>
+      <c r="Z3">
+        <v>0.4633957703927492</v>
+      </c>
+      <c r="AA3">
+        <v>0.2001950640978552</v>
+      </c>
+      <c r="AB3">
+        <v>0.0868612180081394</v>
+      </c>
+      <c r="AC3">
+        <v>0.1133338460897158</v>
+      </c>
+      <c r="AD3">
+        <v>2257.9</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>2257.9</v>
+      </c>
+      <c r="AG3">
+        <v>1972.5</v>
+      </c>
+      <c r="AH3">
+        <v>0.3359220412110392</v>
+      </c>
+      <c r="AI3">
+        <v>0.5035684018020429</v>
+      </c>
+      <c r="AJ3">
+        <v>0.3064744177374497</v>
+      </c>
+      <c r="AK3">
+        <v>0.4698218368902439</v>
+      </c>
+      <c r="AL3">
+        <v>149.1</v>
+      </c>
+      <c r="AM3">
+        <v>99.39999999999999</v>
+      </c>
+      <c r="AN3">
+        <v>2.178809225127859</v>
+      </c>
+      <c r="AO3">
+        <v>5.556673373574783</v>
+      </c>
+      <c r="AP3">
+        <v>1.903406349512689</v>
+      </c>
+      <c r="AQ3">
+        <v>8.335010060362174</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Cyprus</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>ADS Maritime Holding Plc (OB:ADS)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Oil/Gas Distribution</t>
         </is>
       </c>
+      <c r="G4">
+        <v>-0.5752136752136753</v>
+      </c>
+      <c r="H4">
+        <v>-0.5752136752136753</v>
+      </c>
+      <c r="I4">
+        <v>-0.07264957264957266</v>
+      </c>
+      <c r="J4">
+        <v>-0.07218187153809472</v>
+      </c>
+      <c r="K4">
+        <v>2.32</v>
+      </c>
+      <c r="L4">
+        <v>1.982905982905983</v>
+      </c>
+      <c r="M4">
+        <v>0.055</v>
+      </c>
+      <c r="N4">
+        <v>0.003900709219858156</v>
+      </c>
+      <c r="O4">
+        <v>0.02370689655172414</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>-0</v>
+      </c>
+      <c r="S4">
+        <v>0.055</v>
+      </c>
+      <c r="T4">
+        <v>1</v>
+      </c>
+      <c r="U4">
+        <v>9.4</v>
+      </c>
+      <c r="V4">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="W4">
+        <v>0.5021645021645021</v>
+      </c>
+      <c r="X4">
+        <v>0.1099210926416208</v>
+      </c>
+      <c r="Y4">
+        <v>0.3922434095228814</v>
+      </c>
+      <c r="AB4">
+        <v>0.0866279064969763</v>
+      </c>
+      <c r="AD4">
+        <v>11.3</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>11.3</v>
+      </c>
+      <c r="AG4">
+        <v>1.9</v>
+      </c>
+      <c r="AH4">
+        <v>0.4448818897637796</v>
+      </c>
+      <c r="AI4">
+        <v>0.3883161512027491</v>
+      </c>
+      <c r="AJ4">
+        <v>0.11875</v>
+      </c>
+      <c r="AK4">
+        <v>0.09644670050761421</v>
+      </c>
+      <c r="AL4">
+        <v>0.995</v>
+      </c>
+      <c r="AM4">
+        <v>0.373</v>
+      </c>
+      <c r="AN4">
+        <v>-376.6666666666667</v>
+      </c>
+      <c r="AO4">
+        <v>-0.08542713567839197</v>
+      </c>
+      <c r="AP4">
+        <v>-63.33333333333335</v>
+      </c>
+      <c r="AQ4">
+        <v>-0.2278820375335121</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Frontline plc (NYSE:FRO)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>NYSE:FRO</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Oil/Gas Distribution</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Cyprus</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>5.51643192488263</v>
+      </c>
+      <c r="F2">
+        <v>10.1500069689039</v>
+      </c>
+      <c r="G2">
+        <v>2.17880922512786</v>
+      </c>
+      <c r="H2">
+        <v>1.75123516356268</v>
+      </c>
+      <c r="I2">
+        <v>0.335922041211039</v>
+      </c>
+      <c r="J2">
+        <v>0.27</v>
+      </c>
+      <c r="K2">
+        <v>4463.6</v>
+      </c>
+      <c r="L2">
+        <v>5382.60334707198</v>
+      </c>
+      <c r="M2">
+        <v>6436.1</v>
+      </c>
+      <c r="N2">
+        <v>6912.00834707198</v>
+      </c>
+      <c r="O2">
+        <v>2257.9</v>
+      </c>
+      <c r="P2">
+        <v>1814.805</v>
+      </c>
+      <c r="Q2">
+        <v>0.0868612180081394</v>
+      </c>
+      <c r="R2">
+        <v>0.0795387328050452</v>
+      </c>
+      <c r="S2">
+        <v>0.0626484574138359</v>
+      </c>
+      <c r="T2">
+        <v>0.040075</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.0991091775353994</v>
+      </c>
+      <c r="X2">
+        <v>0.09413490795211669</v>
+      </c>
+      <c r="Y2">
+        <v>0.816682480146638</v>
+      </c>
+      <c r="Z2">
+        <v>0.7493229341172</v>
+      </c>
+      <c r="AA2">
+        <v>2257.9</v>
+      </c>
+      <c r="AB2">
+        <v>0.07159823704438384</v>
+      </c>
+      <c r="AC2">
+        <v>5.516431924882629</v>
+      </c>
+      <c r="AD2">
+        <v>2257.9</v>
+      </c>
+      <c r="AE2">
+        <v>149.1</v>
+      </c>
+      <c r="AF2">
+        <v>213.8</v>
+      </c>
+      <c r="AG2">
+        <v>1036.3</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>4463.6</v>
+      </c>
+      <c r="AK2">
+        <v>0.07384654256887045</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.125</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>235.4</v>
+      </c>
+      <c r="AR2">
+        <v>149.1</v>
+      </c>
+      <c r="AS2">
+        <v>2257.9</v>
+      </c>
+      <c r="AT2">
+        <v>285.4</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.08060541558090059</v>
+      </c>
+      <c r="C2">
+        <v>7123.748880000634</v>
+      </c>
+      <c r="D2">
+        <v>6838.348880000634</v>
+      </c>
+      <c r="E2">
+        <v>-2257.9</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>285.4</v>
+      </c>
+      <c r="H2">
+        <v>4463.6</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K2">
+        <v>213.8</v>
+      </c>
+      <c r="L2">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="O2">
+        <v>105.4561224489796</v>
+      </c>
+      <c r="P2">
+        <v>738.1928571428571</v>
+      </c>
+      <c r="Q2">
+        <v>951.992857142857</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.08060541558090059</v>
+      </c>
+      <c r="T2">
+        <v>0.5661120226706918</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2">
+        <v>0.125</v>
+      </c>
+      <c r="W2">
+        <v>0.0391125</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.08055628381142448</v>
+      </c>
+      <c r="C3">
+        <v>7059.892152418622</v>
+      </c>
+      <c r="D3">
+        <v>6841.707152418622</v>
+      </c>
+      <c r="E3">
+        <v>-2190.685</v>
+      </c>
+      <c r="F3">
+        <v>67.215</v>
+      </c>
+      <c r="G3">
+        <v>285.4</v>
+      </c>
+      <c r="H3">
+        <v>4463.6</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>1057.448979591837</v>
+      </c>
       <c r="K3">
-        <v>-0.214</v>
+        <v>213.8</v>
+      </c>
+      <c r="L3">
+        <v>843.6489795918367</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>3.0045105</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>840.6444690918366</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>105.0805586364796</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>735.563910455357</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>949.363910455357</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.08097490789032775</v>
+      </c>
+      <c r="T3">
+        <v>0.5711155380225793</v>
       </c>
       <c r="U3">
-        <v>4.69</v>
+        <v>0.0447</v>
       </c>
       <c r="V3">
-        <v>0.3326241134751773</v>
+        <v>0.125</v>
       </c>
       <c r="W3">
-        <v>-0.003835125448028674</v>
-      </c>
-      <c r="X3">
-        <v>0.1048305442879964</v>
+        <v>0.0391125</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
       </c>
       <c r="Y3">
-        <v>-0.1086656697360251</v>
+        <v>280.7941525222949</v>
       </c>
       <c r="Z3">
         <v>0</v>
       </c>
-      <c r="AA3">
-        <v>-2.330000000000132</v>
-      </c>
-      <c r="AB3">
-        <v>0.1048305442879964</v>
-      </c>
-      <c r="AC3">
-        <v>-2.434830544288129</v>
-      </c>
-      <c r="AD3">
-        <v>0</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>0</v>
-      </c>
-      <c r="AG3">
-        <v>-4.69</v>
-      </c>
-      <c r="AH3">
-        <v>0</v>
-      </c>
-      <c r="AI3">
-        <v>0</v>
-      </c>
-      <c r="AJ3">
-        <v>-0.4984059511158342</v>
-      </c>
-      <c r="AK3">
-        <v>78.16666666666603</v>
-      </c>
-      <c r="AL3">
-        <v>0.045</v>
-      </c>
-      <c r="AM3">
-        <v>-0.019</v>
-      </c>
-      <c r="AN3">
-        <v>0</v>
-      </c>
-      <c r="AO3">
-        <v>-5.177777777777778</v>
-      </c>
-      <c r="AP3">
-        <v>-0.3448529411764706</v>
-      </c>
-      <c r="AQ3">
-        <v>12.26315789473684</v>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.08050715204194835</v>
+      </c>
+      <c r="C4">
+        <v>6996.038724912435</v>
+      </c>
+      <c r="D4">
+        <v>6845.068724912436</v>
+      </c>
+      <c r="E4">
+        <v>-2123.47</v>
+      </c>
+      <c r="F4">
+        <v>134.43</v>
+      </c>
+      <c r="G4">
+        <v>285.4</v>
+      </c>
+      <c r="H4">
+        <v>4463.6</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K4">
+        <v>213.8</v>
+      </c>
+      <c r="L4">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M4">
+        <v>6.009021000000001</v>
+      </c>
+      <c r="N4">
+        <v>837.6399585918367</v>
+      </c>
+      <c r="O4">
+        <v>104.7049948239796</v>
+      </c>
+      <c r="P4">
+        <v>732.9349637678571</v>
+      </c>
+      <c r="Q4">
+        <v>946.7349637678572</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.08135194085913097</v>
+      </c>
+      <c r="T4">
+        <v>0.5762211659326685</v>
+      </c>
+      <c r="U4">
+        <v>0.0447</v>
+      </c>
+      <c r="V4">
+        <v>0.125</v>
+      </c>
+      <c r="W4">
+        <v>0.0391125</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>140.3970762611475</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.08045802027247223</v>
+      </c>
+      <c r="C5">
+        <v>6932.188602348797</v>
+      </c>
+      <c r="D5">
+        <v>6848.433602348797</v>
+      </c>
+      <c r="E5">
+        <v>-2056.255</v>
+      </c>
+      <c r="F5">
+        <v>201.645</v>
+      </c>
+      <c r="G5">
+        <v>285.4</v>
+      </c>
+      <c r="H5">
+        <v>4463.6</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K5">
+        <v>213.8</v>
+      </c>
+      <c r="L5">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M5">
+        <v>9.013531499999999</v>
+      </c>
+      <c r="N5">
+        <v>834.6354480918367</v>
+      </c>
+      <c r="O5">
+        <v>104.3294310114796</v>
+      </c>
+      <c r="P5">
+        <v>730.3060170803572</v>
+      </c>
+      <c r="Q5">
+        <v>944.1060170803571</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.08173674770357961</v>
+      </c>
+      <c r="T5">
+        <v>0.5814320645213161</v>
+      </c>
+      <c r="U5">
+        <v>0.0447</v>
+      </c>
+      <c r="V5">
+        <v>0.125</v>
+      </c>
+      <c r="W5">
+        <v>0.0391125</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>93.598050840765</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.08040888850299609</v>
+      </c>
+      <c r="C6">
+        <v>6868.341789604003</v>
+      </c>
+      <c r="D6">
+        <v>6851.801789604003</v>
+      </c>
+      <c r="E6">
+        <v>-1989.04</v>
+      </c>
+      <c r="F6">
+        <v>268.86</v>
+      </c>
+      <c r="G6">
+        <v>285.4</v>
+      </c>
+      <c r="H6">
+        <v>4463.6</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K6">
+        <v>213.8</v>
+      </c>
+      <c r="L6">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M6">
+        <v>12.018042</v>
+      </c>
+      <c r="N6">
+        <v>831.6309375918366</v>
+      </c>
+      <c r="O6">
+        <v>103.9538671989796</v>
+      </c>
+      <c r="P6">
+        <v>727.6770703928571</v>
+      </c>
+      <c r="Q6">
+        <v>941.4770703928571</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.0821295713572876</v>
+      </c>
+      <c r="T6">
+        <v>0.5867515234972275</v>
+      </c>
+      <c r="U6">
+        <v>0.0447</v>
+      </c>
+      <c r="V6">
+        <v>0.125</v>
+      </c>
+      <c r="W6">
+        <v>0.0391125</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>70.19853813057372</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.08035975673351997</v>
+      </c>
+      <c r="C7">
+        <v>6804.498291563948</v>
+      </c>
+      <c r="D7">
+        <v>6855.173291563948</v>
+      </c>
+      <c r="E7">
+        <v>-1921.825</v>
+      </c>
+      <c r="F7">
+        <v>336.075</v>
+      </c>
+      <c r="G7">
+        <v>285.4</v>
+      </c>
+      <c r="H7">
+        <v>4463.6</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K7">
+        <v>213.8</v>
+      </c>
+      <c r="L7">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M7">
+        <v>15.0225525</v>
+      </c>
+      <c r="N7">
+        <v>828.6264270918367</v>
+      </c>
+      <c r="O7">
+        <v>103.5783033864796</v>
+      </c>
+      <c r="P7">
+        <v>725.0481237053572</v>
+      </c>
+      <c r="Q7">
+        <v>938.8481237053572</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.0825306649826526</v>
+      </c>
+      <c r="T7">
+        <v>0.5921829710831579</v>
+      </c>
+      <c r="U7">
+        <v>0.0447</v>
+      </c>
+      <c r="V7">
+        <v>0.125</v>
+      </c>
+      <c r="W7">
+        <v>0.0391125</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>56.15883050445898</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.08031062496404383</v>
+      </c>
+      <c r="C8">
+        <v>6740.658113124149</v>
+      </c>
+      <c r="D8">
+        <v>6858.548113124149</v>
+      </c>
+      <c r="E8">
+        <v>-1854.61</v>
+      </c>
+      <c r="F8">
+        <v>403.29</v>
+      </c>
+      <c r="G8">
+        <v>285.4</v>
+      </c>
+      <c r="H8">
+        <v>4463.6</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K8">
+        <v>213.8</v>
+      </c>
+      <c r="L8">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M8">
+        <v>18.027063</v>
+      </c>
+      <c r="N8">
+        <v>825.6219165918367</v>
+      </c>
+      <c r="O8">
+        <v>103.2027395739796</v>
+      </c>
+      <c r="P8">
+        <v>722.4191770178571</v>
+      </c>
+      <c r="Q8">
+        <v>936.2191770178572</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.08294029251494026</v>
+      </c>
+      <c r="T8">
+        <v>0.5977299813836826</v>
+      </c>
+      <c r="U8">
+        <v>0.0447</v>
+      </c>
+      <c r="V8">
+        <v>0.125</v>
+      </c>
+      <c r="W8">
+        <v>0.0391125</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>46.7990254203825</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.08026149319456771</v>
+      </c>
+      <c r="C9">
+        <v>6676.821259189765</v>
+      </c>
+      <c r="D9">
+        <v>6861.926259189765</v>
+      </c>
+      <c r="E9">
+        <v>-1787.395</v>
+      </c>
+      <c r="F9">
+        <v>470.5050000000001</v>
+      </c>
+      <c r="G9">
+        <v>285.4</v>
+      </c>
+      <c r="H9">
+        <v>4463.6</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K9">
+        <v>213.8</v>
+      </c>
+      <c r="L9">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M9">
+        <v>21.0315735</v>
+      </c>
+      <c r="N9">
+        <v>822.6174060918366</v>
+      </c>
+      <c r="O9">
+        <v>102.8271757614796</v>
+      </c>
+      <c r="P9">
+        <v>719.7902303303571</v>
+      </c>
+      <c r="Q9">
+        <v>933.5902303303571</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.08335872924147067</v>
+      </c>
+      <c r="T9">
+        <v>0.6033962822283047</v>
+      </c>
+      <c r="U9">
+        <v>0.0447</v>
+      </c>
+      <c r="V9">
+        <v>0.125</v>
+      </c>
+      <c r="W9">
+        <v>0.0391125</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>40.11345036032784</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.0802123614250916</v>
+      </c>
+      <c r="C10">
+        <v>6612.987734675627</v>
+      </c>
+      <c r="D10">
+        <v>6865.307734675627</v>
+      </c>
+      <c r="E10">
+        <v>-1720.18</v>
+      </c>
+      <c r="F10">
+        <v>537.72</v>
+      </c>
+      <c r="G10">
+        <v>285.4</v>
+      </c>
+      <c r="H10">
+        <v>4463.6</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K10">
+        <v>213.8</v>
+      </c>
+      <c r="L10">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M10">
+        <v>24.036084</v>
+      </c>
+      <c r="N10">
+        <v>819.6128955918367</v>
+      </c>
+      <c r="O10">
+        <v>102.4516119489796</v>
+      </c>
+      <c r="P10">
+        <v>717.1612836428571</v>
+      </c>
+      <c r="Q10">
+        <v>930.9612836428571</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.08378626241857781</v>
+      </c>
+      <c r="T10">
+        <v>0.6091857635260706</v>
+      </c>
+      <c r="U10">
+        <v>0.0447</v>
+      </c>
+      <c r="V10">
+        <v>0.125</v>
+      </c>
+      <c r="W10">
+        <v>0.0391125</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>35.09926906528687</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.08016322965561547</v>
+      </c>
+      <c r="C11">
+        <v>6549.157544506259</v>
+      </c>
+      <c r="D11">
+        <v>6868.69254450626</v>
+      </c>
+      <c r="E11">
+        <v>-1652.965</v>
+      </c>
+      <c r="F11">
+        <v>604.9349999999999</v>
+      </c>
+      <c r="G11">
+        <v>285.4</v>
+      </c>
+      <c r="H11">
+        <v>4463.6</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K11">
+        <v>213.8</v>
+      </c>
+      <c r="L11">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M11">
+        <v>27.0405945</v>
+      </c>
+      <c r="N11">
+        <v>816.6083850918367</v>
+      </c>
+      <c r="O11">
+        <v>102.0760481364796</v>
+      </c>
+      <c r="P11">
+        <v>714.5323369553571</v>
+      </c>
+      <c r="Q11">
+        <v>928.3323369553571</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.08422319192924776</v>
+      </c>
+      <c r="T11">
+        <v>0.6151024861710401</v>
+      </c>
+      <c r="U11">
+        <v>0.0447</v>
+      </c>
+      <c r="V11">
+        <v>0.125</v>
+      </c>
+      <c r="W11">
+        <v>0.0391125</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>31.19935028025499</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.08011409788613935</v>
+      </c>
+      <c r="C12">
+        <v>6485.330693615901</v>
+      </c>
+      <c r="D12">
+        <v>6872.080693615901</v>
+      </c>
+      <c r="E12">
+        <v>-1585.75</v>
+      </c>
+      <c r="F12">
+        <v>672.1500000000001</v>
+      </c>
+      <c r="G12">
+        <v>285.4</v>
+      </c>
+      <c r="H12">
+        <v>4463.6</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K12">
+        <v>213.8</v>
+      </c>
+      <c r="L12">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M12">
+        <v>30.04510500000001</v>
+      </c>
+      <c r="N12">
+        <v>813.6038745918366</v>
+      </c>
+      <c r="O12">
+        <v>101.7004843239796</v>
+      </c>
+      <c r="P12">
+        <v>711.903390267857</v>
+      </c>
+      <c r="Q12">
+        <v>925.703390267857</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.08466983098459928</v>
+      </c>
+      <c r="T12">
+        <v>0.6211506915414536</v>
+      </c>
+      <c r="U12">
+        <v>0.0447</v>
+      </c>
+      <c r="V12">
+        <v>0.125</v>
+      </c>
+      <c r="W12">
+        <v>0.0391125</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>28.07941525222949</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.08006496611666322</v>
+      </c>
+      <c r="C13">
+        <v>6421.507186948529</v>
+      </c>
+      <c r="D13">
+        <v>6875.472186948529</v>
+      </c>
+      <c r="E13">
+        <v>-1518.535</v>
+      </c>
+      <c r="F13">
+        <v>739.365</v>
+      </c>
+      <c r="G13">
+        <v>285.4</v>
+      </c>
+      <c r="H13">
+        <v>4463.6</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K13">
+        <v>213.8</v>
+      </c>
+      <c r="L13">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M13">
+        <v>33.0496155</v>
+      </c>
+      <c r="N13">
+        <v>810.5993640918367</v>
+      </c>
+      <c r="O13">
+        <v>101.3249205114796</v>
+      </c>
+      <c r="P13">
+        <v>709.2744435803571</v>
+      </c>
+      <c r="Q13">
+        <v>923.0744435803572</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.0851265068726553</v>
+      </c>
+      <c r="T13">
+        <v>0.6273348116392919</v>
+      </c>
+      <c r="U13">
+        <v>0.0447</v>
+      </c>
+      <c r="V13">
+        <v>0.125</v>
+      </c>
+      <c r="W13">
+        <v>0.0391125</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>25.52674113839045</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.08001583434718709</v>
+      </c>
+      <c r="C14">
+        <v>6357.687029457889</v>
+      </c>
+      <c r="D14">
+        <v>6878.86702945789</v>
+      </c>
+      <c r="E14">
+        <v>-1451.32</v>
+      </c>
+      <c r="F14">
+        <v>806.5799999999999</v>
+      </c>
+      <c r="G14">
+        <v>285.4</v>
+      </c>
+      <c r="H14">
+        <v>4463.6</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K14">
+        <v>213.8</v>
+      </c>
+      <c r="L14">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M14">
+        <v>36.054126</v>
+      </c>
+      <c r="N14">
+        <v>807.5948535918367</v>
+      </c>
+      <c r="O14">
+        <v>100.9493566989796</v>
+      </c>
+      <c r="P14">
+        <v>706.6454968928571</v>
+      </c>
+      <c r="Q14">
+        <v>920.4454968928571</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.08559356175816715</v>
+      </c>
+      <c r="T14">
+        <v>0.6336594799211721</v>
+      </c>
+      <c r="U14">
+        <v>0.0447</v>
+      </c>
+      <c r="V14">
+        <v>0.125</v>
+      </c>
+      <c r="W14">
+        <v>0.0391125</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>23.39951271019125</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.07996670257771096</v>
+      </c>
+      <c r="C15">
+        <v>6293.870226107517</v>
+      </c>
+      <c r="D15">
+        <v>6882.265226107517</v>
+      </c>
+      <c r="E15">
+        <v>-1384.105</v>
+      </c>
+      <c r="F15">
+        <v>873.7950000000001</v>
+      </c>
+      <c r="G15">
+        <v>285.4</v>
+      </c>
+      <c r="H15">
+        <v>4463.6</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K15">
+        <v>213.8</v>
+      </c>
+      <c r="L15">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M15">
+        <v>39.05863650000001</v>
+      </c>
+      <c r="N15">
+        <v>804.5903430918366</v>
+      </c>
+      <c r="O15">
+        <v>100.5737928864796</v>
+      </c>
+      <c r="P15">
+        <v>704.016550205357</v>
+      </c>
+      <c r="Q15">
+        <v>917.8165502053571</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.08607135353759882</v>
+      </c>
+      <c r="T15">
+        <v>0.6401295428761989</v>
+      </c>
+      <c r="U15">
+        <v>0.0447</v>
+      </c>
+      <c r="V15">
+        <v>0.125</v>
+      </c>
+      <c r="W15">
+        <v>0.0391125</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>21.59955019402269</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.07991757080823485</v>
+      </c>
+      <c r="C16">
+        <v>6230.056781870753</v>
+      </c>
+      <c r="D16">
+        <v>6885.666781870754</v>
+      </c>
+      <c r="E16">
+        <v>-1316.89</v>
+      </c>
+      <c r="F16">
+        <v>941.0100000000001</v>
+      </c>
+      <c r="G16">
+        <v>285.4</v>
+      </c>
+      <c r="H16">
+        <v>4463.6</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K16">
+        <v>213.8</v>
+      </c>
+      <c r="L16">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M16">
+        <v>42.06314700000001</v>
+      </c>
+      <c r="N16">
+        <v>801.5858325918367</v>
+      </c>
+      <c r="O16">
+        <v>100.1982290739796</v>
+      </c>
+      <c r="P16">
+        <v>701.3876035178571</v>
+      </c>
+      <c r="Q16">
+        <v>915.187603517857</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.08656025675376144</v>
+      </c>
+      <c r="T16">
+        <v>0.6467500724115752</v>
+      </c>
+      <c r="U16">
+        <v>0.0447</v>
+      </c>
+      <c r="V16">
+        <v>0.125</v>
+      </c>
+      <c r="W16">
+        <v>0.0391125</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>20.05672518016392</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.0798684390387587</v>
+      </c>
+      <c r="C17">
+        <v>6166.246701730786</v>
+      </c>
+      <c r="D17">
+        <v>6889.071701730786</v>
+      </c>
+      <c r="E17">
+        <v>-1249.675</v>
+      </c>
+      <c r="F17">
+        <v>1008.225</v>
+      </c>
+      <c r="G17">
+        <v>285.4</v>
+      </c>
+      <c r="H17">
+        <v>4463.6</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K17">
+        <v>213.8</v>
+      </c>
+      <c r="L17">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M17">
+        <v>45.0676575</v>
+      </c>
+      <c r="N17">
+        <v>798.5813220918367</v>
+      </c>
+      <c r="O17">
+        <v>99.82266526147959</v>
+      </c>
+      <c r="P17">
+        <v>698.758656830357</v>
+      </c>
+      <c r="Q17">
+        <v>912.558656830357</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.08706066357501024</v>
+      </c>
+      <c r="T17">
+        <v>0.6535263791124898</v>
+      </c>
+      <c r="U17">
+        <v>0.0447</v>
+      </c>
+      <c r="V17">
+        <v>0.125</v>
+      </c>
+      <c r="W17">
+        <v>0.0391125</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>18.719610168153</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.07981930726928257</v>
+      </c>
+      <c r="C18">
+        <v>6102.439990680656</v>
+      </c>
+      <c r="D18">
+        <v>6892.479990680657</v>
+      </c>
+      <c r="E18">
+        <v>-1182.46</v>
+      </c>
+      <c r="F18">
+        <v>1075.44</v>
+      </c>
+      <c r="G18">
+        <v>285.4</v>
+      </c>
+      <c r="H18">
+        <v>4463.6</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K18">
+        <v>213.8</v>
+      </c>
+      <c r="L18">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M18">
+        <v>48.072168</v>
+      </c>
+      <c r="N18">
+        <v>795.5768115918366</v>
+      </c>
+      <c r="O18">
+        <v>99.44710144897958</v>
+      </c>
+      <c r="P18">
+        <v>696.1297101428571</v>
+      </c>
+      <c r="Q18">
+        <v>909.9297101428572</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.08757298484438403</v>
+      </c>
+      <c r="T18">
+        <v>0.6604640264491405</v>
+      </c>
+      <c r="U18">
+        <v>0.0447</v>
+      </c>
+      <c r="V18">
+        <v>0.125</v>
+      </c>
+      <c r="W18">
+        <v>0.0391125</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>17.54963453264343</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.07977017549980646</v>
+      </c>
+      <c r="C19">
+        <v>6038.636653723294</v>
+      </c>
+      <c r="D19">
+        <v>6895.891653723294</v>
+      </c>
+      <c r="E19">
+        <v>-1115.245</v>
+      </c>
+      <c r="F19">
+        <v>1142.655</v>
+      </c>
+      <c r="G19">
+        <v>285.4</v>
+      </c>
+      <c r="H19">
+        <v>4463.6</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K19">
+        <v>213.8</v>
+      </c>
+      <c r="L19">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M19">
+        <v>51.0766785</v>
+      </c>
+      <c r="N19">
+        <v>792.5723010918367</v>
+      </c>
+      <c r="O19">
+        <v>99.07153763647959</v>
+      </c>
+      <c r="P19">
+        <v>693.5007634553572</v>
+      </c>
+      <c r="Q19">
+        <v>907.3007634553571</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.0880976512045861</v>
+      </c>
+      <c r="T19">
+        <v>0.6675688460107706</v>
+      </c>
+      <c r="U19">
+        <v>0.0447</v>
+      </c>
+      <c r="V19">
+        <v>0.125</v>
+      </c>
+      <c r="W19">
+        <v>0.0391125</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>16.51730308954676</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.07972104373033034</v>
+      </c>
+      <c r="C20">
+        <v>5974.836695871543</v>
+      </c>
+      <c r="D20">
+        <v>6899.306695871544</v>
+      </c>
+      <c r="E20">
+        <v>-1048.03</v>
+      </c>
+      <c r="F20">
+        <v>1209.87</v>
+      </c>
+      <c r="G20">
+        <v>285.4</v>
+      </c>
+      <c r="H20">
+        <v>4463.6</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K20">
+        <v>213.8</v>
+      </c>
+      <c r="L20">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M20">
+        <v>54.081189</v>
+      </c>
+      <c r="N20">
+        <v>789.5677905918367</v>
+      </c>
+      <c r="O20">
+        <v>98.69597382397959</v>
+      </c>
+      <c r="P20">
+        <v>690.8718167678571</v>
+      </c>
+      <c r="Q20">
+        <v>904.6718167678571</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.0886351143052809</v>
+      </c>
+      <c r="T20">
+        <v>0.6748469538543919</v>
+      </c>
+      <c r="U20">
+        <v>0.0447</v>
+      </c>
+      <c r="V20">
+        <v>0.125</v>
+      </c>
+      <c r="W20">
+        <v>0.0391125</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>15.5996751401275</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.07967191196085421</v>
+      </c>
+      <c r="C21">
+        <v>5911.040122148177</v>
+      </c>
+      <c r="D21">
+        <v>6902.725122148177</v>
+      </c>
+      <c r="E21">
+        <v>-980.8150000000001</v>
+      </c>
+      <c r="F21">
+        <v>1277.085</v>
+      </c>
+      <c r="G21">
+        <v>285.4</v>
+      </c>
+      <c r="H21">
+        <v>4463.6</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K21">
+        <v>213.8</v>
+      </c>
+      <c r="L21">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M21">
+        <v>57.0856995</v>
+      </c>
+      <c r="N21">
+        <v>786.5632800918366</v>
+      </c>
+      <c r="O21">
+        <v>98.32041001147958</v>
+      </c>
+      <c r="P21">
+        <v>688.2428700803571</v>
+      </c>
+      <c r="Q21">
+        <v>902.042870080357</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.08918584809982</v>
+      </c>
+      <c r="T21">
+        <v>0.682304768064522</v>
+      </c>
+      <c r="U21">
+        <v>0.0447</v>
+      </c>
+      <c r="V21">
+        <v>0.125</v>
+      </c>
+      <c r="W21">
+        <v>0.0391125</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>14.77863960643658</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.07962278019137807</v>
+      </c>
+      <c r="C22">
+        <v>5847.246937585934</v>
+      </c>
+      <c r="D22">
+        <v>6906.146937585934</v>
+      </c>
+      <c r="E22">
+        <v>-913.5999999999999</v>
+      </c>
+      <c r="F22">
+        <v>1344.3</v>
+      </c>
+      <c r="G22">
+        <v>285.4</v>
+      </c>
+      <c r="H22">
+        <v>4463.6</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K22">
+        <v>213.8</v>
+      </c>
+      <c r="L22">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M22">
+        <v>60.09021000000001</v>
+      </c>
+      <c r="N22">
+        <v>783.5587695918366</v>
+      </c>
+      <c r="O22">
+        <v>97.94484619897958</v>
+      </c>
+      <c r="P22">
+        <v>685.613923392857</v>
+      </c>
+      <c r="Q22">
+        <v>899.413923392857</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.08975035023922259</v>
+      </c>
+      <c r="T22">
+        <v>0.6899490276299056</v>
+      </c>
+      <c r="U22">
+        <v>0.0447</v>
+      </c>
+      <c r="V22">
+        <v>0.125</v>
+      </c>
+      <c r="W22">
+        <v>0.0391125</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>14.03970762611474</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.07957364842190195</v>
+      </c>
+      <c r="C23">
+        <v>5783.457147227529</v>
+      </c>
+      <c r="D23">
+        <v>6909.57214722753</v>
+      </c>
+      <c r="E23">
+        <v>-846.3850000000002</v>
+      </c>
+      <c r="F23">
+        <v>1411.515</v>
+      </c>
+      <c r="G23">
+        <v>285.4</v>
+      </c>
+      <c r="H23">
+        <v>4463.6</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K23">
+        <v>213.8</v>
+      </c>
+      <c r="L23">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M23">
+        <v>63.0947205</v>
+      </c>
+      <c r="N23">
+        <v>780.5542590918367</v>
+      </c>
+      <c r="O23">
+        <v>97.56928238647959</v>
+      </c>
+      <c r="P23">
+        <v>682.9849767053571</v>
+      </c>
+      <c r="Q23">
+        <v>896.7849767053572</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.09032914357202779</v>
+      </c>
+      <c r="T23">
+        <v>0.6977868127539065</v>
+      </c>
+      <c r="U23">
+        <v>0.0447</v>
+      </c>
+      <c r="V23">
+        <v>0.125</v>
+      </c>
+      <c r="W23">
+        <v>0.0391125</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>13.37115012010928</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.07973626665242584</v>
+      </c>
+      <c r="C24">
+        <v>5704.918222161206</v>
+      </c>
+      <c r="D24">
+        <v>6898.248222161207</v>
+      </c>
+      <c r="E24">
+        <v>-779.1700000000001</v>
+      </c>
+      <c r="F24">
+        <v>1478.73</v>
+      </c>
+      <c r="G24">
+        <v>285.4</v>
+      </c>
+      <c r="H24">
+        <v>4463.6</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K24">
+        <v>213.8</v>
+      </c>
+      <c r="L24">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M24">
+        <v>67.72583400000001</v>
+      </c>
+      <c r="N24">
+        <v>775.9231455918367</v>
+      </c>
+      <c r="O24">
+        <v>96.99039319897959</v>
+      </c>
+      <c r="P24">
+        <v>678.9327523928571</v>
+      </c>
+      <c r="Q24">
+        <v>892.732752392857</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.09092277775952029</v>
+      </c>
+      <c r="T24">
+        <v>0.7058255667272407</v>
+      </c>
+      <c r="U24">
+        <v>0.0458</v>
+      </c>
+      <c r="V24">
+        <v>0.125</v>
+      </c>
+      <c r="W24">
+        <v>0.040075</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>12.4568267345639</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.07969675988294971</v>
+      </c>
+      <c r="C25">
+        <v>5640.45086250852</v>
+      </c>
+      <c r="D25">
+        <v>6900.99586250852</v>
+      </c>
+      <c r="E25">
+        <v>-711.9549999999999</v>
+      </c>
+      <c r="F25">
+        <v>1545.945</v>
+      </c>
+      <c r="G25">
+        <v>285.4</v>
+      </c>
+      <c r="H25">
+        <v>4463.6</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K25">
+        <v>213.8</v>
+      </c>
+      <c r="L25">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M25">
+        <v>70.804281</v>
+      </c>
+      <c r="N25">
+        <v>772.8446985918367</v>
+      </c>
+      <c r="O25">
+        <v>96.60558732397959</v>
+      </c>
+      <c r="P25">
+        <v>676.2391112678572</v>
+      </c>
+      <c r="Q25">
+        <v>890.0391112678572</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.09153183101681781</v>
+      </c>
+      <c r="T25">
+        <v>0.7140731195050771</v>
+      </c>
+      <c r="U25">
+        <v>0.0458</v>
+      </c>
+      <c r="V25">
+        <v>0.125</v>
+      </c>
+      <c r="W25">
+        <v>0.040075</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>11.91522557219156</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.07965725311347358</v>
+      </c>
+      <c r="C26">
+        <v>5575.985692552546</v>
+      </c>
+      <c r="D26">
+        <v>6903.745692552546</v>
+      </c>
+      <c r="E26">
+        <v>-644.7400000000002</v>
+      </c>
+      <c r="F26">
+        <v>1613.16</v>
+      </c>
+      <c r="G26">
+        <v>285.4</v>
+      </c>
+      <c r="H26">
+        <v>4463.6</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K26">
+        <v>213.8</v>
+      </c>
+      <c r="L26">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M26">
+        <v>73.882728</v>
+      </c>
+      <c r="N26">
+        <v>769.7662515918366</v>
+      </c>
+      <c r="O26">
+        <v>96.22078144897958</v>
+      </c>
+      <c r="P26">
+        <v>673.5454701428571</v>
+      </c>
+      <c r="Q26">
+        <v>887.345470142857</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.0921569119914126</v>
+      </c>
+      <c r="T26">
+        <v>0.7225377131454882</v>
+      </c>
+      <c r="U26">
+        <v>0.0458</v>
+      </c>
+      <c r="V26">
+        <v>0.125</v>
+      </c>
+      <c r="W26">
+        <v>0.040075</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>11.41875784001691</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.07961774634399746</v>
+      </c>
+      <c r="C27">
+        <v>5511.522714911902</v>
+      </c>
+      <c r="D27">
+        <v>6906.497714911902</v>
+      </c>
+      <c r="E27">
+        <v>-577.5250000000001</v>
+      </c>
+      <c r="F27">
+        <v>1680.375</v>
+      </c>
+      <c r="G27">
+        <v>285.4</v>
+      </c>
+      <c r="H27">
+        <v>4463.6</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K27">
+        <v>213.8</v>
+      </c>
+      <c r="L27">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M27">
+        <v>76.961175</v>
+      </c>
+      <c r="N27">
+        <v>766.6878045918367</v>
+      </c>
+      <c r="O27">
+        <v>95.83597557397958</v>
+      </c>
+      <c r="P27">
+        <v>670.8518290178571</v>
+      </c>
+      <c r="Q27">
+        <v>884.6518290178572</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.0927986617919966</v>
+      </c>
+      <c r="T27">
+        <v>0.7312280292829768</v>
+      </c>
+      <c r="U27">
+        <v>0.0458</v>
+      </c>
+      <c r="V27">
+        <v>0.125</v>
+      </c>
+      <c r="W27">
+        <v>0.040075</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>10.96200752641623</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.07957823957452133</v>
+      </c>
+      <c r="C28">
+        <v>5447.061932209387</v>
+      </c>
+      <c r="D28">
+        <v>6909.251932209388</v>
+      </c>
+      <c r="E28">
+        <v>-510.3099999999999</v>
+      </c>
+      <c r="F28">
+        <v>1747.59</v>
+      </c>
+      <c r="G28">
+        <v>285.4</v>
+      </c>
+      <c r="H28">
+        <v>4463.6</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K28">
+        <v>213.8</v>
+      </c>
+      <c r="L28">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M28">
+        <v>80.03962200000001</v>
+      </c>
+      <c r="N28">
+        <v>763.6093575918367</v>
+      </c>
+      <c r="O28">
+        <v>95.45116969897958</v>
+      </c>
+      <c r="P28">
+        <v>668.1581878928571</v>
+      </c>
+      <c r="Q28">
+        <v>881.958187892857</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.09345775618178559</v>
+      </c>
+      <c r="T28">
+        <v>0.740153218829587</v>
+      </c>
+      <c r="U28">
+        <v>0.0458</v>
+      </c>
+      <c r="V28">
+        <v>0.125</v>
+      </c>
+      <c r="W28">
+        <v>0.040075</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>10.5403918523233</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.07953873280504521</v>
+      </c>
+      <c r="C29">
+        <v>5382.603347071982</v>
+      </c>
+      <c r="D29">
+        <v>6912.008347071983</v>
+      </c>
+      <c r="E29">
+        <v>-443.095</v>
+      </c>
+      <c r="F29">
+        <v>1814.805</v>
+      </c>
+      <c r="G29">
+        <v>285.4</v>
+      </c>
+      <c r="H29">
+        <v>4463.6</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K29">
+        <v>213.8</v>
+      </c>
+      <c r="L29">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M29">
+        <v>83.11806900000001</v>
+      </c>
+      <c r="N29">
+        <v>760.5309105918367</v>
+      </c>
+      <c r="O29">
+        <v>95.06636382397959</v>
+      </c>
+      <c r="P29">
+        <v>665.4645467678571</v>
+      </c>
+      <c r="Q29">
+        <v>879.2645467678572</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.09413490795211672</v>
+      </c>
+      <c r="T29">
+        <v>0.7493229341172001</v>
+      </c>
+      <c r="U29">
+        <v>0.0458</v>
+      </c>
+      <c r="V29">
+        <v>0.125</v>
+      </c>
+      <c r="W29">
+        <v>0.040075</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>10.15000696890392</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.08003822603556909</v>
+      </c>
+      <c r="C30">
+        <v>5280.699422284399</v>
+      </c>
+      <c r="D30">
+        <v>6877.319422284399</v>
+      </c>
+      <c r="E30">
+        <v>-375.8799999999999</v>
+      </c>
+      <c r="F30">
+        <v>1882.02</v>
+      </c>
+      <c r="G30">
+        <v>285.4</v>
+      </c>
+      <c r="H30">
+        <v>4463.6</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K30">
+        <v>213.8</v>
+      </c>
+      <c r="L30">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M30">
+        <v>90.33696000000002</v>
+      </c>
+      <c r="N30">
+        <v>753.3120195918367</v>
+      </c>
+      <c r="O30">
+        <v>94.16400244897959</v>
+      </c>
+      <c r="P30">
+        <v>659.1480171428572</v>
+      </c>
+      <c r="Q30">
+        <v>872.9480171428572</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.09483086949384595</v>
+      </c>
+      <c r="T30">
+        <v>0.7587473637183578</v>
+      </c>
+      <c r="U30">
+        <v>0.048</v>
+      </c>
+      <c r="V30">
+        <v>0.125</v>
+      </c>
+      <c r="W30">
+        <v>0.042</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>9.338912662013826</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.08001796926609293</v>
+      </c>
+      <c r="C31">
+        <v>5214.884443962845</v>
+      </c>
+      <c r="D31">
+        <v>6878.719443962845</v>
+      </c>
+      <c r="E31">
+        <v>-308.6650000000002</v>
+      </c>
+      <c r="F31">
+        <v>1949.235</v>
+      </c>
+      <c r="G31">
+        <v>285.4</v>
+      </c>
+      <c r="H31">
+        <v>4463.6</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K31">
+        <v>213.8</v>
+      </c>
+      <c r="L31">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M31">
+        <v>93.56327999999999</v>
+      </c>
+      <c r="N31">
+        <v>750.0856995918367</v>
+      </c>
+      <c r="O31">
+        <v>93.76071244897959</v>
+      </c>
+      <c r="P31">
+        <v>656.3249871428571</v>
+      </c>
+      <c r="Q31">
+        <v>870.1249871428572</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.0955464355860464</v>
+      </c>
+      <c r="T31">
+        <v>0.768437270209689</v>
+      </c>
+      <c r="U31">
+        <v>0.048</v>
+      </c>
+      <c r="V31">
+        <v>0.125</v>
+      </c>
+      <c r="W31">
+        <v>0.042</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>9.016881190909904</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.07999771249661682</v>
+      </c>
+      <c r="C32">
+        <v>5149.07003576452</v>
+      </c>
+      <c r="D32">
+        <v>6880.12003576452</v>
+      </c>
+      <c r="E32">
+        <v>-241.4500000000003</v>
+      </c>
+      <c r="F32">
+        <v>2016.45</v>
+      </c>
+      <c r="G32">
+        <v>285.4</v>
+      </c>
+      <c r="H32">
+        <v>4463.6</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K32">
+        <v>213.8</v>
+      </c>
+      <c r="L32">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M32">
+        <v>96.78959999999999</v>
+      </c>
+      <c r="N32">
+        <v>746.8593795918367</v>
+      </c>
+      <c r="O32">
+        <v>93.35742244897959</v>
+      </c>
+      <c r="P32">
+        <v>653.5019571428571</v>
+      </c>
+      <c r="Q32">
+        <v>867.3019571428572</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.09628244642373832</v>
+      </c>
+      <c r="T32">
+        <v>0.7784040311722012</v>
+      </c>
+      <c r="U32">
+        <v>0.048</v>
+      </c>
+      <c r="V32">
+        <v>0.125</v>
+      </c>
+      <c r="W32">
+        <v>0.042</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>8.716318484546241</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.0799774557271407</v>
+      </c>
+      <c r="C33">
+        <v>5083.256198037752</v>
+      </c>
+      <c r="D33">
+        <v>6881.521198037753</v>
+      </c>
+      <c r="E33">
+        <v>-174.2350000000001</v>
+      </c>
+      <c r="F33">
+        <v>2083.665</v>
+      </c>
+      <c r="G33">
+        <v>285.4</v>
+      </c>
+      <c r="H33">
+        <v>4463.6</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K33">
+        <v>213.8</v>
+      </c>
+      <c r="L33">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M33">
+        <v>100.01592</v>
+      </c>
+      <c r="N33">
+        <v>743.6330595918366</v>
+      </c>
+      <c r="O33">
+        <v>92.95413244897958</v>
+      </c>
+      <c r="P33">
+        <v>650.678927142857</v>
+      </c>
+      <c r="Q33">
+        <v>864.4789271428569</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.09703979090889957</v>
+      </c>
+      <c r="T33">
+        <v>0.7886596837568153</v>
+      </c>
+      <c r="U33">
+        <v>0.048</v>
+      </c>
+      <c r="V33">
+        <v>0.125</v>
+      </c>
+      <c r="W33">
+        <v>0.042</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>8.435146920528618</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.07995719895766457</v>
+      </c>
+      <c r="C34">
+        <v>5017.442931131148</v>
+      </c>
+      <c r="D34">
+        <v>6882.922931131148</v>
+      </c>
+      <c r="E34">
+        <v>-107.02</v>
+      </c>
+      <c r="F34">
+        <v>2150.88</v>
+      </c>
+      <c r="G34">
+        <v>285.4</v>
+      </c>
+      <c r="H34">
+        <v>4463.6</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K34">
+        <v>213.8</v>
+      </c>
+      <c r="L34">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M34">
+        <v>103.24224</v>
+      </c>
+      <c r="N34">
+        <v>740.4067395918366</v>
+      </c>
+      <c r="O34">
+        <v>92.55084244897958</v>
+      </c>
+      <c r="P34">
+        <v>647.8558971428571</v>
+      </c>
+      <c r="Q34">
+        <v>861.6558971428572</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.09781941023185967</v>
+      </c>
+      <c r="T34">
+        <v>0.7992169731821532</v>
+      </c>
+      <c r="U34">
+        <v>0.048</v>
+      </c>
+      <c r="V34">
+        <v>0.125</v>
+      </c>
+      <c r="W34">
+        <v>0.042</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>8.171548579262097</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.07993694218818845</v>
+      </c>
+      <c r="C35">
+        <v>4951.630235393596</v>
+      </c>
+      <c r="D35">
+        <v>6884.325235393597</v>
+      </c>
+      <c r="E35">
+        <v>-39.80499999999984</v>
+      </c>
+      <c r="F35">
+        <v>2218.095</v>
+      </c>
+      <c r="G35">
+        <v>285.4</v>
+      </c>
+      <c r="H35">
+        <v>4463.6</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K35">
+        <v>213.8</v>
+      </c>
+      <c r="L35">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M35">
+        <v>106.46856</v>
+      </c>
+      <c r="N35">
+        <v>737.1804195918367</v>
+      </c>
+      <c r="O35">
+        <v>92.14755244897958</v>
+      </c>
+      <c r="P35">
+        <v>645.0328671428571</v>
+      </c>
+      <c r="Q35">
+        <v>858.8328671428571</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.0986223017734156</v>
+      </c>
+      <c r="T35">
+        <v>0.8100894055754116</v>
+      </c>
+      <c r="U35">
+        <v>0.048</v>
+      </c>
+      <c r="V35">
+        <v>0.125</v>
+      </c>
+      <c r="W35">
+        <v>0.042</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>7.923925895042035</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.08036293541871231</v>
+      </c>
+      <c r="C36">
+        <v>4855.045064630003</v>
+      </c>
+      <c r="D36">
+        <v>6854.955064630004</v>
+      </c>
+      <c r="E36">
+        <v>27.40999999999985</v>
+      </c>
+      <c r="F36">
+        <v>2285.31</v>
+      </c>
+      <c r="G36">
+        <v>285.4</v>
+      </c>
+      <c r="H36">
+        <v>4463.6</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K36">
+        <v>213.8</v>
+      </c>
+      <c r="L36">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M36">
+        <v>113.122845</v>
+      </c>
+      <c r="N36">
+        <v>730.5261345918367</v>
+      </c>
+      <c r="O36">
+        <v>91.31576682397959</v>
+      </c>
+      <c r="P36">
+        <v>639.2103677678571</v>
+      </c>
+      <c r="Q36">
+        <v>853.0103677678571</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.09944952336168535</v>
+      </c>
+      <c r="T36">
+        <v>0.8212913056169507</v>
+      </c>
+      <c r="U36">
+        <v>0.0495</v>
+      </c>
+      <c r="V36">
+        <v>0.125</v>
+      </c>
+      <c r="W36">
+        <v>0.0433125</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>7.457812607098386</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.0803558036492362</v>
+      </c>
+      <c r="C37">
+        <v>4788.319702864448</v>
+      </c>
+      <c r="D37">
+        <v>6855.444702864448</v>
+      </c>
+      <c r="E37">
+        <v>94.625</v>
+      </c>
+      <c r="F37">
+        <v>2352.525</v>
+      </c>
+      <c r="G37">
+        <v>285.4</v>
+      </c>
+      <c r="H37">
+        <v>4463.6</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K37">
+        <v>213.8</v>
+      </c>
+      <c r="L37">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M37">
+        <v>116.4499875</v>
+      </c>
+      <c r="N37">
+        <v>727.1989920918367</v>
+      </c>
+      <c r="O37">
+        <v>90.89987401147958</v>
+      </c>
+      <c r="P37">
+        <v>636.2991180803571</v>
+      </c>
+      <c r="Q37">
+        <v>850.0991180803571</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1003021979219018</v>
+      </c>
+      <c r="T37">
+        <v>0.8328378795059217</v>
+      </c>
+      <c r="U37">
+        <v>0.0495</v>
+      </c>
+      <c r="V37">
+        <v>0.125</v>
+      </c>
+      <c r="W37">
+        <v>0.0433125</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>7.244732246895575</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.08034867187976008</v>
+      </c>
+      <c r="C38">
+        <v>4721.594411052008</v>
+      </c>
+      <c r="D38">
+        <v>6855.934411052008</v>
+      </c>
+      <c r="E38">
+        <v>161.8399999999997</v>
+      </c>
+      <c r="F38">
+        <v>2419.74</v>
+      </c>
+      <c r="G38">
+        <v>285.4</v>
+      </c>
+      <c r="H38">
+        <v>4463.6</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K38">
+        <v>213.8</v>
+      </c>
+      <c r="L38">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M38">
+        <v>119.77713</v>
+      </c>
+      <c r="N38">
+        <v>723.8718495918367</v>
+      </c>
+      <c r="O38">
+        <v>90.48398119897959</v>
+      </c>
+      <c r="P38">
+        <v>633.3878683928572</v>
+      </c>
+      <c r="Q38">
+        <v>847.1878683928571</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1011815185621251</v>
+      </c>
+      <c r="T38">
+        <v>0.844745283828923</v>
+      </c>
+      <c r="U38">
+        <v>0.0495</v>
+      </c>
+      <c r="V38">
+        <v>0.125</v>
+      </c>
+      <c r="W38">
+        <v>0.0433125</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>7.04348968448181</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.08034154011028394</v>
+      </c>
+      <c r="C39">
+        <v>4654.869189207673</v>
+      </c>
+      <c r="D39">
+        <v>6856.424189207673</v>
+      </c>
+      <c r="E39">
+        <v>229.0549999999998</v>
+      </c>
+      <c r="F39">
+        <v>2486.955</v>
+      </c>
+      <c r="G39">
+        <v>285.4</v>
+      </c>
+      <c r="H39">
+        <v>4463.6</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K39">
+        <v>213.8</v>
+      </c>
+      <c r="L39">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M39">
+        <v>123.1042725</v>
+      </c>
+      <c r="N39">
+        <v>720.5447070918367</v>
+      </c>
+      <c r="O39">
+        <v>90.06808838647959</v>
+      </c>
+      <c r="P39">
+        <v>630.4766187053572</v>
+      </c>
+      <c r="Q39">
+        <v>844.2766187053571</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1020887541433078</v>
+      </c>
+      <c r="T39">
+        <v>0.8570307009875751</v>
+      </c>
+      <c r="U39">
+        <v>0.0495</v>
+      </c>
+      <c r="V39">
+        <v>0.125</v>
+      </c>
+      <c r="W39">
+        <v>0.0433125</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>6.853125098414734</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.08033440834080782</v>
+      </c>
+      <c r="C40">
+        <v>4588.14403734644</v>
+      </c>
+      <c r="D40">
+        <v>6856.914037346441</v>
+      </c>
+      <c r="E40">
+        <v>296.27</v>
+      </c>
+      <c r="F40">
+        <v>2554.17</v>
+      </c>
+      <c r="G40">
+        <v>285.4</v>
+      </c>
+      <c r="H40">
+        <v>4463.6</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K40">
+        <v>213.8</v>
+      </c>
+      <c r="L40">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M40">
+        <v>126.431415</v>
+      </c>
+      <c r="N40">
+        <v>717.2175645918367</v>
+      </c>
+      <c r="O40">
+        <v>89.65219557397958</v>
+      </c>
+      <c r="P40">
+        <v>627.5653690178571</v>
+      </c>
+      <c r="Q40">
+        <v>841.3653690178571</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1030252553883997</v>
+      </c>
+      <c r="T40">
+        <v>0.8697124219255385</v>
+      </c>
+      <c r="U40">
+        <v>0.0495</v>
+      </c>
+      <c r="V40">
+        <v>0.125</v>
+      </c>
+      <c r="W40">
+        <v>0.0433125</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>6.67277970108803</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.08032727657133169</v>
+      </c>
+      <c r="C41">
+        <v>4521.41895548331</v>
+      </c>
+      <c r="D41">
+        <v>6857.403955483311</v>
+      </c>
+      <c r="E41">
+        <v>363.4850000000001</v>
+      </c>
+      <c r="F41">
+        <v>2621.385</v>
+      </c>
+      <c r="G41">
+        <v>285.4</v>
+      </c>
+      <c r="H41">
+        <v>4463.6</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K41">
+        <v>213.8</v>
+      </c>
+      <c r="L41">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M41">
+        <v>129.7585575</v>
+      </c>
+      <c r="N41">
+        <v>713.8904220918366</v>
+      </c>
+      <c r="O41">
+        <v>89.23630276147958</v>
+      </c>
+      <c r="P41">
+        <v>624.654119330357</v>
+      </c>
+      <c r="Q41">
+        <v>838.4541193303571</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.103992461592347</v>
+      </c>
+      <c r="T41">
+        <v>0.8828099369926157</v>
+      </c>
+      <c r="U41">
+        <v>0.0495</v>
+      </c>
+      <c r="V41">
+        <v>0.125</v>
+      </c>
+      <c r="W41">
+        <v>0.0433125</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>6.501682785675515</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.08032014480185558</v>
+      </c>
+      <c r="C42">
+        <v>4454.693943633288</v>
+      </c>
+      <c r="D42">
+        <v>6857.893943633288</v>
+      </c>
+      <c r="E42">
+        <v>430.7000000000003</v>
+      </c>
+      <c r="F42">
+        <v>2688.6</v>
+      </c>
+      <c r="G42">
+        <v>285.4</v>
+      </c>
+      <c r="H42">
+        <v>4463.6</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K42">
+        <v>213.8</v>
+      </c>
+      <c r="L42">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M42">
+        <v>133.0857</v>
+      </c>
+      <c r="N42">
+        <v>710.5632795918366</v>
+      </c>
+      <c r="O42">
+        <v>88.82040994897957</v>
+      </c>
+      <c r="P42">
+        <v>621.742869642857</v>
+      </c>
+      <c r="Q42">
+        <v>835.5428696428571</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1049919080030926</v>
+      </c>
+      <c r="T42">
+        <v>0.8963440358952621</v>
+      </c>
+      <c r="U42">
+        <v>0.0495</v>
+      </c>
+      <c r="V42">
+        <v>0.125</v>
+      </c>
+      <c r="W42">
+        <v>0.0433125</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>6.339140716033627</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.08031301303237944</v>
+      </c>
+      <c r="C43">
+        <v>4387.969001811385</v>
+      </c>
+      <c r="D43">
+        <v>6858.384001811385</v>
+      </c>
+      <c r="E43">
+        <v>497.915</v>
+      </c>
+      <c r="F43">
+        <v>2755.815</v>
+      </c>
+      <c r="G43">
+        <v>285.4</v>
+      </c>
+      <c r="H43">
+        <v>4463.6</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K43">
+        <v>213.8</v>
+      </c>
+      <c r="L43">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M43">
+        <v>136.4128425</v>
+      </c>
+      <c r="N43">
+        <v>707.2361370918367</v>
+      </c>
+      <c r="O43">
+        <v>88.40451713647958</v>
+      </c>
+      <c r="P43">
+        <v>618.831619955357</v>
+      </c>
+      <c r="Q43">
+        <v>832.6316199553571</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1060252339531855</v>
+      </c>
+      <c r="T43">
+        <v>0.9103369178115575</v>
+      </c>
+      <c r="U43">
+        <v>0.0495</v>
+      </c>
+      <c r="V43">
+        <v>0.125</v>
+      </c>
+      <c r="W43">
+        <v>0.0433125</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>6.184527527837686</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.08082038126290333</v>
+      </c>
+      <c r="C44">
+        <v>4286.064153356708</v>
+      </c>
+      <c r="D44">
+        <v>6823.694153356708</v>
+      </c>
+      <c r="E44">
+        <v>565.1299999999997</v>
+      </c>
+      <c r="F44">
+        <v>2823.03</v>
+      </c>
+      <c r="G44">
+        <v>285.4</v>
+      </c>
+      <c r="H44">
+        <v>4463.6</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K44">
+        <v>213.8</v>
+      </c>
+      <c r="L44">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M44">
+        <v>143.692227</v>
+      </c>
+      <c r="N44">
+        <v>699.9567525918367</v>
+      </c>
+      <c r="O44">
+        <v>87.49459407397958</v>
+      </c>
+      <c r="P44">
+        <v>612.4621585178571</v>
+      </c>
+      <c r="Q44">
+        <v>826.2621585178572</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1070941918325919</v>
+      </c>
+      <c r="T44">
+        <v>0.9248123128973802</v>
+      </c>
+      <c r="U44">
+        <v>0.0509</v>
+      </c>
+      <c r="V44">
+        <v>0.125</v>
+      </c>
+      <c r="W44">
+        <v>0.0445375</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>5.871222105784724</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.0808254994934272</v>
+      </c>
+      <c r="C45">
+        <v>4218.500996805586</v>
+      </c>
+      <c r="D45">
+        <v>6823.345996805586</v>
+      </c>
+      <c r="E45">
+        <v>632.3449999999998</v>
+      </c>
+      <c r="F45">
+        <v>2890.245</v>
+      </c>
+      <c r="G45">
+        <v>285.4</v>
+      </c>
+      <c r="H45">
+        <v>4463.6</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K45">
+        <v>213.8</v>
+      </c>
+      <c r="L45">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M45">
+        <v>147.1134705</v>
+      </c>
+      <c r="N45">
+        <v>696.5355090918367</v>
+      </c>
+      <c r="O45">
+        <v>87.06693863647959</v>
+      </c>
+      <c r="P45">
+        <v>609.4685704553572</v>
+      </c>
+      <c r="Q45">
+        <v>823.2685704553571</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1082006570060126</v>
+      </c>
+      <c r="T45">
+        <v>0.9397956165827055</v>
+      </c>
+      <c r="U45">
+        <v>0.0509</v>
+      </c>
+      <c r="V45">
+        <v>0.125</v>
+      </c>
+      <c r="W45">
+        <v>0.0445375</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>5.734682056812987</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.08083061772395107</v>
+      </c>
+      <c r="C46">
+        <v>4150.937875779738</v>
+      </c>
+      <c r="D46">
+        <v>6822.997875779738</v>
+      </c>
+      <c r="E46">
+        <v>699.5599999999999</v>
+      </c>
+      <c r="F46">
+        <v>2957.46</v>
+      </c>
+      <c r="G46">
+        <v>285.4</v>
+      </c>
+      <c r="H46">
+        <v>4463.6</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K46">
+        <v>213.8</v>
+      </c>
+      <c r="L46">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M46">
+        <v>150.534714</v>
+      </c>
+      <c r="N46">
+        <v>693.1142655918367</v>
+      </c>
+      <c r="O46">
+        <v>86.63928319897958</v>
+      </c>
+      <c r="P46">
+        <v>606.4749823928571</v>
+      </c>
+      <c r="Q46">
+        <v>820.2749823928571</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1093466387927698</v>
+      </c>
+      <c r="T46">
+        <v>0.9553140382567925</v>
+      </c>
+      <c r="U46">
+        <v>0.0509</v>
+      </c>
+      <c r="V46">
+        <v>0.125</v>
+      </c>
+      <c r="W46">
+        <v>0.0445375</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>5.6043483737036</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.08083573595447494</v>
+      </c>
+      <c r="C47">
+        <v>4083.374790273725</v>
+      </c>
+      <c r="D47">
+        <v>6822.649790273726</v>
+      </c>
+      <c r="E47">
+        <v>766.7750000000001</v>
+      </c>
+      <c r="F47">
+        <v>3024.675</v>
+      </c>
+      <c r="G47">
+        <v>285.4</v>
+      </c>
+      <c r="H47">
+        <v>4463.6</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K47">
+        <v>213.8</v>
+      </c>
+      <c r="L47">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M47">
+        <v>153.9559575</v>
+      </c>
+      <c r="N47">
+        <v>689.6930220918366</v>
+      </c>
+      <c r="O47">
+        <v>86.21162776147958</v>
+      </c>
+      <c r="P47">
+        <v>603.481394330357</v>
+      </c>
+      <c r="Q47">
+        <v>817.281394330357</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1105342926444999</v>
+      </c>
+      <c r="T47">
+        <v>0.9713967661735734</v>
+      </c>
+      <c r="U47">
+        <v>0.0509</v>
+      </c>
+      <c r="V47">
+        <v>0.125</v>
+      </c>
+      <c r="W47">
+        <v>0.0445375</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>5.479807298732409</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.08084085418499883</v>
+      </c>
+      <c r="C48">
+        <v>4015.811740282111</v>
+      </c>
+      <c r="D48">
+        <v>6822.301740282111</v>
+      </c>
+      <c r="E48">
+        <v>833.9900000000002</v>
+      </c>
+      <c r="F48">
+        <v>3091.89</v>
+      </c>
+      <c r="G48">
+        <v>285.4</v>
+      </c>
+      <c r="H48">
+        <v>4463.6</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K48">
+        <v>213.8</v>
+      </c>
+      <c r="L48">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M48">
+        <v>157.377201</v>
+      </c>
+      <c r="N48">
+        <v>686.2717785918367</v>
+      </c>
+      <c r="O48">
+        <v>85.78397232397958</v>
+      </c>
+      <c r="P48">
+        <v>600.4878062678571</v>
+      </c>
+      <c r="Q48">
+        <v>814.2878062678571</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1117659336759237</v>
+      </c>
+      <c r="T48">
+        <v>0.9880751506798648</v>
+      </c>
+      <c r="U48">
+        <v>0.0509</v>
+      </c>
+      <c r="V48">
+        <v>0.125</v>
+      </c>
+      <c r="W48">
+        <v>0.0445375</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>5.360681053107792</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.08084597241552269</v>
+      </c>
+      <c r="C49">
+        <v>3948.248725799465</v>
+      </c>
+      <c r="D49">
+        <v>6821.953725799465</v>
+      </c>
+      <c r="E49">
+        <v>901.2049999999999</v>
+      </c>
+      <c r="F49">
+        <v>3159.105</v>
+      </c>
+      <c r="G49">
+        <v>285.4</v>
+      </c>
+      <c r="H49">
+        <v>4463.6</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K49">
+        <v>213.8</v>
+      </c>
+      <c r="L49">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M49">
+        <v>160.7984445</v>
+      </c>
+      <c r="N49">
+        <v>682.8505350918367</v>
+      </c>
+      <c r="O49">
+        <v>85.35631688647959</v>
+      </c>
+      <c r="P49">
+        <v>597.4942182053571</v>
+      </c>
+      <c r="Q49">
+        <v>811.2942182053571</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1130440517274013</v>
+      </c>
+      <c r="T49">
+        <v>1.005382908186394</v>
+      </c>
+      <c r="U49">
+        <v>0.0509</v>
+      </c>
+      <c r="V49">
+        <v>0.125</v>
+      </c>
+      <c r="W49">
+        <v>0.0445375</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>5.246624009424647</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.08085109064604656</v>
+      </c>
+      <c r="C50">
+        <v>3880.68574682035</v>
+      </c>
+      <c r="D50">
+        <v>6821.60574682035</v>
+      </c>
+      <c r="E50">
+        <v>968.4199999999996</v>
+      </c>
+      <c r="F50">
+        <v>3226.32</v>
+      </c>
+      <c r="G50">
+        <v>285.4</v>
+      </c>
+      <c r="H50">
+        <v>4463.6</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K50">
+        <v>213.8</v>
+      </c>
+      <c r="L50">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M50">
+        <v>164.219688</v>
+      </c>
+      <c r="N50">
+        <v>679.4292915918367</v>
+      </c>
+      <c r="O50">
+        <v>84.92866144897958</v>
+      </c>
+      <c r="P50">
+        <v>594.5006301428571</v>
+      </c>
+      <c r="Q50">
+        <v>808.300630142857</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1143713281654741</v>
+      </c>
+      <c r="T50">
+        <v>1.023356348673943</v>
+      </c>
+      <c r="U50">
+        <v>0.0509</v>
+      </c>
+      <c r="V50">
+        <v>0.125</v>
+      </c>
+      <c r="W50">
+        <v>0.0445375</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>5.137319342561634</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.08085620887657044</v>
+      </c>
+      <c r="C51">
+        <v>3813.122803339332</v>
+      </c>
+      <c r="D51">
+        <v>6821.257803339332</v>
+      </c>
+      <c r="E51">
+        <v>1035.635</v>
+      </c>
+      <c r="F51">
+        <v>3293.535</v>
+      </c>
+      <c r="G51">
+        <v>285.4</v>
+      </c>
+      <c r="H51">
+        <v>4463.6</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K51">
+        <v>213.8</v>
+      </c>
+      <c r="L51">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M51">
+        <v>167.6409315</v>
+      </c>
+      <c r="N51">
+        <v>676.0080480918367</v>
+      </c>
+      <c r="O51">
+        <v>84.50100601147959</v>
+      </c>
+      <c r="P51">
+        <v>591.5070420803571</v>
+      </c>
+      <c r="Q51">
+        <v>805.3070420803572</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.115750654659942</v>
+      </c>
+      <c r="T51">
+        <v>1.042034629964925</v>
+      </c>
+      <c r="U51">
+        <v>0.0509</v>
+      </c>
+      <c r="V51">
+        <v>0.125</v>
+      </c>
+      <c r="W51">
+        <v>0.0445375</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>5.032476090672621</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.08086132710709432</v>
+      </c>
+      <c r="C52">
+        <v>3745.559895350982</v>
+      </c>
+      <c r="D52">
+        <v>6820.909895350982</v>
+      </c>
+      <c r="E52">
+        <v>1102.85</v>
+      </c>
+      <c r="F52">
+        <v>3360.75</v>
+      </c>
+      <c r="G52">
+        <v>285.4</v>
+      </c>
+      <c r="H52">
+        <v>4463.6</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K52">
+        <v>213.8</v>
+      </c>
+      <c r="L52">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M52">
+        <v>171.062175</v>
+      </c>
+      <c r="N52">
+        <v>672.5868045918367</v>
+      </c>
+      <c r="O52">
+        <v>84.07335057397958</v>
+      </c>
+      <c r="P52">
+        <v>588.513454017857</v>
+      </c>
+      <c r="Q52">
+        <v>802.3134540178571</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1171851542141886</v>
+      </c>
+      <c r="T52">
+        <v>1.061460042507547</v>
+      </c>
+      <c r="U52">
+        <v>0.0509</v>
+      </c>
+      <c r="V52">
+        <v>0.125</v>
+      </c>
+      <c r="W52">
+        <v>0.0445375</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>4.931826568859169</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.08086644533761819</v>
+      </c>
+      <c r="C53">
+        <v>3677.997022849869</v>
+      </c>
+      <c r="D53">
+        <v>6820.562022849869</v>
+      </c>
+      <c r="E53">
+        <v>1170.065</v>
+      </c>
+      <c r="F53">
+        <v>3427.965</v>
+      </c>
+      <c r="G53">
+        <v>285.4</v>
+      </c>
+      <c r="H53">
+        <v>4463.6</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K53">
+        <v>213.8</v>
+      </c>
+      <c r="L53">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M53">
+        <v>174.4834185</v>
+      </c>
+      <c r="N53">
+        <v>669.1655610918367</v>
+      </c>
+      <c r="O53">
+        <v>83.64569513647959</v>
+      </c>
+      <c r="P53">
+        <v>585.5198659553571</v>
+      </c>
+      <c r="Q53">
+        <v>799.319865955357</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1186782047706494</v>
+      </c>
+      <c r="T53">
+        <v>1.0816783290315</v>
+      </c>
+      <c r="U53">
+        <v>0.0509</v>
+      </c>
+      <c r="V53">
+        <v>0.125</v>
+      </c>
+      <c r="W53">
+        <v>0.0445375</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>4.835124087116832</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.08087156356814205</v>
+      </c>
+      <c r="C54">
+        <v>3610.434185830564</v>
+      </c>
+      <c r="D54">
+        <v>6820.214185830565</v>
+      </c>
+      <c r="E54">
+        <v>1237.28</v>
+      </c>
+      <c r="F54">
+        <v>3495.18</v>
+      </c>
+      <c r="G54">
+        <v>285.4</v>
+      </c>
+      <c r="H54">
+        <v>4463.6</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K54">
+        <v>213.8</v>
+      </c>
+      <c r="L54">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M54">
+        <v>177.904662</v>
+      </c>
+      <c r="N54">
+        <v>665.7443175918366</v>
+      </c>
+      <c r="O54">
+        <v>83.21803969897958</v>
+      </c>
+      <c r="P54">
+        <v>582.526277892857</v>
+      </c>
+      <c r="Q54">
+        <v>796.326277892857</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1202334657669626</v>
+      </c>
+      <c r="T54">
+        <v>1.102739044160618</v>
+      </c>
+      <c r="U54">
+        <v>0.0509</v>
+      </c>
+      <c r="V54">
+        <v>0.125</v>
+      </c>
+      <c r="W54">
+        <v>0.0445375</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>4.742140931595354</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.08087668179866593</v>
+      </c>
+      <c r="C55">
+        <v>3542.871384287638</v>
+      </c>
+      <c r="D55">
+        <v>6819.866384287639</v>
+      </c>
+      <c r="E55">
+        <v>1304.495</v>
+      </c>
+      <c r="F55">
+        <v>3562.395</v>
+      </c>
+      <c r="G55">
+        <v>285.4</v>
+      </c>
+      <c r="H55">
+        <v>4463.6</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K55">
+        <v>213.8</v>
+      </c>
+      <c r="L55">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M55">
+        <v>181.3259055</v>
+      </c>
+      <c r="N55">
+        <v>662.3230740918367</v>
+      </c>
+      <c r="O55">
+        <v>82.79038426147959</v>
+      </c>
+      <c r="P55">
+        <v>579.5326898303571</v>
+      </c>
+      <c r="Q55">
+        <v>793.3326898303571</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.121854908082268</v>
+      </c>
+      <c r="T55">
+        <v>1.124695959933529</v>
+      </c>
+      <c r="U55">
+        <v>0.0509</v>
+      </c>
+      <c r="V55">
+        <v>0.125</v>
+      </c>
+      <c r="W55">
+        <v>0.0445375</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>4.652666574395442</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.08088180002918982</v>
+      </c>
+      <c r="C56">
+        <v>3475.308618215662</v>
+      </c>
+      <c r="D56">
+        <v>6819.518618215662</v>
+      </c>
+      <c r="E56">
+        <v>1371.71</v>
+      </c>
+      <c r="F56">
+        <v>3629.61</v>
+      </c>
+      <c r="G56">
+        <v>285.4</v>
+      </c>
+      <c r="H56">
+        <v>4463.6</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K56">
+        <v>213.8</v>
+      </c>
+      <c r="L56">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M56">
+        <v>184.747149</v>
+      </c>
+      <c r="N56">
+        <v>658.9018305918366</v>
+      </c>
+      <c r="O56">
+        <v>82.36272882397958</v>
+      </c>
+      <c r="P56">
+        <v>576.5391017678571</v>
+      </c>
+      <c r="Q56">
+        <v>790.3391017678571</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1235468478895431</v>
+      </c>
+      <c r="T56">
+        <v>1.147607524218305</v>
+      </c>
+      <c r="U56">
+        <v>0.0509</v>
+      </c>
+      <c r="V56">
+        <v>0.125</v>
+      </c>
+      <c r="W56">
+        <v>0.0445375</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>4.566506082277008</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.08213816825971368</v>
+      </c>
+      <c r="C57">
+        <v>3323.787374065041</v>
+      </c>
+      <c r="D57">
+        <v>6735.212374065041</v>
+      </c>
+      <c r="E57">
+        <v>1438.925</v>
+      </c>
+      <c r="F57">
+        <v>3696.825</v>
+      </c>
+      <c r="G57">
+        <v>285.4</v>
+      </c>
+      <c r="H57">
+        <v>4463.6</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K57">
+        <v>213.8</v>
+      </c>
+      <c r="L57">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M57">
+        <v>197.7801375</v>
+      </c>
+      <c r="N57">
+        <v>645.8688420918367</v>
+      </c>
+      <c r="O57">
+        <v>80.73360526147958</v>
+      </c>
+      <c r="P57">
+        <v>565.135236830357</v>
+      </c>
+      <c r="Q57">
+        <v>778.9352368303571</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.125313985021586</v>
+      </c>
+      <c r="T57">
+        <v>1.171537380249071</v>
+      </c>
+      <c r="U57">
+        <v>0.0535</v>
+      </c>
+      <c r="V57">
+        <v>0.125</v>
+      </c>
+      <c r="W57">
+        <v>0.0468125</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>4.265590014527302</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.08216603649023757</v>
+      </c>
+      <c r="C58">
+        <v>3254.725953240923</v>
+      </c>
+      <c r="D58">
+        <v>6733.365953240924</v>
+      </c>
+      <c r="E58">
+        <v>1506.14</v>
+      </c>
+      <c r="F58">
+        <v>3764.04</v>
+      </c>
+      <c r="G58">
+        <v>285.4</v>
+      </c>
+      <c r="H58">
+        <v>4463.6</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K58">
+        <v>213.8</v>
+      </c>
+      <c r="L58">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M58">
+        <v>201.37614</v>
+      </c>
+      <c r="N58">
+        <v>642.2728395918366</v>
+      </c>
+      <c r="O58">
+        <v>80.28410494897958</v>
+      </c>
+      <c r="P58">
+        <v>561.988734642857</v>
+      </c>
+      <c r="Q58">
+        <v>775.788734642857</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1271614465687217</v>
+      </c>
+      <c r="T58">
+        <v>1.196554957008508</v>
+      </c>
+      <c r="U58">
+        <v>0.0535</v>
+      </c>
+      <c r="V58">
+        <v>0.125</v>
+      </c>
+      <c r="W58">
+        <v>0.0468125</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>4.189418764267884</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.08219390472076143</v>
+      </c>
+      <c r="C59">
+        <v>3185.665544511245</v>
+      </c>
+      <c r="D59">
+        <v>6731.520544511246</v>
+      </c>
+      <c r="E59">
+        <v>1573.355</v>
+      </c>
+      <c r="F59">
+        <v>3831.255000000001</v>
+      </c>
+      <c r="G59">
+        <v>285.4</v>
+      </c>
+      <c r="H59">
+        <v>4463.6</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K59">
+        <v>213.8</v>
+      </c>
+      <c r="L59">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M59">
+        <v>204.9721425</v>
+      </c>
+      <c r="N59">
+        <v>638.6768370918367</v>
+      </c>
+      <c r="O59">
+        <v>79.83460463647958</v>
+      </c>
+      <c r="P59">
+        <v>558.8422324553571</v>
+      </c>
+      <c r="Q59">
+        <v>772.6422324553571</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1290948365599103</v>
+      </c>
+      <c r="T59">
+        <v>1.222736141989314</v>
+      </c>
+      <c r="U59">
+        <v>0.0535</v>
+      </c>
+      <c r="V59">
+        <v>0.125</v>
+      </c>
+      <c r="W59">
+        <v>0.0468125</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>4.115920189456167</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.0822217729512853</v>
+      </c>
+      <c r="C60">
+        <v>3116.606147044079</v>
+      </c>
+      <c r="D60">
+        <v>6729.676147044079</v>
+      </c>
+      <c r="E60">
+        <v>1640.57</v>
+      </c>
+      <c r="F60">
+        <v>3898.47</v>
+      </c>
+      <c r="G60">
+        <v>285.4</v>
+      </c>
+      <c r="H60">
+        <v>4463.6</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K60">
+        <v>213.8</v>
+      </c>
+      <c r="L60">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M60">
+        <v>208.568145</v>
+      </c>
+      <c r="N60">
+        <v>635.0808345918367</v>
+      </c>
+      <c r="O60">
+        <v>79.38510432397959</v>
+      </c>
+      <c r="P60">
+        <v>555.6957302678571</v>
+      </c>
+      <c r="Q60">
+        <v>769.4957302678572</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1311202927411555</v>
+      </c>
+      <c r="T60">
+        <v>1.250164050064444</v>
+      </c>
+      <c r="U60">
+        <v>0.0535</v>
+      </c>
+      <c r="V60">
+        <v>0.125</v>
+      </c>
+      <c r="W60">
+        <v>0.0468125</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>4.044956048258648</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.08364351618180918</v>
+      </c>
+      <c r="C61">
+        <v>2956.618779966805</v>
+      </c>
+      <c r="D61">
+        <v>6636.903779966805</v>
+      </c>
+      <c r="E61">
+        <v>1707.785</v>
+      </c>
+      <c r="F61">
+        <v>3965.685</v>
+      </c>
+      <c r="G61">
+        <v>285.4</v>
+      </c>
+      <c r="H61">
+        <v>4463.6</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K61">
+        <v>213.8</v>
+      </c>
+      <c r="L61">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M61">
+        <v>222.871497</v>
+      </c>
+      <c r="N61">
+        <v>620.7774825918367</v>
+      </c>
+      <c r="O61">
+        <v>77.59718532397959</v>
+      </c>
+      <c r="P61">
+        <v>543.1802972678571</v>
+      </c>
+      <c r="Q61">
+        <v>756.9802972678572</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1332445516629492</v>
+      </c>
+      <c r="T61">
+        <v>1.278929904874947</v>
+      </c>
+      <c r="U61">
+        <v>0.0562</v>
+      </c>
+      <c r="V61">
+        <v>0.125</v>
+      </c>
+      <c r="W61">
+        <v>0.049175</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>3.785360581985218</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.08369500941233304</v>
+      </c>
+      <c r="C62">
+        <v>2886.091689590272</v>
+      </c>
+      <c r="D62">
+        <v>6633.591689590272</v>
+      </c>
+      <c r="E62">
+        <v>1775</v>
+      </c>
+      <c r="F62">
+        <v>4032.9</v>
+      </c>
+      <c r="G62">
+        <v>285.4</v>
+      </c>
+      <c r="H62">
+        <v>4463.6</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K62">
+        <v>213.8</v>
+      </c>
+      <c r="L62">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M62">
+        <v>226.64898</v>
+      </c>
+      <c r="N62">
+        <v>616.9999995918367</v>
+      </c>
+      <c r="O62">
+        <v>77.12499994897959</v>
+      </c>
+      <c r="P62">
+        <v>539.8749996428571</v>
+      </c>
+      <c r="Q62">
+        <v>753.6749996428571</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1354750235308326</v>
+      </c>
+      <c r="T62">
+        <v>1.309134052425975</v>
+      </c>
+      <c r="U62">
+        <v>0.0562</v>
+      </c>
+      <c r="V62">
+        <v>0.125</v>
+      </c>
+      <c r="W62">
+        <v>0.049175</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>3.722271238952132</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.08374650264285693</v>
+      </c>
+      <c r="C63">
+        <v>2815.567903305916</v>
+      </c>
+      <c r="D63">
+        <v>6630.282903305916</v>
+      </c>
+      <c r="E63">
+        <v>1842.215</v>
+      </c>
+      <c r="F63">
+        <v>4100.115</v>
+      </c>
+      <c r="G63">
+        <v>285.4</v>
+      </c>
+      <c r="H63">
+        <v>4463.6</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K63">
+        <v>213.8</v>
+      </c>
+      <c r="L63">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M63">
+        <v>230.426463</v>
+      </c>
+      <c r="N63">
+        <v>613.2225165918367</v>
+      </c>
+      <c r="O63">
+        <v>76.65281457397958</v>
+      </c>
+      <c r="P63">
+        <v>536.569702017857</v>
+      </c>
+      <c r="Q63">
+        <v>750.369702017857</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.137819878571428</v>
+      </c>
+      <c r="T63">
+        <v>1.340887130620645</v>
+      </c>
+      <c r="U63">
+        <v>0.0562</v>
+      </c>
+      <c r="V63">
+        <v>0.125</v>
+      </c>
+      <c r="W63">
+        <v>0.049175</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>3.661250398969309</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.0837979958733808</v>
+      </c>
+      <c r="C64">
+        <v>2745.047416172035</v>
+      </c>
+      <c r="D64">
+        <v>6626.977416172035</v>
+      </c>
+      <c r="E64">
+        <v>1909.43</v>
+      </c>
+      <c r="F64">
+        <v>4167.33</v>
+      </c>
+      <c r="G64">
+        <v>285.4</v>
+      </c>
+      <c r="H64">
+        <v>4463.6</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K64">
+        <v>213.8</v>
+      </c>
+      <c r="L64">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M64">
+        <v>234.203946</v>
+      </c>
+      <c r="N64">
+        <v>609.4450335918367</v>
+      </c>
+      <c r="O64">
+        <v>76.18062919897959</v>
+      </c>
+      <c r="P64">
+        <v>533.2644043928572</v>
+      </c>
+      <c r="Q64">
+        <v>747.0644043928571</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1402881470352126</v>
+      </c>
+      <c r="T64">
+        <v>1.37431142345714</v>
+      </c>
+      <c r="U64">
+        <v>0.0562</v>
+      </c>
+      <c r="V64">
+        <v>0.125</v>
+      </c>
+      <c r="W64">
+        <v>0.049175</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>3.602197973179481</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.08384948910390466</v>
+      </c>
+      <c r="C65">
+        <v>2674.530223256775</v>
+      </c>
+      <c r="D65">
+        <v>6623.675223256775</v>
+      </c>
+      <c r="E65">
+        <v>1976.645</v>
+      </c>
+      <c r="F65">
+        <v>4234.545</v>
+      </c>
+      <c r="G65">
+        <v>285.4</v>
+      </c>
+      <c r="H65">
+        <v>4463.6</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K65">
+        <v>213.8</v>
+      </c>
+      <c r="L65">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M65">
+        <v>237.981429</v>
+      </c>
+      <c r="N65">
+        <v>605.6675505918367</v>
+      </c>
+      <c r="O65">
+        <v>75.70844382397959</v>
+      </c>
+      <c r="P65">
+        <v>529.9591067678572</v>
+      </c>
+      <c r="Q65">
+        <v>743.7591067678572</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1428898354159586</v>
+      </c>
+      <c r="T65">
+        <v>1.409542434825337</v>
+      </c>
+      <c r="U65">
+        <v>0.0562</v>
+      </c>
+      <c r="V65">
+        <v>0.125</v>
+      </c>
+      <c r="W65">
+        <v>0.049175</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>3.545020227573458</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.08653298233442855</v>
+      </c>
+      <c r="C66">
+        <v>2439.665608341688</v>
+      </c>
+      <c r="D66">
+        <v>6456.025608341689</v>
+      </c>
+      <c r="E66">
+        <v>2043.86</v>
+      </c>
+      <c r="F66">
+        <v>4301.76</v>
+      </c>
+      <c r="G66">
+        <v>285.4</v>
+      </c>
+      <c r="H66">
+        <v>4463.6</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K66">
+        <v>213.8</v>
+      </c>
+      <c r="L66">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M66">
+        <v>261.977184</v>
+      </c>
+      <c r="N66">
+        <v>581.6717955918366</v>
+      </c>
+      <c r="O66">
+        <v>72.70897444897957</v>
+      </c>
+      <c r="P66">
+        <v>508.962821142857</v>
+      </c>
+      <c r="Q66">
+        <v>722.7628211428571</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1456360620400793</v>
+      </c>
+      <c r="T66">
+        <v>1.446730724602879</v>
+      </c>
+      <c r="U66">
+        <v>0.0609</v>
+      </c>
+      <c r="V66">
+        <v>0.125</v>
+      </c>
+      <c r="W66">
+        <v>0.0532875</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>3.22031471103925</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.08662560056495243</v>
+      </c>
+      <c r="C67">
+        <v>2366.815717234914</v>
+      </c>
+      <c r="D67">
+        <v>6450.390717234915</v>
+      </c>
+      <c r="E67">
+        <v>2111.075</v>
+      </c>
+      <c r="F67">
+        <v>4368.975</v>
+      </c>
+      <c r="G67">
+        <v>285.4</v>
+      </c>
+      <c r="H67">
+        <v>4463.6</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K67">
+        <v>213.8</v>
+      </c>
+      <c r="L67">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M67">
+        <v>266.0705775</v>
+      </c>
+      <c r="N67">
+        <v>577.5784020918367</v>
+      </c>
+      <c r="O67">
+        <v>72.19730026147958</v>
+      </c>
+      <c r="P67">
+        <v>505.3811018303571</v>
+      </c>
+      <c r="Q67">
+        <v>719.1811018303571</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1485392158998641</v>
+      </c>
+      <c r="T67">
+        <v>1.486044059510566</v>
+      </c>
+      <c r="U67">
+        <v>0.0609</v>
+      </c>
+      <c r="V67">
+        <v>0.125</v>
+      </c>
+      <c r="W67">
+        <v>0.0532875</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>3.170771407792493</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.0867182187954763</v>
+      </c>
+      <c r="C68">
+        <v>2293.975653941839</v>
+      </c>
+      <c r="D68">
+        <v>6444.765653941839</v>
+      </c>
+      <c r="E68">
+        <v>2178.29</v>
+      </c>
+      <c r="F68">
+        <v>4436.190000000001</v>
+      </c>
+      <c r="G68">
+        <v>285.4</v>
+      </c>
+      <c r="H68">
+        <v>4463.6</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K68">
+        <v>213.8</v>
+      </c>
+      <c r="L68">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M68">
+        <v>270.1639710000001</v>
+      </c>
+      <c r="N68">
+        <v>573.4850085918366</v>
+      </c>
+      <c r="O68">
+        <v>71.68562607397958</v>
+      </c>
+      <c r="P68">
+        <v>501.7993825178571</v>
+      </c>
+      <c r="Q68">
+        <v>715.5993825178571</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.1516131435161068</v>
+      </c>
+      <c r="T68">
+        <v>1.52766994353047</v>
+      </c>
+      <c r="U68">
+        <v>0.0609</v>
+      </c>
+      <c r="V68">
+        <v>0.125</v>
+      </c>
+      <c r="W68">
+        <v>0.0532875</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>3.122729416765333</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.08681083702600018</v>
+      </c>
+      <c r="C69">
+        <v>2221.145392773828</v>
+      </c>
+      <c r="D69">
+        <v>6439.150392773829</v>
+      </c>
+      <c r="E69">
+        <v>2245.505000000001</v>
+      </c>
+      <c r="F69">
+        <v>4503.405000000001</v>
+      </c>
+      <c r="G69">
+        <v>285.4</v>
+      </c>
+      <c r="H69">
+        <v>4463.6</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K69">
+        <v>213.8</v>
+      </c>
+      <c r="L69">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M69">
+        <v>274.2573645000001</v>
+      </c>
+      <c r="N69">
+        <v>569.3916150918367</v>
+      </c>
+      <c r="O69">
+        <v>71.17395188647959</v>
+      </c>
+      <c r="P69">
+        <v>498.2176632053571</v>
+      </c>
+      <c r="Q69">
+        <v>712.0176632053572</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.1548733697757581</v>
+      </c>
+      <c r="T69">
+        <v>1.571818608400065</v>
+      </c>
+      <c r="U69">
+        <v>0.0609</v>
+      </c>
+      <c r="V69">
+        <v>0.125</v>
+      </c>
+      <c r="W69">
+        <v>0.0532875</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>3.076121515022568</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.08690345525652406</v>
+      </c>
+      <c r="C70">
+        <v>2148.3249081317</v>
+      </c>
+      <c r="D70">
+        <v>6433.5449081317</v>
+      </c>
+      <c r="E70">
+        <v>2312.72</v>
+      </c>
+      <c r="F70">
+        <v>4570.62</v>
+      </c>
+      <c r="G70">
+        <v>285.4</v>
+      </c>
+      <c r="H70">
+        <v>4463.6</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K70">
+        <v>213.8</v>
+      </c>
+      <c r="L70">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M70">
+        <v>278.350758</v>
+      </c>
+      <c r="N70">
+        <v>565.2982215918366</v>
+      </c>
+      <c r="O70">
+        <v>70.66227769897958</v>
+      </c>
+      <c r="P70">
+        <v>494.6359438928571</v>
+      </c>
+      <c r="Q70">
+        <v>708.435943892857</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.1583373601766377</v>
+      </c>
+      <c r="T70">
+        <v>1.61872656482401</v>
+      </c>
+      <c r="U70">
+        <v>0.0609</v>
+      </c>
+      <c r="V70">
+        <v>0.125</v>
+      </c>
+      <c r="W70">
+        <v>0.0532875</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>3.030884433919295</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.09261094848704793</v>
+      </c>
+      <c r="C71">
+        <v>1753.551061997553</v>
+      </c>
+      <c r="D71">
+        <v>6105.986061997553</v>
+      </c>
+      <c r="E71">
+        <v>2379.935</v>
+      </c>
+      <c r="F71">
+        <v>4637.835</v>
+      </c>
+      <c r="G71">
+        <v>285.4</v>
+      </c>
+      <c r="H71">
+        <v>4463.6</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K71">
+        <v>213.8</v>
+      </c>
+      <c r="L71">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M71">
+        <v>325.576017</v>
+      </c>
+      <c r="N71">
+        <v>518.0729625918367</v>
+      </c>
+      <c r="O71">
+        <v>64.75912032397959</v>
+      </c>
+      <c r="P71">
+        <v>453.3138422678571</v>
+      </c>
+      <c r="Q71">
+        <v>667.1138422678571</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.1620248338291869</v>
+      </c>
+      <c r="T71">
+        <v>1.668660841017241</v>
+      </c>
+      <c r="U71">
+        <v>0.0702</v>
+      </c>
+      <c r="V71">
+        <v>0.125</v>
+      </c>
+      <c r="W71">
+        <v>0.061425</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>2.591250385595314</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.09278494171757179</v>
+      </c>
+      <c r="C72">
+        <v>1676.873511820119</v>
+      </c>
+      <c r="D72">
+        <v>6096.52351182012</v>
+      </c>
+      <c r="E72">
+        <v>2447.15</v>
+      </c>
+      <c r="F72">
+        <v>4705.05</v>
+      </c>
+      <c r="G72">
+        <v>285.4</v>
+      </c>
+      <c r="H72">
+        <v>4463.6</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K72">
+        <v>213.8</v>
+      </c>
+      <c r="L72">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M72">
+        <v>330.29451</v>
+      </c>
+      <c r="N72">
+        <v>513.3544695918367</v>
+      </c>
+      <c r="O72">
+        <v>64.16930869897959</v>
+      </c>
+      <c r="P72">
+        <v>449.1851608928571</v>
+      </c>
+      <c r="Q72">
+        <v>662.9851608928572</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.1659581390585727</v>
+      </c>
+      <c r="T72">
+        <v>1.721924068956688</v>
+      </c>
+      <c r="U72">
+        <v>0.0702</v>
+      </c>
+      <c r="V72">
+        <v>0.125</v>
+      </c>
+      <c r="W72">
+        <v>0.061425</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>2.554232522943953</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.09295893494809568</v>
+      </c>
+      <c r="C73">
+        <v>1600.225244811112</v>
+      </c>
+      <c r="D73">
+        <v>6087.090244811112</v>
+      </c>
+      <c r="E73">
+        <v>2514.364999999999</v>
+      </c>
+      <c r="F73">
+        <v>4772.264999999999</v>
+      </c>
+      <c r="G73">
+        <v>285.4</v>
+      </c>
+      <c r="H73">
+        <v>4463.6</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K73">
+        <v>213.8</v>
+      </c>
+      <c r="L73">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M73">
+        <v>335.013003</v>
+      </c>
+      <c r="N73">
+        <v>508.6359765918367</v>
+      </c>
+      <c r="O73">
+        <v>63.57949707397959</v>
+      </c>
+      <c r="P73">
+        <v>445.0564795178571</v>
+      </c>
+      <c r="Q73">
+        <v>658.8564795178571</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.1701627067175713</v>
+      </c>
+      <c r="T73">
+        <v>1.778860622960924</v>
+      </c>
+      <c r="U73">
+        <v>0.0702</v>
+      </c>
+      <c r="V73">
+        <v>0.125</v>
+      </c>
+      <c r="W73">
+        <v>0.061425</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>2.518257416986996</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.09609392817861954</v>
+      </c>
+      <c r="C74">
+        <v>1367.908490122243</v>
+      </c>
+      <c r="D74">
+        <v>5921.988490122243</v>
+      </c>
+      <c r="E74">
+        <v>2581.579999999999</v>
+      </c>
+      <c r="F74">
+        <v>4839.48</v>
+      </c>
+      <c r="G74">
+        <v>285.4</v>
+      </c>
+      <c r="H74">
+        <v>4463.6</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K74">
+        <v>213.8</v>
+      </c>
+      <c r="L74">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M74">
+        <v>362.477052</v>
+      </c>
+      <c r="N74">
+        <v>481.1719275918367</v>
+      </c>
+      <c r="O74">
+        <v>60.14649094897959</v>
+      </c>
+      <c r="P74">
+        <v>421.0254366428571</v>
+      </c>
+      <c r="Q74">
+        <v>634.8254366428571</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.1746676006379269</v>
+      </c>
+      <c r="T74">
+        <v>1.839864073679748</v>
+      </c>
+      <c r="U74">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V74">
+        <v>0.125</v>
+      </c>
+      <c r="W74">
+        <v>0.0655375</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>2.327454869037714</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.09630904640914342</v>
+      </c>
+      <c r="C75">
+        <v>1289.692226321562</v>
+      </c>
+      <c r="D75">
+        <v>5910.987226321562</v>
+      </c>
+      <c r="E75">
+        <v>2648.795</v>
+      </c>
+      <c r="F75">
+        <v>4906.695</v>
+      </c>
+      <c r="G75">
+        <v>285.4</v>
+      </c>
+      <c r="H75">
+        <v>4463.6</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K75">
+        <v>213.8</v>
+      </c>
+      <c r="L75">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M75">
+        <v>367.5114555</v>
+      </c>
+      <c r="N75">
+        <v>476.1375240918367</v>
+      </c>
+      <c r="O75">
+        <v>59.51719051147959</v>
+      </c>
+      <c r="P75">
+        <v>416.6203335803571</v>
+      </c>
+      <c r="Q75">
+        <v>630.4203335803571</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.1795061904042349</v>
+      </c>
+      <c r="T75">
+        <v>1.905386298525893</v>
+      </c>
+      <c r="U75">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V75">
+        <v>0.125</v>
+      </c>
+      <c r="W75">
+        <v>0.0655375</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>2.295571925626239</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.09652416463966729</v>
+      </c>
+      <c r="C76">
+        <v>1211.516760772769</v>
+      </c>
+      <c r="D76">
+        <v>5900.026760772769</v>
+      </c>
+      <c r="E76">
+        <v>2716.01</v>
+      </c>
+      <c r="F76">
+        <v>4973.91</v>
+      </c>
+      <c r="G76">
+        <v>285.4</v>
+      </c>
+      <c r="H76">
+        <v>4463.6</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K76">
+        <v>213.8</v>
+      </c>
+      <c r="L76">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M76">
+        <v>372.545859</v>
+      </c>
+      <c r="N76">
+        <v>471.1031205918367</v>
+      </c>
+      <c r="O76">
+        <v>58.88789007397959</v>
+      </c>
+      <c r="P76">
+        <v>412.2152305178572</v>
+      </c>
+      <c r="Q76">
+        <v>626.0152305178572</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.1847169793833357</v>
+      </c>
+      <c r="T76">
+        <v>1.975948694514049</v>
+      </c>
+      <c r="U76">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V76">
+        <v>0.125</v>
+      </c>
+      <c r="W76">
+        <v>0.0655375</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>2.264550683388046</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.09673928287019117</v>
+      </c>
+      <c r="C77">
+        <v>1133.38186694507</v>
+      </c>
+      <c r="D77">
+        <v>5889.106866945071</v>
+      </c>
+      <c r="E77">
+        <v>2783.225</v>
+      </c>
+      <c r="F77">
+        <v>5041.125</v>
+      </c>
+      <c r="G77">
+        <v>285.4</v>
+      </c>
+      <c r="H77">
+        <v>4463.6</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K77">
+        <v>213.8</v>
+      </c>
+      <c r="L77">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M77">
+        <v>377.5802624999999</v>
+      </c>
+      <c r="N77">
+        <v>466.0687170918367</v>
+      </c>
+      <c r="O77">
+        <v>58.25858963647959</v>
+      </c>
+      <c r="P77">
+        <v>407.8101274553571</v>
+      </c>
+      <c r="Q77">
+        <v>621.6101274553571</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.1903446314807647</v>
+      </c>
+      <c r="T77">
+        <v>2.052156082181258</v>
+      </c>
+      <c r="U77">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V77">
+        <v>0.125</v>
+      </c>
+      <c r="W77">
+        <v>0.0655375</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>2.234356674276206</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.09695440110071504</v>
+      </c>
+      <c r="C78">
+        <v>1055.287319981647</v>
+      </c>
+      <c r="D78">
+        <v>5878.227319981647</v>
+      </c>
+      <c r="E78">
+        <v>2850.44</v>
+      </c>
+      <c r="F78">
+        <v>5108.34</v>
+      </c>
+      <c r="G78">
+        <v>285.4</v>
+      </c>
+      <c r="H78">
+        <v>4463.6</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K78">
+        <v>213.8</v>
+      </c>
+      <c r="L78">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M78">
+        <v>382.614666</v>
+      </c>
+      <c r="N78">
+        <v>461.0343135918367</v>
+      </c>
+      <c r="O78">
+        <v>57.62928919897958</v>
+      </c>
+      <c r="P78">
+        <v>403.4050243928571</v>
+      </c>
+      <c r="Q78">
+        <v>617.2050243928571</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.1964412545863127</v>
+      </c>
+      <c r="T78">
+        <v>2.1347140854874</v>
+      </c>
+      <c r="U78">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V78">
+        <v>0.125</v>
+      </c>
+      <c r="W78">
+        <v>0.0655375</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>2.204957244351519</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.09716951933123891</v>
+      </c>
+      <c r="C79">
+        <v>977.2328966842224</v>
+      </c>
+      <c r="D79">
+        <v>5867.387896684223</v>
+      </c>
+      <c r="E79">
+        <v>2917.655</v>
+      </c>
+      <c r="F79">
+        <v>5175.555</v>
+      </c>
+      <c r="G79">
+        <v>285.4</v>
+      </c>
+      <c r="H79">
+        <v>4463.6</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K79">
+        <v>213.8</v>
+      </c>
+      <c r="L79">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M79">
+        <v>387.6490695</v>
+      </c>
+      <c r="N79">
+        <v>455.9999100918367</v>
+      </c>
+      <c r="O79">
+        <v>56.99998876147959</v>
+      </c>
+      <c r="P79">
+        <v>398.9999213303571</v>
+      </c>
+      <c r="Q79">
+        <v>612.7999213303572</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.2030680188314735</v>
+      </c>
+      <c r="T79">
+        <v>2.224451045602773</v>
+      </c>
+      <c r="U79">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V79">
+        <v>0.125</v>
+      </c>
+      <c r="W79">
+        <v>0.0655375</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>2.176321435983317</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.09738463756176277</v>
+      </c>
+      <c r="C80">
+        <v>899.2183754977905</v>
+      </c>
+      <c r="D80">
+        <v>5856.588375497791</v>
+      </c>
+      <c r="E80">
+        <v>2984.87</v>
+      </c>
+      <c r="F80">
+        <v>5242.77</v>
+      </c>
+      <c r="G80">
+        <v>285.4</v>
+      </c>
+      <c r="H80">
+        <v>4463.6</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K80">
+        <v>213.8</v>
+      </c>
+      <c r="L80">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M80">
+        <v>392.683473</v>
+      </c>
+      <c r="N80">
+        <v>450.9655065918367</v>
+      </c>
+      <c r="O80">
+        <v>56.37068832397959</v>
+      </c>
+      <c r="P80">
+        <v>394.5948182678571</v>
+      </c>
+      <c r="Q80">
+        <v>608.3948182678571</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.2102972161898309</v>
+      </c>
+      <c r="T80">
+        <v>2.322345911183179</v>
+      </c>
+      <c r="U80">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V80">
+        <v>0.125</v>
+      </c>
+      <c r="W80">
+        <v>0.0655375</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>2.148419879111736</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.09759975579228666</v>
+      </c>
+      <c r="C81">
+        <v>821.24353649553</v>
+      </c>
+      <c r="D81">
+        <v>5845.828536495531</v>
+      </c>
+      <c r="E81">
+        <v>3052.085</v>
+      </c>
+      <c r="F81">
+        <v>5309.985000000001</v>
+      </c>
+      <c r="G81">
+        <v>285.4</v>
+      </c>
+      <c r="H81">
+        <v>4463.6</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K81">
+        <v>213.8</v>
+      </c>
+      <c r="L81">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M81">
+        <v>397.7178765</v>
+      </c>
+      <c r="N81">
+        <v>445.9311030918367</v>
+      </c>
+      <c r="O81">
+        <v>55.74138788647959</v>
+      </c>
+      <c r="P81">
+        <v>390.1897152053571</v>
+      </c>
+      <c r="Q81">
+        <v>603.9897152053571</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.2182149085346984</v>
+      </c>
+      <c r="T81">
+        <v>2.429564097295053</v>
+      </c>
+      <c r="U81">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V81">
+        <v>0.125</v>
+      </c>
+      <c r="W81">
+        <v>0.0655375</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>2.12122469076855</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.09781487402281056</v>
+      </c>
+      <c r="C82">
+        <v>743.3081613638715</v>
+      </c>
+      <c r="D82">
+        <v>5835.108161363873</v>
+      </c>
+      <c r="E82">
+        <v>3119.300000000001</v>
+      </c>
+      <c r="F82">
+        <v>5377.200000000001</v>
+      </c>
+      <c r="G82">
+        <v>285.4</v>
+      </c>
+      <c r="H82">
+        <v>4463.6</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K82">
+        <v>213.8</v>
+      </c>
+      <c r="L82">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M82">
+        <v>402.75228</v>
+      </c>
+      <c r="N82">
+        <v>440.8966995918366</v>
+      </c>
+      <c r="O82">
+        <v>55.11208744897958</v>
+      </c>
+      <c r="P82">
+        <v>385.784612142857</v>
+      </c>
+      <c r="Q82">
+        <v>599.5846121428571</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.2269243701140528</v>
+      </c>
+      <c r="T82">
+        <v>2.547504102018114</v>
+      </c>
+      <c r="U82">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V82">
+        <v>0.125</v>
+      </c>
+      <c r="W82">
+        <v>0.0655375</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>2.094709382133942</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.09802999225333442</v>
+      </c>
+      <c r="C83">
+        <v>665.4120333877308</v>
+      </c>
+      <c r="D83">
+        <v>5824.427033387731</v>
+      </c>
+      <c r="E83">
+        <v>3186.515</v>
+      </c>
+      <c r="F83">
+        <v>5444.415</v>
+      </c>
+      <c r="G83">
+        <v>285.4</v>
+      </c>
+      <c r="H83">
+        <v>4463.6</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K83">
+        <v>213.8</v>
+      </c>
+      <c r="L83">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M83">
+        <v>407.7866835</v>
+      </c>
+      <c r="N83">
+        <v>435.8622960918367</v>
+      </c>
+      <c r="O83">
+        <v>54.48278701147959</v>
+      </c>
+      <c r="P83">
+        <v>381.3795090803571</v>
+      </c>
+      <c r="Q83">
+        <v>595.1795090803571</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.2365506171228128</v>
+      </c>
+      <c r="T83">
+        <v>2.677858844080444</v>
+      </c>
+      <c r="U83">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V83">
+        <v>0.125</v>
+      </c>
+      <c r="W83">
+        <v>0.0655375</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>2.068848772477968</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.09824511048385828</v>
+      </c>
+      <c r="C84">
+        <v>587.5549374359052</v>
+      </c>
+      <c r="D84">
+        <v>5813.784937435906</v>
+      </c>
+      <c r="E84">
+        <v>3253.73</v>
+      </c>
+      <c r="F84">
+        <v>5511.63</v>
+      </c>
+      <c r="G84">
+        <v>285.4</v>
+      </c>
+      <c r="H84">
+        <v>4463.6</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K84">
+        <v>213.8</v>
+      </c>
+      <c r="L84">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M84">
+        <v>412.821087</v>
+      </c>
+      <c r="N84">
+        <v>430.8278925918367</v>
+      </c>
+      <c r="O84">
+        <v>53.85348657397959</v>
+      </c>
+      <c r="P84">
+        <v>376.9744060178571</v>
+      </c>
+      <c r="Q84">
+        <v>590.7744060178571</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.2472464471325461</v>
+      </c>
+      <c r="T84">
+        <v>2.822697446371922</v>
+      </c>
+      <c r="U84">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V84">
+        <v>0.125</v>
+      </c>
+      <c r="W84">
+        <v>0.0655375</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>2.043618909398969</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.09846022871438216</v>
+      </c>
+      <c r="C85">
+        <v>509.7366599466332</v>
+      </c>
+      <c r="D85">
+        <v>5803.181659946634</v>
+      </c>
+      <c r="E85">
+        <v>3320.945</v>
+      </c>
+      <c r="F85">
+        <v>5578.845</v>
+      </c>
+      <c r="G85">
+        <v>285.4</v>
+      </c>
+      <c r="H85">
+        <v>4463.6</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K85">
+        <v>213.8</v>
+      </c>
+      <c r="L85">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M85">
+        <v>417.8554905</v>
+      </c>
+      <c r="N85">
+        <v>425.7934890918367</v>
+      </c>
+      <c r="O85">
+        <v>53.22418613647959</v>
+      </c>
+      <c r="P85">
+        <v>372.5693029553571</v>
+      </c>
+      <c r="Q85">
+        <v>586.3693029553572</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.259200610084601</v>
+      </c>
+      <c r="T85">
+        <v>2.984575884227104</v>
+      </c>
+      <c r="U85">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V85">
+        <v>0.125</v>
+      </c>
+      <c r="W85">
+        <v>0.0655375</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>2.018996994827897</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.110655846944906</v>
+      </c>
+      <c r="C86">
+        <v>-101.282031607413</v>
+      </c>
+      <c r="D86">
+        <v>5259.377968392587</v>
+      </c>
+      <c r="E86">
+        <v>3388.159999999999</v>
+      </c>
+      <c r="F86">
+        <v>5646.059999999999</v>
+      </c>
+      <c r="G86">
+        <v>285.4</v>
+      </c>
+      <c r="H86">
+        <v>4463.6</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K86">
+        <v>213.8</v>
+      </c>
+      <c r="L86">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M86">
+        <v>514.920672</v>
+      </c>
+      <c r="N86">
+        <v>328.7283075918367</v>
+      </c>
+      <c r="O86">
+        <v>41.09103844897959</v>
+      </c>
+      <c r="P86">
+        <v>287.6372691428571</v>
+      </c>
+      <c r="Q86">
+        <v>501.4372691428571</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.2726490434056627</v>
+      </c>
+      <c r="T86">
+        <v>3.166689126814182</v>
+      </c>
+      <c r="U86">
+        <v>0.0912</v>
+      </c>
+      <c r="V86">
+        <v>0.125</v>
+      </c>
+      <c r="W86">
+        <v>0.07980000000000001</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>1.638405730177865</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.1110135901754299</v>
+      </c>
+      <c r="C87">
+        <v>-182.9143941665479</v>
+      </c>
+      <c r="D87">
+        <v>5244.960605833452</v>
+      </c>
+      <c r="E87">
+        <v>3455.375</v>
+      </c>
+      <c r="F87">
+        <v>5713.275</v>
+      </c>
+      <c r="G87">
+        <v>285.4</v>
+      </c>
+      <c r="H87">
+        <v>4463.6</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K87">
+        <v>213.8</v>
+      </c>
+      <c r="L87">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M87">
+        <v>521.0506799999999</v>
+      </c>
+      <c r="N87">
+        <v>322.5982995918367</v>
+      </c>
+      <c r="O87">
+        <v>40.32478744897959</v>
+      </c>
+      <c r="P87">
+        <v>282.2735121428572</v>
+      </c>
+      <c r="Q87">
+        <v>496.0735121428572</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.2878906011695327</v>
+      </c>
+      <c r="T87">
+        <v>3.373084135079539</v>
+      </c>
+      <c r="U87">
+        <v>0.0912</v>
+      </c>
+      <c r="V87">
+        <v>0.125</v>
+      </c>
+      <c r="W87">
+        <v>0.07980000000000001</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>1.61913036864636</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.1113713334059538</v>
+      </c>
+      <c r="C88">
+        <v>-264.4679291147813</v>
+      </c>
+      <c r="D88">
+        <v>5230.622070885219</v>
+      </c>
+      <c r="E88">
+        <v>3522.59</v>
+      </c>
+      <c r="F88">
+        <v>5780.49</v>
+      </c>
+      <c r="G88">
+        <v>285.4</v>
+      </c>
+      <c r="H88">
+        <v>4463.6</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K88">
+        <v>213.8</v>
+      </c>
+      <c r="L88">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M88">
+        <v>527.180688</v>
+      </c>
+      <c r="N88">
+        <v>316.4682915918366</v>
+      </c>
+      <c r="O88">
+        <v>39.55853644897958</v>
+      </c>
+      <c r="P88">
+        <v>276.9097551428571</v>
+      </c>
+      <c r="Q88">
+        <v>490.7097551428571</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.3053095243282413</v>
+      </c>
+      <c r="T88">
+        <v>3.608964144525661</v>
+      </c>
+      <c r="U88">
+        <v>0.0912</v>
+      </c>
+      <c r="V88">
+        <v>0.125</v>
+      </c>
+      <c r="W88">
+        <v>0.07980000000000001</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>1.600303271336519</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.1117290766364777</v>
+      </c>
+      <c r="C89">
+        <v>-345.9432811801025</v>
+      </c>
+      <c r="D89">
+        <v>5216.361718819898</v>
+      </c>
+      <c r="E89">
+        <v>3589.805</v>
+      </c>
+      <c r="F89">
+        <v>5847.705</v>
+      </c>
+      <c r="G89">
+        <v>285.4</v>
+      </c>
+      <c r="H89">
+        <v>4463.6</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K89">
+        <v>213.8</v>
+      </c>
+      <c r="L89">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M89">
+        <v>533.310696</v>
+      </c>
+      <c r="N89">
+        <v>310.3382835918367</v>
+      </c>
+      <c r="O89">
+        <v>38.79228544897958</v>
+      </c>
+      <c r="P89">
+        <v>271.5459981428571</v>
+      </c>
+      <c r="Q89">
+        <v>485.3459981428571</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.3254082818190588</v>
+      </c>
+      <c r="T89">
+        <v>3.881133386194262</v>
+      </c>
+      <c r="U89">
+        <v>0.0912</v>
+      </c>
+      <c r="V89">
+        <v>0.125</v>
+      </c>
+      <c r="W89">
+        <v>0.07980000000000001</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>1.581908980861386</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.1120868198670015</v>
+      </c>
+      <c r="C90">
+        <v>-427.341088078676</v>
+      </c>
+      <c r="D90">
+        <v>5202.178911921324</v>
+      </c>
+      <c r="E90">
+        <v>3657.02</v>
+      </c>
+      <c r="F90">
+        <v>5914.92</v>
+      </c>
+      <c r="G90">
+        <v>285.4</v>
+      </c>
+      <c r="H90">
+        <v>4463.6</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K90">
+        <v>213.8</v>
+      </c>
+      <c r="L90">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M90">
+        <v>539.440704</v>
+      </c>
+      <c r="N90">
+        <v>304.2082755918367</v>
+      </c>
+      <c r="O90">
+        <v>38.02603444897959</v>
+      </c>
+      <c r="P90">
+        <v>266.1822411428571</v>
+      </c>
+      <c r="Q90">
+        <v>479.9822411428571</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.3488568322250127</v>
+      </c>
+      <c r="T90">
+        <v>4.198664168140964</v>
+      </c>
+      <c r="U90">
+        <v>0.0912</v>
+      </c>
+      <c r="V90">
+        <v>0.125</v>
+      </c>
+      <c r="W90">
+        <v>0.07980000000000001</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>1.563932742442507</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.1124445630975254</v>
+      </c>
+      <c r="C91">
+        <v>-508.6619806099116</v>
+      </c>
+      <c r="D91">
+        <v>5188.073019390089</v>
+      </c>
+      <c r="E91">
+        <v>3724.235</v>
+      </c>
+      <c r="F91">
+        <v>5982.135</v>
+      </c>
+      <c r="G91">
+        <v>285.4</v>
+      </c>
+      <c r="H91">
+        <v>4463.6</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K91">
+        <v>213.8</v>
+      </c>
+      <c r="L91">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M91">
+        <v>545.5707120000001</v>
+      </c>
+      <c r="N91">
+        <v>298.0782675918366</v>
+      </c>
+      <c r="O91">
+        <v>37.25978344897958</v>
+      </c>
+      <c r="P91">
+        <v>260.818484142857</v>
+      </c>
+      <c r="Q91">
+        <v>474.618484142857</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.3765687554320492</v>
+      </c>
+      <c r="T91">
+        <v>4.573927819532522</v>
+      </c>
+      <c r="U91">
+        <v>0.0912</v>
+      </c>
+      <c r="V91">
+        <v>0.125</v>
+      </c>
+      <c r="W91">
+        <v>0.07980000000000001</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>1.546360464437535</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.1128023063280493</v>
+      </c>
+      <c r="C92">
+        <v>-589.9065827499708</v>
+      </c>
+      <c r="D92">
+        <v>5174.04341725003</v>
+      </c>
+      <c r="E92">
+        <v>3791.45</v>
+      </c>
+      <c r="F92">
+        <v>6049.35</v>
+      </c>
+      <c r="G92">
+        <v>285.4</v>
+      </c>
+      <c r="H92">
+        <v>4463.6</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K92">
+        <v>213.8</v>
+      </c>
+      <c r="L92">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M92">
+        <v>551.70072</v>
+      </c>
+      <c r="N92">
+        <v>291.9482595918366</v>
+      </c>
+      <c r="O92">
+        <v>36.49353244897958</v>
+      </c>
+      <c r="P92">
+        <v>255.4547271428571</v>
+      </c>
+      <c r="Q92">
+        <v>469.2547271428571</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.4098230632804929</v>
+      </c>
+      <c r="T92">
+        <v>5.024244201202391</v>
+      </c>
+      <c r="U92">
+        <v>0.0912</v>
+      </c>
+      <c r="V92">
+        <v>0.125</v>
+      </c>
+      <c r="W92">
+        <v>0.07980000000000001</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>1.52917868149934</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.1131600495585732</v>
+      </c>
+      <c r="C93">
+        <v>-671.0755117437939</v>
+      </c>
+      <c r="D93">
+        <v>5160.089488256207</v>
+      </c>
+      <c r="E93">
+        <v>3858.665</v>
+      </c>
+      <c r="F93">
+        <v>6116.565000000001</v>
+      </c>
+      <c r="G93">
+        <v>285.4</v>
+      </c>
+      <c r="H93">
+        <v>4463.6</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K93">
+        <v>213.8</v>
+      </c>
+      <c r="L93">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M93">
+        <v>557.830728</v>
+      </c>
+      <c r="N93">
+        <v>285.8182515918367</v>
+      </c>
+      <c r="O93">
+        <v>35.72728144897958</v>
+      </c>
+      <c r="P93">
+        <v>250.0909701428571</v>
+      </c>
+      <c r="Q93">
+        <v>463.8909701428571</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.4504672173174796</v>
+      </c>
+      <c r="T93">
+        <v>5.574630889910009</v>
+      </c>
+      <c r="U93">
+        <v>0.0912</v>
+      </c>
+      <c r="V93">
+        <v>0.125</v>
+      </c>
+      <c r="W93">
+        <v>0.07980000000000001</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>1.512374520164183</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.1691036593594997</v>
+      </c>
+      <c r="C94">
+        <v>-2268.9632337335</v>
+      </c>
+      <c r="D94">
+        <v>3629.416766266501</v>
+      </c>
+      <c r="E94">
+        <v>3925.880000000001</v>
+      </c>
+      <c r="F94">
+        <v>6183.780000000001</v>
+      </c>
+      <c r="G94">
+        <v>285.4</v>
+      </c>
+      <c r="H94">
+        <v>4463.6</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K94">
+        <v>213.8</v>
+      </c>
+      <c r="L94">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M94">
+        <v>968.3799480000002</v>
+      </c>
+      <c r="N94">
+        <v>-124.7309684081636</v>
+      </c>
+      <c r="O94">
+        <v>-15.59137105102045</v>
+      </c>
+      <c r="P94">
+        <v>-109.1395973571431</v>
+      </c>
+      <c r="Q94">
+        <v>104.6604026428569</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.5090129078960364</v>
+      </c>
+      <c r="T94">
+        <v>6.367432943221524</v>
+      </c>
+      <c r="U94">
+        <v>0.1566</v>
+      </c>
+      <c r="V94">
+        <v>0.1088995312911824</v>
+      </c>
+      <c r="W94">
+        <v>0.1395463333998009</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.871196250329459</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.1702816593594997</v>
+      </c>
+      <c r="C95">
+        <v>-2358.707781617833</v>
+      </c>
+      <c r="D95">
+        <v>3606.887218382167</v>
+      </c>
+      <c r="E95">
+        <v>3993.095</v>
+      </c>
+      <c r="F95">
+        <v>6250.995</v>
+      </c>
+      <c r="G95">
+        <v>285.4</v>
+      </c>
+      <c r="H95">
+        <v>4463.6</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K95">
+        <v>213.8</v>
+      </c>
+      <c r="L95">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M95">
+        <v>978.9058170000001</v>
+      </c>
+      <c r="N95">
+        <v>-135.2568374081634</v>
+      </c>
+      <c r="O95">
+        <v>-16.90710467602042</v>
+      </c>
+      <c r="P95">
+        <v>-118.349732732143</v>
+      </c>
+      <c r="Q95">
+        <v>95.45026726785704</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.5761861804526129</v>
+      </c>
+      <c r="T95">
+        <v>7.277066220824598</v>
+      </c>
+      <c r="U95">
+        <v>0.1566</v>
+      </c>
+      <c r="V95">
+        <v>0.1077285685891267</v>
+      </c>
+      <c r="W95">
+        <v>0.1397297061589428</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.8618285487130133</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.1714596593594997</v>
+      </c>
+      <c r="C96">
+        <v>-2448.174351413656</v>
+      </c>
+      <c r="D96">
+        <v>3584.635648586343</v>
+      </c>
+      <c r="E96">
+        <v>4060.31</v>
+      </c>
+      <c r="F96">
+        <v>6318.21</v>
+      </c>
+      <c r="G96">
+        <v>285.4</v>
+      </c>
+      <c r="H96">
+        <v>4463.6</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K96">
+        <v>213.8</v>
+      </c>
+      <c r="L96">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M96">
+        <v>989.4316860000001</v>
+      </c>
+      <c r="N96">
+        <v>-145.7827064081634</v>
+      </c>
+      <c r="O96">
+        <v>-18.22283830102043</v>
+      </c>
+      <c r="P96">
+        <v>-127.559868107143</v>
+      </c>
+      <c r="Q96">
+        <v>86.24013189285699</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.665750543861382</v>
+      </c>
+      <c r="T96">
+        <v>8.489910590962035</v>
+      </c>
+      <c r="U96">
+        <v>0.1566</v>
+      </c>
+      <c r="V96">
+        <v>0.1065825199871147</v>
+      </c>
+      <c r="W96">
+        <v>0.1399091773700179</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.8526601598969175</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.1726376593594997</v>
+      </c>
+      <c r="C97">
+        <v>-2537.368056275249</v>
+      </c>
+      <c r="D97">
+        <v>3562.656943724751</v>
+      </c>
+      <c r="E97">
+        <v>4127.525</v>
+      </c>
+      <c r="F97">
+        <v>6385.425</v>
+      </c>
+      <c r="G97">
+        <v>285.4</v>
+      </c>
+      <c r="H97">
+        <v>4463.6</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K97">
+        <v>213.8</v>
+      </c>
+      <c r="L97">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M97">
+        <v>999.9575550000002</v>
+      </c>
+      <c r="N97">
+        <v>-156.3085754081635</v>
+      </c>
+      <c r="O97">
+        <v>-19.53857192602044</v>
+      </c>
+      <c r="P97">
+        <v>-136.7700034821431</v>
+      </c>
+      <c r="Q97">
+        <v>77.02999651785694</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>0.7911406526336588</v>
+      </c>
+      <c r="T97">
+        <v>10.18789270915445</v>
+      </c>
+      <c r="U97">
+        <v>0.1566</v>
+      </c>
+      <c r="V97">
+        <v>0.1054605987240924</v>
+      </c>
+      <c r="W97">
+        <v>0.1400848702398071</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.8436847897927393</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.1738156593594997</v>
+      </c>
+      <c r="C98">
+        <v>-2626.293884718652</v>
+      </c>
+      <c r="D98">
+        <v>3540.946115281347</v>
+      </c>
+      <c r="E98">
+        <v>4194.74</v>
+      </c>
+      <c r="F98">
+        <v>6452.639999999999</v>
+      </c>
+      <c r="G98">
+        <v>285.4</v>
+      </c>
+      <c r="H98">
+        <v>4463.6</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K98">
+        <v>213.8</v>
+      </c>
+      <c r="L98">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M98">
+        <v>1010.483424</v>
+      </c>
+      <c r="N98">
+        <v>-166.8344444081633</v>
+      </c>
+      <c r="O98">
+        <v>-20.85430555102042</v>
+      </c>
+      <c r="P98">
+        <v>-145.9801388571429</v>
+      </c>
+      <c r="Q98">
+        <v>67.81986114285709</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>0.9792258157920712</v>
+      </c>
+      <c r="T98">
+        <v>12.73486588644303</v>
+      </c>
+      <c r="U98">
+        <v>0.1566</v>
+      </c>
+      <c r="V98">
+        <v>0.1043620508207165</v>
+      </c>
+      <c r="W98">
+        <v>0.1402569028414758</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.8348964065657317</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.1749936593594997</v>
+      </c>
+      <c r="C99">
+        <v>-2714.956704396405</v>
+      </c>
+      <c r="D99">
+        <v>3519.498295603594</v>
+      </c>
+      <c r="E99">
+        <v>4261.955</v>
+      </c>
+      <c r="F99">
+        <v>6519.855</v>
+      </c>
+      <c r="G99">
+        <v>285.4</v>
+      </c>
+      <c r="H99">
+        <v>4463.6</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K99">
+        <v>213.8</v>
+      </c>
+      <c r="L99">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M99">
+        <v>1021.009293</v>
+      </c>
+      <c r="N99">
+        <v>-177.3603134081634</v>
+      </c>
+      <c r="O99">
+        <v>-22.17003917602042</v>
+      </c>
+      <c r="P99">
+        <v>-155.190274232143</v>
+      </c>
+      <c r="Q99">
+        <v>58.60972576785704</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.292701087722762</v>
+      </c>
+      <c r="T99">
+        <v>16.97982118192404</v>
+      </c>
+      <c r="U99">
+        <v>0.1566</v>
+      </c>
+      <c r="V99">
+        <v>0.1032861533895751</v>
+      </c>
+      <c r="W99">
+        <v>0.1404253883791926</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.8262892271166005</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.1761716593594997</v>
+      </c>
+      <c r="C100">
+        <v>-2803.361265735901</v>
+      </c>
+      <c r="D100">
+        <v>3498.308734264098</v>
+      </c>
+      <c r="E100">
+        <v>4329.17</v>
+      </c>
+      <c r="F100">
+        <v>6587.07</v>
+      </c>
+      <c r="G100">
+        <v>285.4</v>
+      </c>
+      <c r="H100">
+        <v>4463.6</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K100">
+        <v>213.8</v>
+      </c>
+      <c r="L100">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M100">
+        <v>1031.535162</v>
+      </c>
+      <c r="N100">
+        <v>-187.8861824081634</v>
+      </c>
+      <c r="O100">
+        <v>-23.48577280102043</v>
+      </c>
+      <c r="P100">
+        <v>-164.400409607143</v>
+      </c>
+      <c r="Q100">
+        <v>49.39959039285699</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>1.919651631584143</v>
+      </c>
+      <c r="T100">
+        <v>25.46973177288606</v>
+      </c>
+      <c r="U100">
+        <v>0.1566</v>
+      </c>
+      <c r="V100">
+        <v>0.1022322130488651</v>
+      </c>
+      <c r="W100">
+        <v>0.1405904354365477</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.8178577043909208</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.1773496593594996</v>
+      </c>
+      <c r="C101">
+        <v>-2891.512205447114</v>
+      </c>
+      <c r="D101">
+        <v>3477.372794552886</v>
+      </c>
+      <c r="E101">
+        <v>4396.385</v>
+      </c>
+      <c r="F101">
+        <v>6654.285</v>
+      </c>
+      <c r="G101">
+        <v>285.4</v>
+      </c>
+      <c r="H101">
+        <v>4463.6</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>1057.448979591837</v>
+      </c>
+      <c r="K101">
+        <v>213.8</v>
+      </c>
+      <c r="L101">
+        <v>843.6489795918367</v>
+      </c>
+      <c r="M101">
+        <v>1042.061031</v>
+      </c>
+      <c r="N101">
+        <v>-198.4120514081635</v>
+      </c>
+      <c r="O101">
+        <v>-24.80150642602044</v>
+      </c>
+      <c r="P101">
+        <v>-173.6105449821431</v>
+      </c>
+      <c r="Q101">
+        <v>40.18945501785694</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>3.800503263168285</v>
+      </c>
+      <c r="T101">
+        <v>50.93946354577211</v>
+      </c>
+      <c r="U101">
+        <v>0.1566</v>
+      </c>
+      <c r="V101">
+        <v>0.1011995644322099</v>
+      </c>
+      <c r="W101">
+        <v>0.1407521482099159</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.8095965154576791</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/cyprus/cyprus_oil_gas_distribution.xlsx
+++ b/research/traditional_assets/database/data/cyprus/cyprus_oil_gas_distribution.xlsx
@@ -1388,7 +1388,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1525,22 +1525,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07937436471013312</v>
+        <v>0.07931452175424546</v>
       </c>
       <c r="C2">
-        <v>7895.205980324839</v>
+        <v>7839.233531323476</v>
       </c>
       <c r="D2">
-        <v>7574.30598032484</v>
+        <v>7587.830531323477</v>
       </c>
       <c r="E2">
-        <v>-3790.699999999999</v>
+        <v>-3721.203</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>69.49699999999999</v>
       </c>
       <c r="G2">
         <v>320.9</v>
@@ -1561,28 +1561,28 @@
         <v>925.225</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>3.495699099999999</v>
       </c>
       <c r="N2">
-        <v>925.225</v>
+        <v>921.7293009</v>
       </c>
       <c r="O2">
-        <v>115.653125</v>
+        <v>115.2161626125</v>
       </c>
       <c r="P2">
-        <v>809.571875</v>
+        <v>806.5131382874999</v>
       </c>
       <c r="Q2">
-        <v>1125.471875</v>
+        <v>1122.4131382875</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07937436471013312</v>
+        <v>0.07967110783257117</v>
       </c>
       <c r="T2">
-        <v>0.5661120226706919</v>
+        <v>0.5711155380225794</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>264.6752404976733</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1607,22 +1607,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07931452175424546</v>
+        <v>0.07925467879835781</v>
       </c>
       <c r="C3">
-        <v>7839.233531323476</v>
+        <v>7783.30946713033</v>
       </c>
       <c r="D3">
-        <v>7587.830531323477</v>
+        <v>7601.40346713033</v>
       </c>
       <c r="E3">
-        <v>-3721.203</v>
+        <v>-3651.705999999999</v>
       </c>
       <c r="F3">
-        <v>69.49699999999999</v>
+        <v>138.994</v>
       </c>
       <c r="G3">
         <v>320.9</v>
@@ -1643,28 +1643,28 @@
         <v>925.225</v>
       </c>
       <c r="M3">
-        <v>3.495699099999999</v>
+        <v>6.991398199999998</v>
       </c>
       <c r="N3">
-        <v>921.7293009</v>
+        <v>918.2336018</v>
       </c>
       <c r="O3">
-        <v>115.2161626125</v>
+        <v>114.779200225</v>
       </c>
       <c r="P3">
-        <v>806.5131382874999</v>
+        <v>803.454401575</v>
       </c>
       <c r="Q3">
-        <v>1122.4131382875</v>
+        <v>1119.354401575</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07967110783257117</v>
+        <v>0.0799739069370998</v>
       </c>
       <c r="T3">
-        <v>0.5711155380225794</v>
+        <v>0.5762211659326686</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1681,7 +1681,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>264.6752404976733</v>
+        <v>132.3376202488367</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1689,22 +1689,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07925467879835781</v>
+        <v>0.07919483584247011</v>
       </c>
       <c r="C4">
-        <v>7783.30946713033</v>
+        <v>7727.434047859573</v>
       </c>
       <c r="D4">
-        <v>7601.40346713033</v>
+        <v>7615.025047859574</v>
       </c>
       <c r="E4">
-        <v>-3651.705999999999</v>
+        <v>-3582.208999999999</v>
       </c>
       <c r="F4">
-        <v>138.994</v>
+        <v>208.491</v>
       </c>
       <c r="G4">
         <v>320.9</v>
@@ -1725,28 +1725,28 @@
         <v>925.225</v>
       </c>
       <c r="M4">
-        <v>6.991398199999998</v>
+        <v>10.4870973</v>
       </c>
       <c r="N4">
-        <v>918.2336018</v>
+        <v>914.7379027000001</v>
       </c>
       <c r="O4">
-        <v>114.779200225</v>
+        <v>114.3422378375</v>
       </c>
       <c r="P4">
-        <v>803.454401575</v>
+        <v>800.3956648625001</v>
       </c>
       <c r="Q4">
-        <v>1119.354401575</v>
+        <v>1116.2956648625</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.0799739069370998</v>
+        <v>0.08028294932213415</v>
       </c>
       <c r="T4">
-        <v>0.5762211659326686</v>
+        <v>0.5814320645213162</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1763,7 +1763,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>132.3376202488367</v>
+        <v>88.22508016589113</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1771,22 +1771,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07919483584247011</v>
+        <v>0.07913499288658246</v>
       </c>
       <c r="C5">
-        <v>7727.434047859573</v>
+        <v>7671.60753549318</v>
       </c>
       <c r="D5">
-        <v>7615.025047859574</v>
+        <v>7628.695535493181</v>
       </c>
       <c r="E5">
-        <v>-3582.208999999999</v>
+        <v>-3512.712</v>
       </c>
       <c r="F5">
-        <v>208.491</v>
+        <v>277.9879999999999</v>
       </c>
       <c r="G5">
         <v>320.9</v>
@@ -1807,28 +1807,28 @@
         <v>925.225</v>
       </c>
       <c r="M5">
-        <v>10.4870973</v>
+        <v>13.9827964</v>
       </c>
       <c r="N5">
-        <v>914.7379027000001</v>
+        <v>911.2422036</v>
       </c>
       <c r="O5">
-        <v>114.3422378375</v>
+        <v>113.90527545</v>
       </c>
       <c r="P5">
-        <v>800.3956648625001</v>
+        <v>797.3369281500001</v>
       </c>
       <c r="Q5">
-        <v>1116.2956648625</v>
+        <v>1113.23692815</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08028294932213415</v>
+        <v>0.08059843009019006</v>
       </c>
       <c r="T5">
-        <v>0.5814320645213162</v>
+        <v>0.5867515234972276</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1845,7 +1845,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>88.22508016589113</v>
+        <v>66.16881012441834</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1853,22 +1853,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07913499288658246</v>
+        <v>0.07907514993069478</v>
       </c>
       <c r="C6">
-        <v>7671.60753549318</v>
+        <v>7615.830193897783</v>
       </c>
       <c r="D6">
-        <v>7628.695535493181</v>
+        <v>7642.415193897783</v>
       </c>
       <c r="E6">
-        <v>-3512.712</v>
+        <v>-3443.214999999999</v>
       </c>
       <c r="F6">
-        <v>277.9879999999999</v>
+        <v>347.485</v>
       </c>
       <c r="G6">
         <v>320.9</v>
@@ -1889,28 +1889,28 @@
         <v>925.225</v>
       </c>
       <c r="M6">
-        <v>13.9827964</v>
+        <v>17.4784955</v>
       </c>
       <c r="N6">
-        <v>911.2422036</v>
+        <v>907.7465045</v>
       </c>
       <c r="O6">
-        <v>113.90527545</v>
+        <v>113.4683130625</v>
       </c>
       <c r="P6">
-        <v>797.3369281500001</v>
+        <v>794.2781914375</v>
       </c>
       <c r="Q6">
-        <v>1113.23692815</v>
+        <v>1110.1781914375</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08059843009019006</v>
+        <v>0.0809205525586261</v>
       </c>
       <c r="T6">
-        <v>0.5867515234972276</v>
+        <v>0.592182971083158</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1927,7 +1927,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>66.16881012441834</v>
+        <v>52.93504809953466</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1935,22 +1935,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07907514993069478</v>
+        <v>0.07901530697480712</v>
       </c>
       <c r="C7">
-        <v>7615.830193897783</v>
+        <v>7560.102288841585</v>
       </c>
       <c r="D7">
-        <v>7642.415193897783</v>
+        <v>7656.184288841585</v>
       </c>
       <c r="E7">
-        <v>-3443.214999999999</v>
+        <v>-3373.717999999999</v>
       </c>
       <c r="F7">
-        <v>347.485</v>
+        <v>416.982</v>
       </c>
       <c r="G7">
         <v>320.9</v>
@@ -1971,28 +1971,28 @@
         <v>925.225</v>
       </c>
       <c r="M7">
-        <v>17.4784955</v>
+        <v>20.9741946</v>
       </c>
       <c r="N7">
-        <v>907.7465045</v>
+        <v>904.2508054</v>
       </c>
       <c r="O7">
-        <v>113.4683130625</v>
+        <v>113.031350675</v>
       </c>
       <c r="P7">
-        <v>794.2781914375</v>
+        <v>791.219454725</v>
       </c>
       <c r="Q7">
-        <v>1110.1781914375</v>
+        <v>1107.119454725</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.0809205525586261</v>
+        <v>0.08124952869660332</v>
       </c>
       <c r="T7">
-        <v>0.592182971083158</v>
+        <v>0.5977299813836827</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>52.93504809953466</v>
+        <v>44.11254008294555</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2017,22 +2017,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07901530697480712</v>
+        <v>0.07895546401891947</v>
       </c>
       <c r="C8">
-        <v>7560.102288841585</v>
+        <v>7504.424088011561</v>
       </c>
       <c r="D8">
-        <v>7656.184288841585</v>
+        <v>7670.003088011562</v>
       </c>
       <c r="E8">
-        <v>-3373.717999999999</v>
+        <v>-3304.221</v>
       </c>
       <c r="F8">
-        <v>416.9819999999999</v>
+        <v>486.4789999999999</v>
       </c>
       <c r="G8">
         <v>320.9</v>
@@ -2053,28 +2053,28 @@
         <v>925.225</v>
       </c>
       <c r="M8">
-        <v>20.97419459999999</v>
+        <v>24.46989369999999</v>
       </c>
       <c r="N8">
-        <v>904.2508054</v>
+        <v>900.7551063000001</v>
       </c>
       <c r="O8">
-        <v>113.031350675</v>
+        <v>112.5943882875</v>
       </c>
       <c r="P8">
-        <v>791.219454725</v>
+        <v>788.1607180125001</v>
       </c>
       <c r="Q8">
-        <v>1107.119454725</v>
+        <v>1104.0607180125</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08124952869660332</v>
+        <v>0.08158557959023599</v>
       </c>
       <c r="T8">
-        <v>0.5977299813836827</v>
+        <v>0.6033962822283048</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2091,7 +2091,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>44.11254008294556</v>
+        <v>37.81074864252476</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2099,22 +2099,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07895546401891947</v>
+        <v>0.0788956210630318</v>
       </c>
       <c r="C9">
-        <v>7504.424088011561</v>
+        <v>7448.795861030807</v>
       </c>
       <c r="D9">
-        <v>7670.003088011562</v>
+        <v>7683.871861030807</v>
       </c>
       <c r="E9">
-        <v>-3304.221</v>
+        <v>-3234.723999999999</v>
       </c>
       <c r="F9">
-        <v>486.479</v>
+        <v>555.9759999999999</v>
       </c>
       <c r="G9">
         <v>320.9</v>
@@ -2135,28 +2135,28 @@
         <v>925.225</v>
       </c>
       <c r="M9">
-        <v>24.4698937</v>
+        <v>27.96559279999999</v>
       </c>
       <c r="N9">
-        <v>900.7551063000001</v>
+        <v>897.2594072000001</v>
       </c>
       <c r="O9">
-        <v>112.5943882875</v>
+        <v>112.1574259</v>
       </c>
       <c r="P9">
-        <v>788.1607180125001</v>
+        <v>785.1019813</v>
       </c>
       <c r="Q9">
-        <v>1104.0607180125</v>
+        <v>1101.0019813</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08158557959023599</v>
+        <v>0.08192893593807804</v>
       </c>
       <c r="T9">
-        <v>0.6033962822283048</v>
+        <v>0.6091857635260708</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>37.81074864252476</v>
+        <v>33.08440506220917</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2181,22 +2181,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.0788956210630318</v>
+        <v>0.07883577810714412</v>
       </c>
       <c r="C10">
-        <v>7448.795861030807</v>
+        <v>7393.217879476048</v>
       </c>
       <c r="D10">
-        <v>7683.871861030807</v>
+        <v>7697.790879476049</v>
       </c>
       <c r="E10">
-        <v>-3234.723999999999</v>
+        <v>-3165.226999999999</v>
       </c>
       <c r="F10">
-        <v>555.9759999999999</v>
+        <v>625.4729999999998</v>
       </c>
       <c r="G10">
         <v>320.9</v>
@@ -2217,28 +2217,28 @@
         <v>925.225</v>
       </c>
       <c r="M10">
-        <v>27.96559279999999</v>
+        <v>31.46129189999999</v>
       </c>
       <c r="N10">
-        <v>897.2594072000001</v>
+        <v>893.7637081</v>
       </c>
       <c r="O10">
-        <v>112.1574259</v>
+        <v>111.7204635125</v>
       </c>
       <c r="P10">
-        <v>785.1019813</v>
+        <v>782.0432445875</v>
       </c>
       <c r="Q10">
-        <v>1101.0019813</v>
+        <v>1097.9432445875</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08192893593807804</v>
+        <v>0.08227983857927926</v>
       </c>
       <c r="T10">
-        <v>0.6091857635260708</v>
+        <v>0.6151024861710402</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2255,7 +2255,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>33.08440506220917</v>
+        <v>29.40836005529704</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07883577810714412</v>
+        <v>0.07877593515125646</v>
       </c>
       <c r="C11">
-        <v>7393.217879476048</v>
+        <v>7337.690416895381</v>
       </c>
       <c r="D11">
-        <v>7697.790879476049</v>
+        <v>7711.760416895381</v>
       </c>
       <c r="E11">
-        <v>-3165.226999999999</v>
+        <v>-3095.73</v>
       </c>
       <c r="F11">
-        <v>625.4729999999998</v>
+        <v>694.9699999999998</v>
       </c>
       <c r="G11">
         <v>320.9</v>
@@ -2299,28 +2299,28 @@
         <v>925.225</v>
       </c>
       <c r="M11">
-        <v>31.46129189999999</v>
+        <v>34.95699099999999</v>
       </c>
       <c r="N11">
-        <v>893.7637081</v>
+        <v>890.268009</v>
       </c>
       <c r="O11">
-        <v>111.7204635125</v>
+        <v>111.283501125</v>
       </c>
       <c r="P11">
-        <v>782.0432445875</v>
+        <v>778.984507875</v>
       </c>
       <c r="Q11">
-        <v>1097.9432445875</v>
+        <v>1094.884507875</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08227983857927926</v>
+        <v>0.08263853905695162</v>
       </c>
       <c r="T11">
-        <v>0.6151024861710402</v>
+        <v>0.6211506915414537</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2337,7 +2337,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>29.40836005529704</v>
+        <v>26.46752404976733</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2345,22 +2345,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07877593515125646</v>
+        <v>0.07871609219536878</v>
       </c>
       <c r="C12">
-        <v>7337.690416895381</v>
+        <v>7282.213748826204</v>
       </c>
       <c r="D12">
-        <v>7711.760416895381</v>
+        <v>7725.780748826204</v>
       </c>
       <c r="E12">
-        <v>-3095.73</v>
+        <v>-3026.232999999999</v>
       </c>
       <c r="F12">
-        <v>694.9699999999999</v>
+        <v>764.4669999999999</v>
       </c>
       <c r="G12">
         <v>320.9</v>
@@ -2381,28 +2381,28 @@
         <v>925.225</v>
       </c>
       <c r="M12">
-        <v>34.956991</v>
+        <v>38.45269009999999</v>
       </c>
       <c r="N12">
-        <v>890.268009</v>
+        <v>886.7723099</v>
       </c>
       <c r="O12">
-        <v>111.283501125</v>
+        <v>110.8465387375</v>
       </c>
       <c r="P12">
-        <v>778.984507875</v>
+        <v>775.9257711625</v>
       </c>
       <c r="Q12">
-        <v>1094.884507875</v>
+        <v>1091.8257711625</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08263853905695162</v>
+        <v>0.08300530021951549</v>
       </c>
       <c r="T12">
-        <v>0.6211506915414537</v>
+        <v>0.6273348116392921</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2419,7 +2419,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>26.46752404976733</v>
+        <v>24.06138549978849</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2427,22 +2427,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07871609219536878</v>
+        <v>0.07865624923948113</v>
       </c>
       <c r="C13">
-        <v>7282.213748826204</v>
+        <v>7226.788152813306</v>
       </c>
       <c r="D13">
-        <v>7725.780748826204</v>
+        <v>7739.852152813306</v>
       </c>
       <c r="E13">
-        <v>-3026.232999999999</v>
+        <v>-2956.735999999999</v>
       </c>
       <c r="F13">
-        <v>764.4669999999999</v>
+        <v>833.9639999999998</v>
       </c>
       <c r="G13">
         <v>320.9</v>
@@ -2463,28 +2463,28 @@
         <v>925.225</v>
       </c>
       <c r="M13">
-        <v>38.45269009999999</v>
+        <v>41.94838919999999</v>
       </c>
       <c r="N13">
-        <v>886.7723099</v>
+        <v>883.2766108000001</v>
       </c>
       <c r="O13">
-        <v>110.8465387375</v>
+        <v>110.40957635</v>
       </c>
       <c r="P13">
-        <v>775.9257711625</v>
+        <v>772.8670344500001</v>
       </c>
       <c r="Q13">
-        <v>1091.8257711625</v>
+        <v>1088.76703445</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08300530021951549</v>
+        <v>0.08338039686304674</v>
       </c>
       <c r="T13">
-        <v>0.6273348116392921</v>
+        <v>0.6336594799211722</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2501,7 +2501,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>24.06138549978849</v>
+        <v>22.05627004147278</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2509,22 +2509,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07865624923948113</v>
+        <v>0.07859640628359345</v>
       </c>
       <c r="C14">
-        <v>7226.788152813306</v>
+        <v>7171.413908427224</v>
       </c>
       <c r="D14">
-        <v>7739.852152813306</v>
+        <v>7753.974908427224</v>
       </c>
       <c r="E14">
-        <v>-2956.735999999999</v>
+        <v>-2887.239</v>
       </c>
       <c r="F14">
-        <v>833.9639999999998</v>
+        <v>903.4609999999999</v>
       </c>
       <c r="G14">
         <v>320.9</v>
@@ -2545,28 +2545,28 @@
         <v>925.225</v>
       </c>
       <c r="M14">
-        <v>41.94838919999999</v>
+        <v>45.44408829999999</v>
       </c>
       <c r="N14">
-        <v>883.2766108000001</v>
+        <v>879.7809117</v>
       </c>
       <c r="O14">
-        <v>110.40957635</v>
+        <v>109.9726139625</v>
       </c>
       <c r="P14">
-        <v>772.8670344500001</v>
+        <v>769.8082977375001</v>
       </c>
       <c r="Q14">
-        <v>1088.76703445</v>
+        <v>1085.7082977375</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08338039686304674</v>
+        <v>0.08376411641792351</v>
       </c>
       <c r="T14">
-        <v>0.6336594799211722</v>
+        <v>0.6401295428761991</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>22.05627004147278</v>
+        <v>20.35963388443641</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2591,22 +2591,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07859640628359345</v>
+        <v>0.0785365633277058</v>
       </c>
       <c r="C15">
-        <v>7171.413908427224</v>
+        <v>7116.091297282705</v>
       </c>
       <c r="D15">
-        <v>7753.974908427224</v>
+        <v>7768.149297282705</v>
       </c>
       <c r="E15">
-        <v>-2887.239</v>
+        <v>-2817.741999999999</v>
       </c>
       <c r="F15">
-        <v>903.4609999999999</v>
+        <v>972.958</v>
       </c>
       <c r="G15">
         <v>320.9</v>
@@ -2627,28 +2627,28 @@
         <v>925.225</v>
       </c>
       <c r="M15">
-        <v>45.44408829999999</v>
+        <v>48.93978739999999</v>
       </c>
       <c r="N15">
-        <v>879.7809117</v>
+        <v>876.2852126</v>
       </c>
       <c r="O15">
-        <v>109.9726139625</v>
+        <v>109.535651575</v>
       </c>
       <c r="P15">
-        <v>769.8082977375001</v>
+        <v>766.749561025</v>
       </c>
       <c r="Q15">
-        <v>1085.7082977375</v>
+        <v>1082.649561025</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08376411641792351</v>
+        <v>0.08415675968337884</v>
       </c>
       <c r="T15">
-        <v>0.6401295428761991</v>
+        <v>0.6467500724115754</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2665,7 +2665,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>20.35963388443641</v>
+        <v>18.90537432126238</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2673,22 +2673,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.0785365633277058</v>
+        <v>0.07847672037181813</v>
       </c>
       <c r="C16">
-        <v>7116.091297282705</v>
+        <v>7060.820603057474</v>
       </c>
       <c r="D16">
-        <v>7768.149297282705</v>
+        <v>7782.375603057474</v>
       </c>
       <c r="E16">
-        <v>-2817.741999999999</v>
+        <v>-2748.244999999999</v>
       </c>
       <c r="F16">
-        <v>972.958</v>
+        <v>1042.455</v>
       </c>
       <c r="G16">
         <v>320.9</v>
@@ -2709,28 +2709,28 @@
         <v>925.225</v>
       </c>
       <c r="M16">
-        <v>48.93978739999999</v>
+        <v>52.4354865</v>
       </c>
       <c r="N16">
-        <v>876.2852126</v>
+        <v>872.7895135</v>
       </c>
       <c r="O16">
-        <v>109.535651575</v>
+        <v>109.0986891875</v>
       </c>
       <c r="P16">
-        <v>766.749561025</v>
+        <v>763.6908243125</v>
       </c>
       <c r="Q16">
-        <v>1082.649561025</v>
+        <v>1079.5908243125</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08415675968337884</v>
+        <v>0.08455864161390368</v>
       </c>
       <c r="T16">
-        <v>0.6467500724115754</v>
+        <v>0.65352637911249</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2747,7 +2747,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>18.90537432126238</v>
+        <v>17.64501603317822</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2755,22 +2755,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.0784767203718181</v>
+        <v>0.07841687741593045</v>
       </c>
       <c r="C17">
-        <v>7060.820603057479</v>
+        <v>7005.602111511125</v>
       </c>
       <c r="D17">
-        <v>7782.37560305748</v>
+        <v>7796.654111511126</v>
       </c>
       <c r="E17">
-        <v>-2748.245</v>
+        <v>-2678.748</v>
       </c>
       <c r="F17">
-        <v>1042.455</v>
+        <v>1111.952</v>
       </c>
       <c r="G17">
         <v>320.9</v>
@@ -2791,28 +2791,28 @@
         <v>925.225</v>
       </c>
       <c r="M17">
-        <v>52.43548649999998</v>
+        <v>55.93118559999998</v>
       </c>
       <c r="N17">
-        <v>872.7895135</v>
+        <v>869.2938144000001</v>
       </c>
       <c r="O17">
-        <v>109.0986891875</v>
+        <v>108.6617268</v>
       </c>
       <c r="P17">
-        <v>763.6908243125</v>
+        <v>760.6320876000001</v>
       </c>
       <c r="Q17">
-        <v>1079.5908243125</v>
+        <v>1076.5320876</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08455864161390367</v>
+        <v>0.08497009216182197</v>
       </c>
       <c r="T17">
-        <v>0.6535263791124899</v>
+        <v>0.6604640264491406</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2829,7 +2829,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>17.64501603317822</v>
+        <v>16.54220253110459</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2837,22 +2837,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07841687741593045</v>
+        <v>0.0783570344600428</v>
       </c>
       <c r="C18">
-        <v>7005.602111511125</v>
+        <v>6950.436110504264</v>
       </c>
       <c r="D18">
-        <v>7796.654111511126</v>
+        <v>7810.985110504264</v>
       </c>
       <c r="E18">
-        <v>-2678.748</v>
+        <v>-2609.250999999999</v>
       </c>
       <c r="F18">
-        <v>1111.952</v>
+        <v>1181.449</v>
       </c>
       <c r="G18">
         <v>320.9</v>
@@ -2873,28 +2873,28 @@
         <v>925.225</v>
       </c>
       <c r="M18">
-        <v>55.93118559999998</v>
+        <v>59.42688469999999</v>
       </c>
       <c r="N18">
-        <v>869.2938144000001</v>
+        <v>865.7981153000001</v>
       </c>
       <c r="O18">
-        <v>108.6617268</v>
+        <v>108.2247644125</v>
       </c>
       <c r="P18">
-        <v>760.6320876000001</v>
+        <v>757.5733508875001</v>
       </c>
       <c r="Q18">
-        <v>1076.5320876</v>
+        <v>1073.4733508875</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08497009216182197</v>
+        <v>0.08539145718077445</v>
       </c>
       <c r="T18">
-        <v>0.6604640264491406</v>
+        <v>0.6675688460107708</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2911,7 +2911,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>16.54220253110459</v>
+        <v>15.56913179398078</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2919,22 +2919,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.0783570344600428</v>
+        <v>0.07829719150415512</v>
       </c>
       <c r="C19">
-        <v>6950.436110504264</v>
+        <v>6895.32289001787</v>
       </c>
       <c r="D19">
-        <v>7810.985110504264</v>
+        <v>7825.36889001787</v>
       </c>
       <c r="E19">
-        <v>-2609.250999999999</v>
+        <v>-2539.753999999999</v>
       </c>
       <c r="F19">
-        <v>1181.449</v>
+        <v>1250.946</v>
       </c>
       <c r="G19">
         <v>320.9</v>
@@ -2955,28 +2955,28 @@
         <v>925.225</v>
       </c>
       <c r="M19">
-        <v>59.42688469999999</v>
+        <v>62.92258379999999</v>
       </c>
       <c r="N19">
-        <v>865.7981153000001</v>
+        <v>862.3024162</v>
       </c>
       <c r="O19">
-        <v>108.2247644125</v>
+        <v>107.787802025</v>
       </c>
       <c r="P19">
-        <v>757.5733508875001</v>
+        <v>754.514614175</v>
       </c>
       <c r="Q19">
-        <v>1073.4733508875</v>
+        <v>1070.414614175</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08539145718077445</v>
+        <v>0.08582309939531113</v>
       </c>
       <c r="T19">
-        <v>0.6675688460107708</v>
+        <v>0.674846953854392</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2993,7 +2993,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>15.56913179398078</v>
+        <v>14.70418002764852</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3001,22 +3001,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07829719150415512</v>
+        <v>0.07823734854826749</v>
       </c>
       <c r="C20">
-        <v>6895.32289001787</v>
+        <v>6840.262742172818</v>
       </c>
       <c r="D20">
-        <v>7825.36889001787</v>
+        <v>7839.805742172818</v>
       </c>
       <c r="E20">
-        <v>-2539.754</v>
+        <v>-2470.257</v>
       </c>
       <c r="F20">
-        <v>1250.946</v>
+        <v>1320.443</v>
       </c>
       <c r="G20">
         <v>320.9</v>
@@ -3037,28 +3037,28 @@
         <v>925.225</v>
       </c>
       <c r="M20">
-        <v>62.92258379999998</v>
+        <v>66.41828289999998</v>
       </c>
       <c r="N20">
-        <v>862.3024162</v>
+        <v>858.8067171</v>
       </c>
       <c r="O20">
-        <v>107.787802025</v>
+        <v>107.3508396375</v>
       </c>
       <c r="P20">
-        <v>754.514614175</v>
+        <v>751.4558774625</v>
       </c>
       <c r="Q20">
-        <v>1070.414614175</v>
+        <v>1067.3558774625</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08582309939531113</v>
+        <v>0.08626539944230552</v>
       </c>
       <c r="T20">
-        <v>0.674846953854392</v>
+        <v>0.6823047680645222</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -3075,7 +3075,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>14.70418002764852</v>
+        <v>13.93027581566702</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3083,22 +3083,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07823734854826749</v>
+        <v>0.07817750559237979</v>
       </c>
       <c r="C21">
-        <v>6840.262742172818</v>
+        <v>6785.255961249711</v>
       </c>
       <c r="D21">
-        <v>7839.805742172818</v>
+        <v>7854.295961249711</v>
       </c>
       <c r="E21">
-        <v>-2470.257</v>
+        <v>-2400.759999999999</v>
       </c>
       <c r="F21">
-        <v>1320.443</v>
+        <v>1389.94</v>
       </c>
       <c r="G21">
         <v>320.9</v>
@@ -3119,28 +3119,28 @@
         <v>925.225</v>
       </c>
       <c r="M21">
-        <v>66.41828289999998</v>
+        <v>69.91398199999999</v>
       </c>
       <c r="N21">
-        <v>858.8067171</v>
+        <v>855.311018</v>
       </c>
       <c r="O21">
-        <v>107.3508396375</v>
+        <v>106.91387725</v>
       </c>
       <c r="P21">
-        <v>751.4558774625</v>
+        <v>748.3971407499999</v>
       </c>
       <c r="Q21">
-        <v>1067.3558774625</v>
+        <v>1064.29714075</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08626539944230552</v>
+        <v>0.08671875699047474</v>
       </c>
       <c r="T21">
-        <v>0.6823047680645222</v>
+        <v>0.6899490276299058</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3157,7 +3157,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>13.93027581566702</v>
+        <v>13.23376202488367</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3165,22 +3165,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07817750559237979</v>
+        <v>0.07839328763649214</v>
       </c>
       <c r="C22">
-        <v>6785.255961249711</v>
+        <v>6663.760032621098</v>
       </c>
       <c r="D22">
-        <v>7854.295961249711</v>
+        <v>7802.297032621098</v>
       </c>
       <c r="E22">
-        <v>-2400.759999999999</v>
+        <v>-2331.262999999999</v>
       </c>
       <c r="F22">
-        <v>1389.94</v>
+        <v>1459.437</v>
       </c>
       <c r="G22">
         <v>320.9</v>
@@ -3201,45 +3201,45 @@
         <v>925.225</v>
       </c>
       <c r="M22">
-        <v>69.91398199999999</v>
+        <v>75.5988366</v>
       </c>
       <c r="N22">
-        <v>855.311018</v>
+        <v>849.6261634</v>
       </c>
       <c r="O22">
-        <v>106.91387725</v>
+        <v>106.203270425</v>
       </c>
       <c r="P22">
-        <v>748.3971407499999</v>
+        <v>743.422892975</v>
       </c>
       <c r="Q22">
-        <v>1064.29714075</v>
+        <v>1059.322892975</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08671875699047474</v>
+        <v>0.08718359194492675</v>
       </c>
       <c r="T22">
-        <v>0.6899490276299058</v>
+        <v>0.6977868127539067</v>
       </c>
       <c r="U22">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V22">
         <v>0.125</v>
       </c>
       <c r="W22">
-        <v>0.0440125</v>
+        <v>0.045325</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y22">
-        <v>13.23376202488367</v>
+        <v>12.238614264601</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3247,22 +3247,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07839328763649214</v>
+        <v>0.07834656968060447</v>
       </c>
       <c r="C23">
-        <v>6663.760032621098</v>
+        <v>6605.462595959711</v>
       </c>
       <c r="D23">
-        <v>7802.297032621098</v>
+        <v>7813.496595959711</v>
       </c>
       <c r="E23">
-        <v>-2331.263</v>
+        <v>-2261.766</v>
       </c>
       <c r="F23">
-        <v>1459.437</v>
+        <v>1528.934</v>
       </c>
       <c r="G23">
         <v>320.9</v>
@@ -3283,28 +3283,28 @@
         <v>925.225</v>
       </c>
       <c r="M23">
-        <v>75.59883659999998</v>
+        <v>79.19878119999998</v>
       </c>
       <c r="N23">
-        <v>849.6261634</v>
+        <v>846.0262188</v>
       </c>
       <c r="O23">
-        <v>106.203270425</v>
+        <v>105.75327735</v>
       </c>
       <c r="P23">
-        <v>743.422892975</v>
+        <v>740.2729414500001</v>
       </c>
       <c r="Q23">
-        <v>1059.322892975</v>
+        <v>1056.17294145</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08718359194492675</v>
+        <v>0.08766034574436471</v>
       </c>
       <c r="T23">
-        <v>0.6977868127539066</v>
+        <v>0.7058255667272409</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3321,7 +3321,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>12.238614264601</v>
+        <v>11.68231361621005</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07834656968060447</v>
+        <v>0.07829985172471679</v>
       </c>
       <c r="C24">
-        <v>6605.462595959711</v>
+        <v>6547.197357642518</v>
       </c>
       <c r="D24">
-        <v>7813.496595959711</v>
+        <v>7824.728357642518</v>
       </c>
       <c r="E24">
-        <v>-2261.766</v>
+        <v>-2192.268999999999</v>
       </c>
       <c r="F24">
-        <v>1528.934</v>
+        <v>1598.431</v>
       </c>
       <c r="G24">
         <v>320.9</v>
@@ -3365,28 +3365,28 @@
         <v>925.225</v>
       </c>
       <c r="M24">
-        <v>79.19878119999998</v>
+        <v>82.79872579999999</v>
       </c>
       <c r="N24">
-        <v>846.0262188</v>
+        <v>842.4262742000001</v>
       </c>
       <c r="O24">
-        <v>105.75327735</v>
+        <v>105.303284275</v>
       </c>
       <c r="P24">
-        <v>740.2729414500001</v>
+        <v>737.1229899250001</v>
       </c>
       <c r="Q24">
-        <v>1056.17294145</v>
+        <v>1053.022989925</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08766034574436471</v>
+        <v>0.08814948275937246</v>
       </c>
       <c r="T24">
-        <v>0.7058255667272409</v>
+        <v>0.7140731195050772</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3403,7 +3403,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>11.68231361621005</v>
+        <v>11.17438693724439</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3411,22 +3411,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07829985172471679</v>
+        <v>0.07825313376882914</v>
       </c>
       <c r="C25">
-        <v>6547.197357642518</v>
+        <v>6488.964456723029</v>
       </c>
       <c r="D25">
-        <v>7824.728357642518</v>
+        <v>7835.992456723029</v>
       </c>
       <c r="E25">
-        <v>-2192.268999999999</v>
+        <v>-2122.771999999999</v>
       </c>
       <c r="F25">
-        <v>1598.431</v>
+        <v>1667.928</v>
       </c>
       <c r="G25">
         <v>320.9</v>
@@ -3447,28 +3447,28 @@
         <v>925.225</v>
       </c>
       <c r="M25">
-        <v>82.79872579999999</v>
+        <v>86.39867039999999</v>
       </c>
       <c r="N25">
-        <v>842.4262742000001</v>
+        <v>838.8263296</v>
       </c>
       <c r="O25">
-        <v>105.303284275</v>
+        <v>104.8532912</v>
       </c>
       <c r="P25">
-        <v>737.1229899250001</v>
+        <v>733.9730384</v>
       </c>
       <c r="Q25">
-        <v>1053.022989925</v>
+        <v>1049.8730384</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08814948275937246</v>
+        <v>0.08865149180109097</v>
       </c>
       <c r="T25">
-        <v>0.7140731195050772</v>
+        <v>0.7225377131454884</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3485,7 +3485,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>11.17438693724439</v>
+        <v>10.70878748152587</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3493,22 +3493,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07825313376882913</v>
+        <v>0.07820641581294147</v>
       </c>
       <c r="C26">
-        <v>6488.964456723032</v>
+        <v>6430.764033056632</v>
       </c>
       <c r="D26">
-        <v>7835.992456723032</v>
+        <v>7847.289033056632</v>
       </c>
       <c r="E26">
-        <v>-2122.772</v>
+        <v>-2053.275</v>
       </c>
       <c r="F26">
-        <v>1667.928</v>
+        <v>1737.425</v>
       </c>
       <c r="G26">
         <v>320.9</v>
@@ -3529,28 +3529,28 @@
         <v>925.225</v>
       </c>
       <c r="M26">
-        <v>86.39867039999999</v>
+        <v>89.99861499999999</v>
       </c>
       <c r="N26">
-        <v>838.8263296</v>
+        <v>835.2263850000001</v>
       </c>
       <c r="O26">
-        <v>104.8532912</v>
+        <v>104.403298125</v>
       </c>
       <c r="P26">
-        <v>733.9730384</v>
+        <v>730.8230868750001</v>
       </c>
       <c r="Q26">
-        <v>1049.8730384</v>
+        <v>1046.723086875</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08865149180109096</v>
+        <v>0.08916688775058862</v>
       </c>
       <c r="T26">
-        <v>0.7225377131454883</v>
+        <v>0.731228029282977</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3567,7 +3567,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>10.70878748152587</v>
+        <v>10.28043598226484</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3575,22 +3575,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07820641581294147</v>
+        <v>0.0781596978570538</v>
       </c>
       <c r="C27">
-        <v>6430.764033056632</v>
+        <v>6372.596227306329</v>
       </c>
       <c r="D27">
-        <v>7847.289033056632</v>
+        <v>7858.618227306329</v>
       </c>
       <c r="E27">
-        <v>-2053.275</v>
+        <v>-1983.778</v>
       </c>
       <c r="F27">
-        <v>1737.425</v>
+        <v>1806.922</v>
       </c>
       <c r="G27">
         <v>320.9</v>
@@ -3611,28 +3611,28 @@
         <v>925.225</v>
       </c>
       <c r="M27">
-        <v>89.99861499999999</v>
+        <v>93.59855959999999</v>
       </c>
       <c r="N27">
-        <v>835.2263850000001</v>
+        <v>831.6264404000001</v>
       </c>
       <c r="O27">
-        <v>104.403298125</v>
+        <v>103.95330505</v>
       </c>
       <c r="P27">
-        <v>730.8230868750001</v>
+        <v>727.6731353500001</v>
       </c>
       <c r="Q27">
-        <v>1046.723086875</v>
+        <v>1043.57313535</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08916688775058862</v>
+        <v>0.08969621332034297</v>
       </c>
       <c r="T27">
-        <v>0.731228029282977</v>
+        <v>0.7401532188295871</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3649,7 +3649,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>10.28043598226484</v>
+        <v>9.885034598331577</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3657,22 +3657,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.0781596978570538</v>
+        <v>0.07851460490116613</v>
       </c>
       <c r="C28">
-        <v>6372.596227306329</v>
+        <v>6217.844370208509</v>
       </c>
       <c r="D28">
-        <v>7858.618227306329</v>
+        <v>7773.363370208509</v>
       </c>
       <c r="E28">
-        <v>-1983.778</v>
+        <v>-1914.280999999999</v>
       </c>
       <c r="F28">
-        <v>1806.922</v>
+        <v>1876.419</v>
       </c>
       <c r="G28">
         <v>320.9</v>
@@ -3693,45 +3693,45 @@
         <v>925.225</v>
       </c>
       <c r="M28">
-        <v>93.59855959999999</v>
+        <v>100.3884165</v>
       </c>
       <c r="N28">
-        <v>831.6264404000001</v>
+        <v>824.8365835000001</v>
       </c>
       <c r="O28">
-        <v>103.95330505</v>
+        <v>103.1045729375</v>
       </c>
       <c r="P28">
-        <v>727.6731353500001</v>
+        <v>721.7320105625</v>
       </c>
       <c r="Q28">
-        <v>1043.57313535</v>
+        <v>1037.6320105625</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08969621332034297</v>
+        <v>0.09024004096050156</v>
       </c>
       <c r="T28">
-        <v>0.7401532188295871</v>
+        <v>0.7493229341172002</v>
       </c>
       <c r="U28">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V28">
         <v>0.125</v>
       </c>
       <c r="W28">
-        <v>0.045325</v>
+        <v>0.0468125</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y28">
-        <v>9.885034598331577</v>
+        <v>9.216451780569725</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3739,22 +3739,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07851460490116613</v>
+        <v>0.07848276194527848</v>
       </c>
       <c r="C29">
-        <v>6217.844370208509</v>
+        <v>6155.920991657966</v>
       </c>
       <c r="D29">
-        <v>7773.363370208509</v>
+        <v>7780.936991657966</v>
       </c>
       <c r="E29">
-        <v>-1914.280999999999</v>
+        <v>-1844.783999999999</v>
       </c>
       <c r="F29">
-        <v>1876.419</v>
+        <v>1945.916</v>
       </c>
       <c r="G29">
         <v>320.9</v>
@@ -3775,28 +3775,28 @@
         <v>925.225</v>
       </c>
       <c r="M29">
-        <v>100.3884165</v>
+        <v>104.106506</v>
       </c>
       <c r="N29">
-        <v>824.8365835000001</v>
+        <v>821.1184940000001</v>
       </c>
       <c r="O29">
-        <v>103.1045729375</v>
+        <v>102.63981175</v>
       </c>
       <c r="P29">
-        <v>721.7320105625</v>
+        <v>718.47868225</v>
       </c>
       <c r="Q29">
-        <v>1037.6320105625</v>
+        <v>1034.37868225</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09024004096050156</v>
+        <v>0.09079897492399788</v>
       </c>
       <c r="T29">
-        <v>0.7493229341172002</v>
+        <v>0.758747363718358</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3813,7 +3813,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>9.216451780569725</v>
+        <v>8.887292788406519</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3821,22 +3821,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07848276194527848</v>
+        <v>0.0784509189893908</v>
       </c>
       <c r="C30">
-        <v>6155.920991657966</v>
+        <v>6094.012385524327</v>
       </c>
       <c r="D30">
-        <v>7780.936991657966</v>
+        <v>7788.525385524327</v>
       </c>
       <c r="E30">
-        <v>-1844.783999999999</v>
+        <v>-1775.286999999999</v>
       </c>
       <c r="F30">
-        <v>1945.916</v>
+        <v>2015.413</v>
       </c>
       <c r="G30">
         <v>320.9</v>
@@ -3857,28 +3857,28 @@
         <v>925.225</v>
       </c>
       <c r="M30">
-        <v>104.106506</v>
+        <v>107.8245955</v>
       </c>
       <c r="N30">
-        <v>821.1184940000001</v>
+        <v>817.4004045</v>
       </c>
       <c r="O30">
-        <v>102.63981175</v>
+        <v>102.1750505625</v>
       </c>
       <c r="P30">
-        <v>718.47868225</v>
+        <v>715.2253539375</v>
       </c>
       <c r="Q30">
-        <v>1034.37868225</v>
+        <v>1031.1253539375</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09079897492399788</v>
+        <v>0.09137365350618423</v>
       </c>
       <c r="T30">
-        <v>0.758747363718358</v>
+        <v>0.7684372702096893</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -3895,7 +3895,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>8.887292788406519</v>
+        <v>8.580834416392502</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3903,22 +3903,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.0784509189893908</v>
+        <v>0.07841907603350312</v>
       </c>
       <c r="C31">
-        <v>6094.012385524327</v>
+        <v>6032.118595070378</v>
       </c>
       <c r="D31">
-        <v>7788.525385524327</v>
+        <v>7796.128595070379</v>
       </c>
       <c r="E31">
-        <v>-1775.287</v>
+        <v>-1705.79</v>
       </c>
       <c r="F31">
-        <v>2015.413</v>
+        <v>2084.909999999999</v>
       </c>
       <c r="G31">
         <v>320.9</v>
@@ -3939,28 +3939,28 @@
         <v>925.225</v>
       </c>
       <c r="M31">
-        <v>107.8245955</v>
+        <v>111.542685</v>
       </c>
       <c r="N31">
-        <v>817.4004045</v>
+        <v>813.682315</v>
       </c>
       <c r="O31">
-        <v>102.1750505625</v>
+        <v>101.710289375</v>
       </c>
       <c r="P31">
-        <v>715.2253539375</v>
+        <v>711.972025625</v>
       </c>
       <c r="Q31">
-        <v>1031.1253539375</v>
+        <v>1027.872025625</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09137365350618423</v>
+        <v>0.09196475147643304</v>
       </c>
       <c r="T31">
-        <v>0.7684372702096892</v>
+        <v>0.7784040311722014</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -3977,7 +3977,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>8.580834416392502</v>
+        <v>8.294806602512754</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3985,22 +3985,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07841907603350312</v>
+        <v>0.07838723307761547</v>
       </c>
       <c r="C32">
-        <v>6032.118595070378</v>
+        <v>5970.239663728004</v>
       </c>
       <c r="D32">
-        <v>7796.128595070379</v>
+        <v>7803.746663728003</v>
       </c>
       <c r="E32">
-        <v>-1705.79</v>
+        <v>-1636.293</v>
       </c>
       <c r="F32">
-        <v>2084.909999999999</v>
+        <v>2154.407</v>
       </c>
       <c r="G32">
         <v>320.9</v>
@@ -4021,28 +4021,28 @@
         <v>925.225</v>
       </c>
       <c r="M32">
-        <v>111.542685</v>
+        <v>115.2607745</v>
       </c>
       <c r="N32">
-        <v>813.682315</v>
+        <v>809.9642255</v>
       </c>
       <c r="O32">
-        <v>101.710289375</v>
+        <v>101.2455281875</v>
       </c>
       <c r="P32">
-        <v>711.972025625</v>
+        <v>708.7186973125</v>
       </c>
       <c r="Q32">
-        <v>1027.872025625</v>
+        <v>1024.6186973125</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09196475147643304</v>
+        <v>0.09257298272118183</v>
       </c>
       <c r="T32">
-        <v>0.7784040311722014</v>
+        <v>0.7886596837568155</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -4059,7 +4059,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>8.294806602512754</v>
+        <v>8.027232195980083</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4067,22 +4067,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07838723307761547</v>
+        <v>0.07835539012172779</v>
       </c>
       <c r="C33">
-        <v>5970.239663728004</v>
+        <v>5908.375635099029</v>
       </c>
       <c r="D33">
-        <v>7803.746663728003</v>
+        <v>7811.379635099029</v>
       </c>
       <c r="E33">
-        <v>-1636.293</v>
+        <v>-1566.796</v>
       </c>
       <c r="F33">
-        <v>2154.407</v>
+        <v>2223.904</v>
       </c>
       <c r="G33">
         <v>320.9</v>
@@ -4103,28 +4103,28 @@
         <v>925.225</v>
       </c>
       <c r="M33">
-        <v>115.2607745</v>
+        <v>118.978864</v>
       </c>
       <c r="N33">
-        <v>809.9642255</v>
+        <v>806.2461360000001</v>
       </c>
       <c r="O33">
-        <v>101.2455281875</v>
+        <v>100.780767</v>
       </c>
       <c r="P33">
-        <v>708.7186973125</v>
+        <v>705.4653690000001</v>
       </c>
       <c r="Q33">
-        <v>1024.6186973125</v>
+        <v>1021.365369</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09257298272118183</v>
+        <v>0.09319910312018795</v>
       </c>
       <c r="T33">
-        <v>0.7886596837568155</v>
+        <v>0.7992169731821533</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4141,7 +4141,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>8.027232195980083</v>
+        <v>7.776381189855706</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4149,22 +4149,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07835539012172779</v>
+        <v>0.07855454716584014</v>
       </c>
       <c r="C34">
-        <v>5908.375635099029</v>
+        <v>5791.383205817438</v>
       </c>
       <c r="D34">
-        <v>7811.379635099029</v>
+        <v>7763.884205817438</v>
       </c>
       <c r="E34">
-        <v>-1566.796</v>
+        <v>-1497.299</v>
       </c>
       <c r="F34">
-        <v>2223.904</v>
+        <v>2293.401</v>
       </c>
       <c r="G34">
         <v>320.9</v>
@@ -4185,45 +4185,45 @@
         <v>925.225</v>
       </c>
       <c r="M34">
-        <v>118.978864</v>
+        <v>124.5316743</v>
       </c>
       <c r="N34">
-        <v>806.2461360000001</v>
+        <v>800.6933257000001</v>
       </c>
       <c r="O34">
-        <v>100.780767</v>
+        <v>100.0866657125</v>
       </c>
       <c r="P34">
-        <v>705.4653690000001</v>
+        <v>700.6066599875001</v>
       </c>
       <c r="Q34">
-        <v>1021.365369</v>
+        <v>1016.5066599875</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09319910312018795</v>
+        <v>0.09384391368035841</v>
       </c>
       <c r="T34">
-        <v>0.7992169731821533</v>
+        <v>0.8100894055754119</v>
       </c>
       <c r="U34">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V34">
         <v>0.125</v>
       </c>
       <c r="W34">
-        <v>0.0468125</v>
+        <v>0.0475125</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y34">
-        <v>7.776381189855706</v>
+        <v>7.429635915527076</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4231,22 +4231,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07855454716584014</v>
+        <v>0.07852970420995246</v>
       </c>
       <c r="C35">
-        <v>5791.383205817438</v>
+        <v>5727.779257328226</v>
       </c>
       <c r="D35">
-        <v>7763.884205817438</v>
+        <v>7769.777257328226</v>
       </c>
       <c r="E35">
-        <v>-1497.299</v>
+        <v>-1427.802</v>
       </c>
       <c r="F35">
-        <v>2293.401</v>
+        <v>2362.898</v>
       </c>
       <c r="G35">
         <v>320.9</v>
@@ -4267,28 +4267,28 @@
         <v>925.225</v>
       </c>
       <c r="M35">
-        <v>124.5316743</v>
+        <v>128.3053614</v>
       </c>
       <c r="N35">
-        <v>800.6933257000001</v>
+        <v>796.9196386000001</v>
       </c>
       <c r="O35">
-        <v>100.0866657125</v>
+        <v>99.61495482500001</v>
       </c>
       <c r="P35">
-        <v>700.6066599875001</v>
+        <v>697.3046837750001</v>
       </c>
       <c r="Q35">
-        <v>1016.5066599875</v>
+        <v>1013.204683775</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09384391368035841</v>
+        <v>0.09450826395447344</v>
       </c>
       <c r="T35">
-        <v>0.8100894055754119</v>
+        <v>0.8212913056169509</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4305,7 +4305,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>7.429635915527076</v>
+        <v>7.211117212129222</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4313,22 +4313,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07852970420995246</v>
+        <v>0.07850486125406481</v>
       </c>
       <c r="C36">
-        <v>5727.779257328226</v>
+        <v>5664.184261686576</v>
       </c>
       <c r="D36">
-        <v>7769.777257328226</v>
+        <v>7775.679261686576</v>
       </c>
       <c r="E36">
-        <v>-1427.802</v>
+        <v>-1358.304999999999</v>
       </c>
       <c r="F36">
-        <v>2362.898</v>
+        <v>2432.395</v>
       </c>
       <c r="G36">
         <v>320.9</v>
@@ -4349,28 +4349,28 @@
         <v>925.225</v>
       </c>
       <c r="M36">
-        <v>128.3053614</v>
+        <v>132.0790485</v>
       </c>
       <c r="N36">
-        <v>796.9196386000001</v>
+        <v>793.1459515</v>
       </c>
       <c r="O36">
-        <v>99.61495482500001</v>
+        <v>99.1432439375</v>
       </c>
       <c r="P36">
-        <v>697.3046837750001</v>
+        <v>694.0027075625001</v>
       </c>
       <c r="Q36">
-        <v>1013.204683775</v>
+        <v>1009.9027075625</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09450826395447344</v>
+        <v>0.09519305577548431</v>
       </c>
       <c r="T36">
-        <v>0.8212913056169509</v>
+        <v>0.8328378795059218</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4387,7 +4387,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>7.211117212129222</v>
+        <v>7.005085291782671</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07850486125406481</v>
+        <v>0.07848001829817713</v>
       </c>
       <c r="C37">
-        <v>5664.184261686576</v>
+        <v>5600.598239310036</v>
       </c>
       <c r="D37">
-        <v>7775.679261686576</v>
+        <v>7781.590239310036</v>
       </c>
       <c r="E37">
-        <v>-1358.304999999999</v>
+        <v>-1288.808</v>
       </c>
       <c r="F37">
-        <v>2432.395</v>
+        <v>2501.892</v>
       </c>
       <c r="G37">
         <v>320.9</v>
@@ -4431,28 +4431,28 @@
         <v>925.225</v>
       </c>
       <c r="M37">
-        <v>132.0790485</v>
+        <v>135.8527356</v>
       </c>
       <c r="N37">
-        <v>793.1459515</v>
+        <v>789.3722644000001</v>
       </c>
       <c r="O37">
-        <v>99.1432439375</v>
+        <v>98.67153305000001</v>
       </c>
       <c r="P37">
-        <v>694.0027075625001</v>
+        <v>690.7007313500001</v>
       </c>
       <c r="Q37">
-        <v>1009.9027075625</v>
+        <v>1006.60073135</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09519305577548431</v>
+        <v>0.09589924734090177</v>
       </c>
       <c r="T37">
-        <v>0.8328378795059218</v>
+        <v>0.8447452838289231</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4469,7 +4469,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>7.005085291782671</v>
+        <v>6.810499589233153</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4477,22 +4477,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07848001829817713</v>
+        <v>0.07845517534228946</v>
       </c>
       <c r="C38">
-        <v>5600.598239310037</v>
+        <v>5537.021210678273</v>
       </c>
       <c r="D38">
-        <v>7781.590239310036</v>
+        <v>7787.510210678272</v>
       </c>
       <c r="E38">
-        <v>-1288.808</v>
+        <v>-1219.311</v>
       </c>
       <c r="F38">
-        <v>2501.891999999999</v>
+        <v>2571.389</v>
       </c>
       <c r="G38">
         <v>320.9</v>
@@ -4513,28 +4513,28 @@
         <v>925.225</v>
       </c>
       <c r="M38">
-        <v>135.8527356</v>
+        <v>139.6264227</v>
       </c>
       <c r="N38">
-        <v>789.3722644000001</v>
+        <v>785.5985773</v>
       </c>
       <c r="O38">
-        <v>98.67153305000001</v>
+        <v>98.1998221625</v>
       </c>
       <c r="P38">
-        <v>690.7007313500001</v>
+        <v>687.3987551375</v>
       </c>
       <c r="Q38">
-        <v>1006.60073135</v>
+        <v>1003.2987551375</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09589924734090177</v>
+        <v>0.09662785768617375</v>
       </c>
       <c r="T38">
-        <v>0.8447452838289231</v>
+        <v>0.8570307009875753</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4551,7 +4551,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>6.810499589233154</v>
+        <v>6.626432032767392</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4559,22 +4559,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07845517534228946</v>
+        <v>0.07843033238640179</v>
       </c>
       <c r="C39">
-        <v>5537.021210678273</v>
+        <v>5473.453196333328</v>
       </c>
       <c r="D39">
-        <v>7787.510210678272</v>
+        <v>7793.439196333328</v>
       </c>
       <c r="E39">
-        <v>-1219.311</v>
+        <v>-1149.814</v>
       </c>
       <c r="F39">
-        <v>2571.389</v>
+        <v>2640.886</v>
       </c>
       <c r="G39">
         <v>320.9</v>
@@ -4595,28 +4595,28 @@
         <v>925.225</v>
       </c>
       <c r="M39">
-        <v>139.6264227</v>
+        <v>143.4001098</v>
       </c>
       <c r="N39">
-        <v>785.5985773</v>
+        <v>781.8248902</v>
       </c>
       <c r="O39">
-        <v>98.1998221625</v>
+        <v>97.728111275</v>
       </c>
       <c r="P39">
-        <v>687.3987551375</v>
+        <v>684.0967789250001</v>
       </c>
       <c r="Q39">
-        <v>1003.2987551375</v>
+        <v>999.9967789250001</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09662785768617375</v>
+        <v>0.09737997159097064</v>
       </c>
       <c r="T39">
-        <v>0.8570307009875753</v>
+        <v>0.8697124219255388</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -4633,7 +4633,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>6.626432032767392</v>
+        <v>6.452052242431408</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4641,22 +4641,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07843033238640179</v>
+        <v>0.07840548943051413</v>
       </c>
       <c r="C40">
-        <v>5473.453196333328</v>
+        <v>5409.894216879846</v>
       </c>
       <c r="D40">
-        <v>7793.439196333328</v>
+        <v>7799.377216879846</v>
       </c>
       <c r="E40">
-        <v>-1149.814</v>
+        <v>-1080.317</v>
       </c>
       <c r="F40">
-        <v>2640.886</v>
+        <v>2710.383</v>
       </c>
       <c r="G40">
         <v>320.9</v>
@@ -4677,28 +4677,28 @@
         <v>925.225</v>
       </c>
       <c r="M40">
-        <v>143.4001098</v>
+        <v>147.1737969</v>
       </c>
       <c r="N40">
-        <v>781.8248902</v>
+        <v>778.0512031000001</v>
       </c>
       <c r="O40">
-        <v>97.728111275</v>
+        <v>97.25640038750001</v>
       </c>
       <c r="P40">
-        <v>684.0967789250001</v>
+        <v>680.7948027125001</v>
       </c>
       <c r="Q40">
-        <v>999.9967789250001</v>
+        <v>996.6948027125001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09737997159097064</v>
+        <v>0.09815674496805596</v>
       </c>
       <c r="T40">
-        <v>0.8697124219255388</v>
+        <v>0.8828099369926159</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -4715,7 +4715,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>6.452052242431408</v>
+        <v>6.286615005445987</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4723,22 +4723,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07840548943051413</v>
+        <v>0.07838064647462648</v>
       </c>
       <c r="C41">
-        <v>5409.894216879846</v>
+        <v>5346.344292985319</v>
       </c>
       <c r="D41">
-        <v>7799.377216879846</v>
+        <v>7805.32429298532</v>
       </c>
       <c r="E41">
-        <v>-1080.317</v>
+        <v>-1010.82</v>
       </c>
       <c r="F41">
-        <v>2710.383</v>
+        <v>2779.88</v>
       </c>
       <c r="G41">
         <v>320.9</v>
@@ -4759,28 +4759,28 @@
         <v>925.225</v>
       </c>
       <c r="M41">
-        <v>147.1737969</v>
+        <v>150.947484</v>
       </c>
       <c r="N41">
-        <v>778.0512031000001</v>
+        <v>774.2775160000001</v>
       </c>
       <c r="O41">
-        <v>97.25640038750001</v>
+        <v>96.78468950000001</v>
       </c>
       <c r="P41">
-        <v>680.7948027125001</v>
+        <v>677.4928265000001</v>
       </c>
       <c r="Q41">
-        <v>996.6948027125001</v>
+        <v>993.3928265000001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09815674496805596</v>
+        <v>0.09895941079104412</v>
       </c>
       <c r="T41">
-        <v>0.8828099369926159</v>
+        <v>0.8963440358952623</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4797,7 +4797,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>6.286615005445987</v>
+        <v>6.129449630309838</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4805,22 +4805,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07838064647462648</v>
+        <v>0.07871455351873879</v>
       </c>
       <c r="C42">
-        <v>5346.344292985319</v>
+        <v>5197.664910592526</v>
       </c>
       <c r="D42">
-        <v>7805.32429298532</v>
+        <v>7726.141910592527</v>
       </c>
       <c r="E42">
-        <v>-1010.82</v>
+        <v>-941.3229999999994</v>
       </c>
       <c r="F42">
-        <v>2779.88</v>
+        <v>2849.377</v>
       </c>
       <c r="G42">
         <v>320.9</v>
@@ -4841,45 +4841,45 @@
         <v>925.225</v>
       </c>
       <c r="M42">
-        <v>150.947484</v>
+        <v>157.5705481</v>
       </c>
       <c r="N42">
-        <v>774.2775160000001</v>
+        <v>767.6544519</v>
       </c>
       <c r="O42">
-        <v>96.78468950000001</v>
+        <v>95.9568064875</v>
       </c>
       <c r="P42">
-        <v>677.4928265000001</v>
+        <v>671.6976454125</v>
       </c>
       <c r="Q42">
-        <v>993.3928265000001</v>
+        <v>987.5976454125</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09895941079104412</v>
+        <v>0.09978928562498102</v>
       </c>
       <c r="T42">
-        <v>0.8963440358952623</v>
+        <v>0.9103369178115576</v>
       </c>
       <c r="U42">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V42">
         <v>0.125</v>
       </c>
       <c r="W42">
-        <v>0.0475125</v>
+        <v>0.0483875</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y42">
-        <v>6.129449630309838</v>
+        <v>5.871814315279392</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4887,22 +4887,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07871455351873879</v>
+        <v>0.07869846056285112</v>
       </c>
       <c r="C43">
-        <v>5197.664910592526</v>
+        <v>5131.947311173035</v>
       </c>
       <c r="D43">
-        <v>7726.141910592527</v>
+        <v>7729.921311173035</v>
       </c>
       <c r="E43">
-        <v>-941.3229999999994</v>
+        <v>-871.8259999999996</v>
       </c>
       <c r="F43">
-        <v>2849.377</v>
+        <v>2918.874</v>
       </c>
       <c r="G43">
         <v>320.9</v>
@@ -4923,28 +4923,28 @@
         <v>925.225</v>
       </c>
       <c r="M43">
-        <v>157.5705481</v>
+        <v>161.4137322</v>
       </c>
       <c r="N43">
-        <v>767.6544519</v>
+        <v>763.8112678</v>
       </c>
       <c r="O43">
-        <v>95.9568064875</v>
+        <v>95.476408475</v>
       </c>
       <c r="P43">
-        <v>671.6976454125</v>
+        <v>668.334859325</v>
       </c>
       <c r="Q43">
-        <v>987.5976454125</v>
+        <v>984.234859325</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09978928562498102</v>
+        <v>0.100647776832502</v>
       </c>
       <c r="T43">
-        <v>0.9103369178115576</v>
+        <v>0.9248123128973804</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.871814315279392</v>
+        <v>5.732009212534645</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4969,22 +4969,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07869846056285114</v>
+        <v>0.07868236760696347</v>
       </c>
       <c r="C44">
-        <v>5131.947311173033</v>
+        <v>5066.233411105579</v>
       </c>
       <c r="D44">
-        <v>7729.921311173032</v>
+        <v>7733.704411105578</v>
       </c>
       <c r="E44">
-        <v>-871.826</v>
+        <v>-802.3289999999997</v>
       </c>
       <c r="F44">
-        <v>2918.873999999999</v>
+        <v>2988.371</v>
       </c>
       <c r="G44">
         <v>320.9</v>
@@ -5005,28 +5005,28 @@
         <v>925.225</v>
       </c>
       <c r="M44">
-        <v>161.4137322</v>
+        <v>165.2569163</v>
       </c>
       <c r="N44">
-        <v>763.8112678</v>
+        <v>759.9680837000001</v>
       </c>
       <c r="O44">
-        <v>95.476408475</v>
+        <v>94.99601046250001</v>
       </c>
       <c r="P44">
-        <v>668.334859325</v>
+        <v>664.9720732375001</v>
       </c>
       <c r="Q44">
-        <v>984.234859325</v>
+        <v>980.8720732375001</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.100647776832502</v>
+        <v>0.1015363905385324</v>
       </c>
       <c r="T44">
-        <v>0.9248123128973803</v>
+        <v>0.9397956165827056</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -5043,7 +5043,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.732009212534646</v>
+        <v>5.598706672708259</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5051,22 +5051,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07868236760696347</v>
+        <v>0.07866627465107581</v>
       </c>
       <c r="C45">
-        <v>5066.233411105579</v>
+        <v>5000.523215824319</v>
       </c>
       <c r="D45">
-        <v>7733.704411105578</v>
+        <v>7737.491215824319</v>
       </c>
       <c r="E45">
-        <v>-802.3289999999997</v>
+        <v>-732.8319999999999</v>
       </c>
       <c r="F45">
-        <v>2988.371</v>
+        <v>3057.867999999999</v>
       </c>
       <c r="G45">
         <v>320.9</v>
@@ -5087,28 +5087,28 @@
         <v>925.225</v>
       </c>
       <c r="M45">
-        <v>165.2569163</v>
+        <v>169.1001004</v>
       </c>
       <c r="N45">
-        <v>759.9680837000001</v>
+        <v>756.1248996</v>
       </c>
       <c r="O45">
-        <v>94.99601046250001</v>
+        <v>94.51561245000001</v>
       </c>
       <c r="P45">
-        <v>664.9720732375001</v>
+        <v>661.60928715</v>
       </c>
       <c r="Q45">
-        <v>980.8720732375001</v>
+        <v>977.50928715</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1015363905385324</v>
+        <v>0.1024567404483497</v>
       </c>
       <c r="T45">
-        <v>0.9397956165827056</v>
+        <v>0.9553140382567926</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5125,7 +5125,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.598706672708259</v>
+        <v>5.471463339237617</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5133,22 +5133,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07866627465107581</v>
+        <v>0.07865018169518814</v>
       </c>
       <c r="C46">
-        <v>5000.523215824319</v>
+        <v>4934.816730774064</v>
       </c>
       <c r="D46">
-        <v>7737.491215824319</v>
+        <v>7741.281730774064</v>
       </c>
       <c r="E46">
-        <v>-732.8319999999999</v>
+        <v>-663.3349999999996</v>
       </c>
       <c r="F46">
-        <v>3057.867999999999</v>
+        <v>3127.365</v>
       </c>
       <c r="G46">
         <v>320.9</v>
@@ -5169,28 +5169,28 @@
         <v>925.225</v>
       </c>
       <c r="M46">
-        <v>169.1001004</v>
+        <v>172.9432845</v>
       </c>
       <c r="N46">
-        <v>756.1248996</v>
+        <v>752.2817155</v>
       </c>
       <c r="O46">
-        <v>94.51561245000001</v>
+        <v>94.0352144375</v>
       </c>
       <c r="P46">
-        <v>661.60928715</v>
+        <v>658.2465010625</v>
       </c>
       <c r="Q46">
-        <v>977.50928715</v>
+        <v>974.1465010625</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1024567404483497</v>
+        <v>0.1034105576276148</v>
       </c>
       <c r="T46">
-        <v>0.9553140382567926</v>
+        <v>0.9713967661735736</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5207,7 +5207,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.471463339237617</v>
+        <v>5.349875265032335</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5215,22 +5215,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07865018169518814</v>
+        <v>0.07863408873930047</v>
       </c>
       <c r="C47">
-        <v>4934.816730774064</v>
+        <v>4869.113961410296</v>
       </c>
       <c r="D47">
-        <v>7741.281730774064</v>
+        <v>7745.075961410295</v>
       </c>
       <c r="E47">
-        <v>-663.3349999999996</v>
+        <v>-593.8379999999997</v>
       </c>
       <c r="F47">
-        <v>3127.365</v>
+        <v>3196.862</v>
       </c>
       <c r="G47">
         <v>320.9</v>
@@ -5251,28 +5251,28 @@
         <v>925.225</v>
       </c>
       <c r="M47">
-        <v>172.9432845</v>
+        <v>176.7864686</v>
       </c>
       <c r="N47">
-        <v>752.2817155</v>
+        <v>748.4385314000001</v>
       </c>
       <c r="O47">
-        <v>94.0352144375</v>
+        <v>93.55481642500001</v>
       </c>
       <c r="P47">
-        <v>658.2465010625</v>
+        <v>654.8837149750001</v>
       </c>
       <c r="Q47">
-        <v>974.1465010625</v>
+        <v>970.7837149750001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1034105576276148</v>
+        <v>0.1043997013690749</v>
       </c>
       <c r="T47">
-        <v>0.9713967661735736</v>
+        <v>0.9880751506798651</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5289,7 +5289,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.349875265032335</v>
+        <v>5.233573628835981</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5297,22 +5297,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07863408873930047</v>
+        <v>0.0786179957834128</v>
       </c>
       <c r="C48">
-        <v>4869.113961410296</v>
+        <v>4803.414913199193</v>
       </c>
       <c r="D48">
-        <v>7745.075961410295</v>
+        <v>7748.873913199192</v>
       </c>
       <c r="E48">
-        <v>-593.8379999999997</v>
+        <v>-524.3409999999999</v>
       </c>
       <c r="F48">
-        <v>3196.862</v>
+        <v>3266.358999999999</v>
       </c>
       <c r="G48">
         <v>320.9</v>
@@ -5333,28 +5333,28 @@
         <v>925.225</v>
       </c>
       <c r="M48">
-        <v>176.7864686</v>
+        <v>180.6296527</v>
       </c>
       <c r="N48">
-        <v>748.4385314000001</v>
+        <v>744.5953473000001</v>
       </c>
       <c r="O48">
-        <v>93.55481642500001</v>
+        <v>93.07441841250001</v>
       </c>
       <c r="P48">
-        <v>654.8837149750001</v>
+        <v>651.5209288875001</v>
       </c>
       <c r="Q48">
-        <v>970.7837149750001</v>
+        <v>967.4209288875001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1043997013690749</v>
+        <v>0.1054261712894581</v>
       </c>
       <c r="T48">
-        <v>0.9880751506798651</v>
+        <v>1.005382908186394</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.233573628835981</v>
+        <v>5.122220998435215</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5379,22 +5379,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.0786179957834128</v>
+        <v>0.07860190282752513</v>
       </c>
       <c r="C49">
-        <v>4803.414913199193</v>
+        <v>4737.719591617664</v>
       </c>
       <c r="D49">
-        <v>7748.873913199192</v>
+        <v>7752.675591617664</v>
       </c>
       <c r="E49">
-        <v>-524.3409999999999</v>
+        <v>-454.8439999999996</v>
       </c>
       <c r="F49">
-        <v>3266.358999999999</v>
+        <v>3335.856</v>
       </c>
       <c r="G49">
         <v>320.9</v>
@@ -5415,28 +5415,28 @@
         <v>925.225</v>
       </c>
       <c r="M49">
-        <v>180.6296527</v>
+        <v>184.4728368</v>
       </c>
       <c r="N49">
-        <v>744.5953473000001</v>
+        <v>740.7521632</v>
       </c>
       <c r="O49">
-        <v>93.07441841250001</v>
+        <v>92.59402040000001</v>
       </c>
       <c r="P49">
-        <v>651.5209288875001</v>
+        <v>648.1581428000001</v>
       </c>
       <c r="Q49">
-        <v>967.4209288875001</v>
+        <v>964.0581428</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1054261712894581</v>
+        <v>0.1064921208221637</v>
       </c>
       <c r="T49">
-        <v>1.005382908186394</v>
+        <v>1.023356348673943</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5453,7 +5453,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.122220998435215</v>
+        <v>5.015508060967814</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07860190282752513</v>
+        <v>0.07858580987163746</v>
       </c>
       <c r="C50">
-        <v>4737.719591617664</v>
+        <v>4672.028002153374</v>
       </c>
       <c r="D50">
-        <v>7752.675591617664</v>
+        <v>7756.481002153374</v>
       </c>
       <c r="E50">
-        <v>-454.8440000000001</v>
+        <v>-385.3469999999998</v>
       </c>
       <c r="F50">
-        <v>3335.855999999999</v>
+        <v>3405.353</v>
       </c>
       <c r="G50">
         <v>320.9</v>
@@ -5497,28 +5497,28 @@
         <v>925.225</v>
       </c>
       <c r="M50">
-        <v>184.4728368</v>
+        <v>188.3160209</v>
       </c>
       <c r="N50">
-        <v>740.7521632</v>
+        <v>736.9089791</v>
       </c>
       <c r="O50">
-        <v>92.59402040000001</v>
+        <v>92.1136223875</v>
       </c>
       <c r="P50">
-        <v>648.1581428000001</v>
+        <v>644.7953567125001</v>
       </c>
       <c r="Q50">
-        <v>964.0581428</v>
+        <v>960.6953567125</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1064921208221637</v>
+        <v>0.1075998722973284</v>
       </c>
       <c r="T50">
-        <v>1.023356348673943</v>
+        <v>1.042034629964925</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5535,7 +5535,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.015508060967814</v>
+        <v>4.913150753601125</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5543,22 +5543,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07858580987163746</v>
+        <v>0.07856971691574981</v>
       </c>
       <c r="C51">
-        <v>4672.028002153374</v>
+        <v>4606.340150304762</v>
       </c>
       <c r="D51">
-        <v>7756.481002153374</v>
+        <v>7760.290150304761</v>
       </c>
       <c r="E51">
-        <v>-385.3469999999998</v>
+        <v>-315.8499999999999</v>
       </c>
       <c r="F51">
-        <v>3405.353</v>
+        <v>3474.849999999999</v>
       </c>
       <c r="G51">
         <v>320.9</v>
@@ -5579,28 +5579,28 @@
         <v>925.225</v>
       </c>
       <c r="M51">
-        <v>188.3160209</v>
+        <v>192.159205</v>
       </c>
       <c r="N51">
-        <v>736.9089791</v>
+        <v>733.065795</v>
       </c>
       <c r="O51">
-        <v>92.1136223875</v>
+        <v>91.633224375</v>
       </c>
       <c r="P51">
-        <v>644.7953567125001</v>
+        <v>641.4325706249999</v>
       </c>
       <c r="Q51">
-        <v>960.6953567125</v>
+        <v>957.3325706249999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1075998722973284</v>
+        <v>0.1087519338314996</v>
       </c>
       <c r="T51">
-        <v>1.042034629964925</v>
+        <v>1.061460042507547</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5617,7 +5617,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.913150753601125</v>
+        <v>4.814887738529102</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5625,22 +5625,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07856971691574981</v>
+        <v>0.07855362395986214</v>
       </c>
       <c r="C52">
-        <v>4606.340150304762</v>
+        <v>4540.65604158108</v>
       </c>
       <c r="D52">
-        <v>7760.290150304761</v>
+        <v>7764.10304158108</v>
       </c>
       <c r="E52">
-        <v>-315.8499999999999</v>
+        <v>-246.3530000000001</v>
       </c>
       <c r="F52">
-        <v>3474.849999999999</v>
+        <v>3544.346999999999</v>
       </c>
       <c r="G52">
         <v>320.9</v>
@@ -5661,28 +5661,28 @@
         <v>925.225</v>
       </c>
       <c r="M52">
-        <v>192.159205</v>
+        <v>196.0023891</v>
       </c>
       <c r="N52">
-        <v>733.065795</v>
+        <v>729.2226109000001</v>
       </c>
       <c r="O52">
-        <v>91.633224375</v>
+        <v>91.15282636250001</v>
       </c>
       <c r="P52">
-        <v>641.4325706249999</v>
+        <v>638.0697845375</v>
       </c>
       <c r="Q52">
-        <v>957.3325706249999</v>
+        <v>953.9697845375</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1087519338314996</v>
+        <v>0.1099510182854329</v>
       </c>
       <c r="T52">
-        <v>1.061460042507547</v>
+        <v>1.081678329031501</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5699,7 +5699,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.814887738529102</v>
+        <v>4.720478175028532</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5707,22 +5707,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07855362395986214</v>
+        <v>0.07853753100397447</v>
       </c>
       <c r="C53">
-        <v>4540.65604158108</v>
+        <v>4474.975681502408</v>
       </c>
       <c r="D53">
-        <v>7764.10304158108</v>
+        <v>7767.919681502409</v>
       </c>
       <c r="E53">
-        <v>-246.3530000000001</v>
+        <v>-176.8559999999998</v>
       </c>
       <c r="F53">
-        <v>3544.346999999999</v>
+        <v>3613.844</v>
       </c>
       <c r="G53">
         <v>320.9</v>
@@ -5743,28 +5743,28 @@
         <v>925.225</v>
       </c>
       <c r="M53">
-        <v>196.0023891</v>
+        <v>199.8455732</v>
       </c>
       <c r="N53">
-        <v>729.2226109000001</v>
+        <v>725.3794268</v>
       </c>
       <c r="O53">
-        <v>91.15282636250001</v>
+        <v>90.67242835</v>
       </c>
       <c r="P53">
-        <v>638.0697845375</v>
+        <v>634.70699845</v>
       </c>
       <c r="Q53">
-        <v>953.9697845375</v>
+        <v>950.60699845</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1099510182854329</v>
+        <v>0.1112000645916135</v>
       </c>
       <c r="T53">
-        <v>1.081678329031501</v>
+        <v>1.102739044160619</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5781,7 +5781,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>4.720478175028532</v>
+        <v>4.629699748585675</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5789,22 +5789,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07853753100397447</v>
+        <v>0.07852143804808681</v>
       </c>
       <c r="C54">
-        <v>4474.975681502408</v>
+        <v>4409.299075599683</v>
       </c>
       <c r="D54">
-        <v>7767.919681502409</v>
+        <v>7771.740075599683</v>
       </c>
       <c r="E54">
-        <v>-176.8559999999998</v>
+        <v>-107.3589999999999</v>
       </c>
       <c r="F54">
-        <v>3613.844</v>
+        <v>3683.340999999999</v>
       </c>
       <c r="G54">
         <v>320.9</v>
@@ -5825,28 +5825,28 @@
         <v>925.225</v>
       </c>
       <c r="M54">
-        <v>199.8455732</v>
+        <v>203.6887573</v>
       </c>
       <c r="N54">
-        <v>725.3794268</v>
+        <v>721.5362427</v>
       </c>
       <c r="O54">
-        <v>90.67242835</v>
+        <v>90.1920303375</v>
       </c>
       <c r="P54">
-        <v>634.70699845</v>
+        <v>631.3442123625</v>
       </c>
       <c r="Q54">
-        <v>950.60699845</v>
+        <v>947.2442123625</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1112000645916135</v>
+        <v>0.11250226180444</v>
       </c>
       <c r="T54">
-        <v>1.102739044160619</v>
+        <v>1.124695959933529</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5863,7 +5863,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>4.629699748585675</v>
+        <v>4.542346923140663</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5871,22 +5871,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07852143804808681</v>
+        <v>0.07968659509219914</v>
       </c>
       <c r="C55">
-        <v>4409.299075599683</v>
+        <v>4072.578482628563</v>
       </c>
       <c r="D55">
-        <v>7771.740075599683</v>
+        <v>7504.516482628563</v>
       </c>
       <c r="E55">
-        <v>-107.3589999999999</v>
+        <v>-37.86199999999963</v>
       </c>
       <c r="F55">
-        <v>3683.340999999999</v>
+        <v>3752.838</v>
       </c>
       <c r="G55">
         <v>320.9</v>
@@ -5907,45 +5907,45 @@
         <v>925.225</v>
       </c>
       <c r="M55">
-        <v>203.6887573</v>
+        <v>216.9140364</v>
       </c>
       <c r="N55">
-        <v>721.5362427</v>
+        <v>708.3109636</v>
       </c>
       <c r="O55">
-        <v>90.1920303375</v>
+        <v>88.53887045</v>
       </c>
       <c r="P55">
-        <v>631.3442123625</v>
+        <v>619.77209315</v>
       </c>
       <c r="Q55">
-        <v>947.2442123625</v>
+        <v>935.67209315</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.11250226180444</v>
+        <v>0.1138610762873895</v>
       </c>
       <c r="T55">
-        <v>1.124695959933529</v>
+        <v>1.147607524218305</v>
       </c>
       <c r="U55">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V55">
         <v>0.125</v>
       </c>
       <c r="W55">
-        <v>0.0483875</v>
+        <v>0.050575</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y55">
-        <v>4.542346923140663</v>
+        <v>4.265399396716957</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5953,22 +5953,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07968659509219914</v>
+        <v>0.07969237713631147</v>
       </c>
       <c r="C56">
-        <v>4072.578482628563</v>
+        <v>4001.80121110409</v>
       </c>
       <c r="D56">
-        <v>7504.516482628563</v>
+        <v>7503.23621110409</v>
       </c>
       <c r="E56">
-        <v>-37.86199999999963</v>
+        <v>31.63500000000022</v>
       </c>
       <c r="F56">
-        <v>3752.838</v>
+        <v>3822.335</v>
       </c>
       <c r="G56">
         <v>320.9</v>
@@ -5989,28 +5989,28 @@
         <v>925.225</v>
       </c>
       <c r="M56">
-        <v>216.9140364</v>
+        <v>220.930963</v>
       </c>
       <c r="N56">
-        <v>708.3109636</v>
+        <v>704.294037</v>
       </c>
       <c r="O56">
-        <v>88.53887045</v>
+        <v>88.036754625</v>
       </c>
       <c r="P56">
-        <v>619.77209315</v>
+        <v>616.257282375</v>
       </c>
       <c r="Q56">
-        <v>935.67209315</v>
+        <v>932.157282375</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1138610762873895</v>
+        <v>0.1152802825251366</v>
       </c>
       <c r="T56">
-        <v>1.147607524218305</v>
+        <v>1.171537380249071</v>
       </c>
       <c r="U56">
         <v>0.0578</v>
@@ -6027,7 +6027,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>4.265399396716957</v>
+        <v>4.187846680413012</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6035,22 +6035,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07969237713631147</v>
+        <v>0.07969815918042381</v>
       </c>
       <c r="C57">
-        <v>4001.80121110409</v>
+        <v>3931.024376334095</v>
       </c>
       <c r="D57">
-        <v>7503.23621110409</v>
+        <v>7501.956376334096</v>
       </c>
       <c r="E57">
-        <v>31.63500000000022</v>
+        <v>101.1320000000005</v>
       </c>
       <c r="F57">
-        <v>3822.335</v>
+        <v>3891.832</v>
       </c>
       <c r="G57">
         <v>320.9</v>
@@ -6071,28 +6071,28 @@
         <v>925.225</v>
       </c>
       <c r="M57">
-        <v>220.930963</v>
+        <v>224.9478896</v>
       </c>
       <c r="N57">
-        <v>704.294037</v>
+        <v>700.2771104000001</v>
       </c>
       <c r="O57">
-        <v>88.036754625</v>
+        <v>87.53463880000001</v>
       </c>
       <c r="P57">
-        <v>616.257282375</v>
+        <v>612.7424716</v>
       </c>
       <c r="Q57">
-        <v>932.157282375</v>
+        <v>928.6424716</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1152802825251366</v>
+        <v>0.1167639981373269</v>
       </c>
       <c r="T57">
-        <v>1.171537380249071</v>
+        <v>1.196554957008508</v>
       </c>
       <c r="U57">
         <v>0.0578</v>
@@ -6109,7 +6109,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>4.187846680413012</v>
+        <v>4.113063703977065</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6117,22 +6117,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07969815918042381</v>
+        <v>0.07970394122453613</v>
       </c>
       <c r="C58">
-        <v>3931.024376334095</v>
+        <v>3860.24797809513</v>
       </c>
       <c r="D58">
-        <v>7501.956376334096</v>
+        <v>7500.67697809513</v>
       </c>
       <c r="E58">
-        <v>101.1320000000005</v>
+        <v>170.6290000000004</v>
       </c>
       <c r="F58">
-        <v>3891.832</v>
+        <v>3961.329</v>
       </c>
       <c r="G58">
         <v>320.9</v>
@@ -6153,28 +6153,28 @@
         <v>925.225</v>
       </c>
       <c r="M58">
-        <v>224.9478896</v>
+        <v>228.9648162</v>
       </c>
       <c r="N58">
-        <v>700.2771104000001</v>
+        <v>696.2601838</v>
       </c>
       <c r="O58">
-        <v>87.53463880000001</v>
+        <v>87.03252297500001</v>
       </c>
       <c r="P58">
-        <v>612.7424716</v>
+        <v>609.227660825</v>
       </c>
       <c r="Q58">
-        <v>928.6424716</v>
+        <v>925.127660825</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1167639981373269</v>
+        <v>0.118316723777991</v>
       </c>
       <c r="T58">
-        <v>1.196554957008508</v>
+        <v>1.222736141989314</v>
       </c>
       <c r="U58">
         <v>0.0578</v>
@@ -6191,7 +6191,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>4.113063703977065</v>
+        <v>4.040904691626591</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6199,22 +6199,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07970394122453613</v>
+        <v>0.08148597326864848</v>
       </c>
       <c r="C59">
-        <v>3860.24797809513</v>
+        <v>3416.193539886088</v>
       </c>
       <c r="D59">
-        <v>7500.67697809513</v>
+        <v>7126.119539886088</v>
       </c>
       <c r="E59">
-        <v>170.6290000000004</v>
+        <v>240.1260000000007</v>
       </c>
       <c r="F59">
-        <v>3961.329</v>
+        <v>4030.826</v>
       </c>
       <c r="G59">
         <v>320.9</v>
@@ -6235,45 +6235,45 @@
         <v>925.225</v>
       </c>
       <c r="M59">
-        <v>228.9648162</v>
+        <v>247.0896338</v>
       </c>
       <c r="N59">
-        <v>696.2601838</v>
+        <v>678.1353662</v>
       </c>
       <c r="O59">
-        <v>87.03252297500001</v>
+        <v>84.766920775</v>
       </c>
       <c r="P59">
-        <v>609.227660825</v>
+        <v>593.368445425</v>
       </c>
       <c r="Q59">
-        <v>925.127660825</v>
+        <v>909.268445425</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.118316723777991</v>
+        <v>0.1199433887348773</v>
       </c>
       <c r="T59">
-        <v>1.222736141989314</v>
+        <v>1.250164050064445</v>
       </c>
       <c r="U59">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V59">
         <v>0.125</v>
       </c>
       <c r="W59">
-        <v>0.050575</v>
+        <v>0.0536375</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y59">
-        <v>4.040904691626591</v>
+        <v>3.744491364412715</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6281,22 +6281,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08148597326864847</v>
+        <v>0.08152238031276079</v>
       </c>
       <c r="C60">
-        <v>3416.193539886091</v>
+        <v>3339.433839411854</v>
       </c>
       <c r="D60">
-        <v>7126.119539886091</v>
+        <v>7118.856839411854</v>
       </c>
       <c r="E60">
-        <v>240.1259999999997</v>
+        <v>309.623</v>
       </c>
       <c r="F60">
-        <v>4030.825999999999</v>
+        <v>4100.322999999999</v>
       </c>
       <c r="G60">
         <v>320.9</v>
@@ -6317,28 +6317,28 @@
         <v>925.225</v>
       </c>
       <c r="M60">
-        <v>247.0896337999999</v>
+        <v>251.3497999</v>
       </c>
       <c r="N60">
-        <v>678.1353662000001</v>
+        <v>673.8752001</v>
       </c>
       <c r="O60">
-        <v>84.76692077500002</v>
+        <v>84.2344000125</v>
       </c>
       <c r="P60">
-        <v>593.3684454250001</v>
+        <v>589.6408000875</v>
       </c>
       <c r="Q60">
-        <v>909.2684454250001</v>
+        <v>905.5408000875</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1199433887348773</v>
+        <v>0.1216494032018556</v>
       </c>
       <c r="T60">
-        <v>1.250164050064444</v>
+        <v>1.278929904874947</v>
       </c>
       <c r="U60">
         <v>0.0613</v>
@@ -6355,7 +6355,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.744491364412716</v>
+        <v>3.681025409083686</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6363,22 +6363,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08152238031276079</v>
+        <v>0.08155878735687314</v>
       </c>
       <c r="C61">
-        <v>3339.433839411854</v>
+        <v>3262.688927663749</v>
       </c>
       <c r="D61">
-        <v>7118.856839411854</v>
+        <v>7111.608927663749</v>
       </c>
       <c r="E61">
-        <v>309.623</v>
+        <v>379.1199999999994</v>
       </c>
       <c r="F61">
-        <v>4100.322999999999</v>
+        <v>4169.819999999999</v>
       </c>
       <c r="G61">
         <v>320.9</v>
@@ -6399,28 +6399,28 @@
         <v>925.225</v>
       </c>
       <c r="M61">
-        <v>251.3497999</v>
+        <v>255.6099659999999</v>
       </c>
       <c r="N61">
-        <v>673.8752001</v>
+        <v>669.6150340000002</v>
       </c>
       <c r="O61">
-        <v>84.2344000125</v>
+        <v>83.70187925000002</v>
       </c>
       <c r="P61">
-        <v>589.6408000875</v>
+        <v>585.9131547500001</v>
       </c>
       <c r="Q61">
-        <v>905.5408000875</v>
+        <v>901.8131547500001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1216494032018556</v>
+        <v>0.1234407183921828</v>
       </c>
       <c r="T61">
-        <v>1.278929904874947</v>
+        <v>1.309134052425975</v>
       </c>
       <c r="U61">
         <v>0.0613</v>
@@ -6437,7 +6437,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.681025409083686</v>
+        <v>3.619674985598959</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6445,22 +6445,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08155878735687314</v>
+        <v>0.08159519440098548</v>
       </c>
       <c r="C62">
-        <v>3262.688927663749</v>
+        <v>3185.958759517242</v>
       </c>
       <c r="D62">
-        <v>7111.608927663749</v>
+        <v>7104.375759517242</v>
       </c>
       <c r="E62">
-        <v>379.1199999999994</v>
+        <v>448.6169999999997</v>
       </c>
       <c r="F62">
-        <v>4169.819999999999</v>
+        <v>4239.316999999999</v>
       </c>
       <c r="G62">
         <v>320.9</v>
@@ -6481,28 +6481,28 @@
         <v>925.225</v>
       </c>
       <c r="M62">
-        <v>255.6099659999999</v>
+        <v>259.8701320999999</v>
       </c>
       <c r="N62">
-        <v>669.6150340000002</v>
+        <v>665.3548679</v>
       </c>
       <c r="O62">
-        <v>83.70187925000002</v>
+        <v>83.16935848750001</v>
       </c>
       <c r="P62">
-        <v>585.9131547500001</v>
+        <v>582.1855094125001</v>
       </c>
       <c r="Q62">
-        <v>901.8131547500001</v>
+        <v>898.0855094125001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1234407183921828</v>
+        <v>0.1253238958999628</v>
       </c>
       <c r="T62">
-        <v>1.309134052425975</v>
+        <v>1.340887130620645</v>
       </c>
       <c r="U62">
         <v>0.0613</v>
@@ -6519,7 +6519,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.619674985598959</v>
+        <v>3.560336051408811</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08159519440098548</v>
+        <v>0.08163160144509779</v>
       </c>
       <c r="C63">
-        <v>3185.958759517242</v>
+        <v>3109.243290031209</v>
       </c>
       <c r="D63">
-        <v>7104.375759517242</v>
+        <v>7097.157290031209</v>
       </c>
       <c r="E63">
-        <v>448.6169999999997</v>
+        <v>518.114</v>
       </c>
       <c r="F63">
-        <v>4239.316999999999</v>
+        <v>4308.813999999999</v>
       </c>
       <c r="G63">
         <v>320.9</v>
@@ -6563,28 +6563,28 @@
         <v>925.225</v>
       </c>
       <c r="M63">
-        <v>259.8701320999999</v>
+        <v>264.1302982</v>
       </c>
       <c r="N63">
-        <v>665.3548679</v>
+        <v>661.0947018000001</v>
       </c>
       <c r="O63">
-        <v>83.16935848750001</v>
+        <v>82.63683772500001</v>
       </c>
       <c r="P63">
-        <v>582.1855094125001</v>
+        <v>578.4578640750001</v>
       </c>
       <c r="Q63">
-        <v>898.0855094125001</v>
+        <v>894.3578640750001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1253238958999628</v>
+        <v>0.1273061880134153</v>
       </c>
       <c r="T63">
-        <v>1.340887130620645</v>
+        <v>1.37431142345714</v>
       </c>
       <c r="U63">
         <v>0.0613</v>
@@ -6601,7 +6601,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.560336051408811</v>
+        <v>3.502911276386088</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6609,22 +6609,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08163160144509779</v>
+        <v>0.08321150848921015</v>
       </c>
       <c r="C64">
-        <v>3109.243290031209</v>
+        <v>2740.029725570099</v>
       </c>
       <c r="D64">
-        <v>7097.157290031209</v>
+        <v>6797.440725570099</v>
       </c>
       <c r="E64">
-        <v>518.114</v>
+        <v>587.6110000000003</v>
       </c>
       <c r="F64">
-        <v>4308.813999999999</v>
+        <v>4378.311</v>
       </c>
       <c r="G64">
         <v>320.9</v>
@@ -6645,45 +6645,45 @@
         <v>925.225</v>
       </c>
       <c r="M64">
-        <v>264.1302982</v>
+        <v>280.6497351</v>
       </c>
       <c r="N64">
-        <v>661.0947018000001</v>
+        <v>644.5752649000001</v>
       </c>
       <c r="O64">
-        <v>82.63683772500001</v>
+        <v>80.57190811250001</v>
       </c>
       <c r="P64">
-        <v>578.4578640750001</v>
+        <v>564.0033567875</v>
       </c>
       <c r="Q64">
-        <v>894.3578640750001</v>
+        <v>879.9033567875</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1273061880134153</v>
+        <v>0.1293956310519193</v>
       </c>
       <c r="T64">
-        <v>1.37431142345714</v>
+        <v>1.409542434825338</v>
       </c>
       <c r="U64">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V64">
         <v>0.125</v>
       </c>
       <c r="W64">
-        <v>0.0536375</v>
+        <v>0.05608750000000001</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y64">
-        <v>3.502911276386088</v>
+        <v>3.296725007313218</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6691,22 +6691,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08321150848921015</v>
+        <v>0.08327241553332247</v>
       </c>
       <c r="C65">
-        <v>2740.029725570099</v>
+        <v>2659.484277899171</v>
       </c>
       <c r="D65">
-        <v>6797.440725570099</v>
+        <v>6786.39227789917</v>
       </c>
       <c r="E65">
-        <v>587.6110000000003</v>
+        <v>657.1079999999997</v>
       </c>
       <c r="F65">
-        <v>4378.311</v>
+        <v>4447.807999999999</v>
       </c>
       <c r="G65">
         <v>320.9</v>
@@ -6727,28 +6727,28 @@
         <v>925.225</v>
       </c>
       <c r="M65">
-        <v>280.6497351</v>
+        <v>285.1044927999999</v>
       </c>
       <c r="N65">
-        <v>644.5752649000001</v>
+        <v>640.1205072</v>
       </c>
       <c r="O65">
-        <v>80.57190811250001</v>
+        <v>80.0150634</v>
       </c>
       <c r="P65">
-        <v>564.0033567875</v>
+        <v>560.1054438</v>
       </c>
       <c r="Q65">
-        <v>879.9033567875</v>
+        <v>876.0054438</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1293956310519193</v>
+        <v>0.1316011542592291</v>
       </c>
       <c r="T65">
-        <v>1.409542434825338</v>
+        <v>1.446730724602879</v>
       </c>
       <c r="U65">
         <v>0.0641</v>
@@ -6765,7 +6765,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.296725007313218</v>
+        <v>3.245213679073949</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6773,22 +6773,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08327241553332247</v>
+        <v>0.08333332257743481</v>
       </c>
       <c r="C66">
-        <v>2659.484277899171</v>
+        <v>2578.974687873844</v>
       </c>
       <c r="D66">
-        <v>6786.39227789917</v>
+        <v>6775.379687873844</v>
       </c>
       <c r="E66">
-        <v>657.1079999999997</v>
+        <v>726.605</v>
       </c>
       <c r="F66">
-        <v>4447.807999999999</v>
+        <v>4517.304999999999</v>
       </c>
       <c r="G66">
         <v>320.9</v>
@@ -6809,28 +6809,28 @@
         <v>925.225</v>
       </c>
       <c r="M66">
-        <v>285.1044927999999</v>
+        <v>289.5592505</v>
       </c>
       <c r="N66">
-        <v>640.1205072</v>
+        <v>635.6657495000001</v>
       </c>
       <c r="O66">
-        <v>80.0150634</v>
+        <v>79.45821868750001</v>
       </c>
       <c r="P66">
-        <v>560.1054438</v>
+        <v>556.2075308125001</v>
       </c>
       <c r="Q66">
-        <v>876.0054438</v>
+        <v>872.1075308125</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1316011542592291</v>
+        <v>0.1339327073640995</v>
       </c>
       <c r="T66">
-        <v>1.446730724602879</v>
+        <v>1.486044059510566</v>
       </c>
       <c r="U66">
         <v>0.0641</v>
@@ -6847,7 +6847,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>3.245213679073949</v>
+        <v>3.195287314780503</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6855,22 +6855,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08333332257743481</v>
+        <v>0.08339422962154713</v>
       </c>
       <c r="C67">
-        <v>2578.974687873844</v>
+        <v>2498.500781213397</v>
       </c>
       <c r="D67">
-        <v>6775.379687873844</v>
+        <v>6764.402781213397</v>
       </c>
       <c r="E67">
-        <v>726.605</v>
+        <v>796.1020000000003</v>
       </c>
       <c r="F67">
-        <v>4517.304999999999</v>
+        <v>4586.802</v>
       </c>
       <c r="G67">
         <v>320.9</v>
@@ -6891,28 +6891,28 @@
         <v>925.225</v>
       </c>
       <c r="M67">
-        <v>289.5592505</v>
+        <v>294.0140082</v>
       </c>
       <c r="N67">
-        <v>635.6657495000001</v>
+        <v>631.2109918000001</v>
       </c>
       <c r="O67">
-        <v>79.45821868750001</v>
+        <v>78.90137397500001</v>
       </c>
       <c r="P67">
-        <v>556.2075308125001</v>
+        <v>552.309617825</v>
       </c>
       <c r="Q67">
-        <v>872.1075308125</v>
+        <v>868.209617825</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1339327073640995</v>
+        <v>0.1364014106516092</v>
       </c>
       <c r="T67">
-        <v>1.486044059510566</v>
+        <v>1.52766994353047</v>
       </c>
       <c r="U67">
         <v>0.0641</v>
@@ -6929,7 +6929,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.195287314780503</v>
+        <v>3.146873870617163</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6937,22 +6937,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08339422962154713</v>
+        <v>0.08345513666565949</v>
       </c>
       <c r="C68">
-        <v>2498.500781213397</v>
+        <v>2418.062384764695</v>
       </c>
       <c r="D68">
-        <v>6764.402781213397</v>
+        <v>6753.461384764695</v>
       </c>
       <c r="E68">
-        <v>796.1020000000003</v>
+        <v>865.5990000000006</v>
       </c>
       <c r="F68">
-        <v>4586.802</v>
+        <v>4656.299</v>
       </c>
       <c r="G68">
         <v>320.9</v>
@@ -6973,28 +6973,28 @@
         <v>925.225</v>
       </c>
       <c r="M68">
-        <v>294.0140082</v>
+        <v>298.4687659</v>
       </c>
       <c r="N68">
-        <v>631.2109918000001</v>
+        <v>626.7562341</v>
       </c>
       <c r="O68">
-        <v>78.90137397500001</v>
+        <v>78.3445292625</v>
       </c>
       <c r="P68">
-        <v>552.309617825</v>
+        <v>548.4117048375</v>
       </c>
       <c r="Q68">
-        <v>868.209617825</v>
+        <v>864.3117048375</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1364014106516092</v>
+        <v>0.1390197323201803</v>
       </c>
       <c r="T68">
-        <v>1.52766994353047</v>
+        <v>1.571818608400065</v>
       </c>
       <c r="U68">
         <v>0.0641</v>
@@ -7011,7 +7011,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>3.146873870617163</v>
+        <v>3.099905603891533</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7019,22 +7019,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08345513666565949</v>
+        <v>0.08351604370977181</v>
       </c>
       <c r="C69">
-        <v>2418.062384764695</v>
+        <v>2337.659326493103</v>
       </c>
       <c r="D69">
-        <v>6753.461384764695</v>
+        <v>6742.555326493102</v>
       </c>
       <c r="E69">
-        <v>865.5990000000006</v>
+        <v>935.096</v>
       </c>
       <c r="F69">
-        <v>4656.299</v>
+        <v>4725.795999999999</v>
       </c>
       <c r="G69">
         <v>320.9</v>
@@ -7055,28 +7055,28 @@
         <v>925.225</v>
       </c>
       <c r="M69">
-        <v>298.4687659</v>
+        <v>302.9235236</v>
       </c>
       <c r="N69">
-        <v>626.7562341</v>
+        <v>622.3014764000001</v>
       </c>
       <c r="O69">
-        <v>78.3445292625</v>
+        <v>77.78768455000001</v>
       </c>
       <c r="P69">
-        <v>548.4117048375</v>
+        <v>544.5137918500001</v>
       </c>
       <c r="Q69">
-        <v>864.3117048375</v>
+        <v>860.4137918500001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1390197323201803</v>
+        <v>0.1418016990930369</v>
       </c>
       <c r="T69">
-        <v>1.571818608400065</v>
+        <v>1.61872656482401</v>
       </c>
       <c r="U69">
         <v>0.0641</v>
@@ -7093,7 +7093,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>3.099905603891533</v>
+        <v>3.054318756775481</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7101,22 +7101,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08351604370977181</v>
+        <v>0.08357695075388415</v>
       </c>
       <c r="C70">
-        <v>2337.659326493103</v>
+        <v>2257.291435473439</v>
       </c>
       <c r="D70">
-        <v>6742.555326493102</v>
+        <v>6731.684435473439</v>
       </c>
       <c r="E70">
-        <v>935.096</v>
+        <v>1004.593</v>
       </c>
       <c r="F70">
-        <v>4725.795999999999</v>
+        <v>4795.293</v>
       </c>
       <c r="G70">
         <v>320.9</v>
@@ -7137,28 +7137,28 @@
         <v>925.225</v>
       </c>
       <c r="M70">
-        <v>302.9235236</v>
+        <v>307.3782813</v>
       </c>
       <c r="N70">
-        <v>622.3014764000001</v>
+        <v>617.8467187</v>
       </c>
       <c r="O70">
-        <v>77.78768455000001</v>
+        <v>77.2308398375</v>
       </c>
       <c r="P70">
-        <v>544.5137918500001</v>
+        <v>540.6158788625</v>
       </c>
       <c r="Q70">
-        <v>860.4137918500001</v>
+        <v>856.5158788625</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1418016990930369</v>
+        <v>0.1447631475931747</v>
       </c>
       <c r="T70">
-        <v>1.61872656482401</v>
+        <v>1.668660841017241</v>
       </c>
       <c r="U70">
         <v>0.0641</v>
@@ -7175,7 +7175,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.054318756775481</v>
+        <v>3.010053267546851</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7183,22 +7183,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08357695075388415</v>
+        <v>0.08841535779799647</v>
       </c>
       <c r="C71">
-        <v>2257.291435473439</v>
+        <v>1423.501207062079</v>
       </c>
       <c r="D71">
-        <v>6731.684435473439</v>
+        <v>5967.391207062079</v>
       </c>
       <c r="E71">
-        <v>1004.593</v>
+        <v>1074.090000000001</v>
       </c>
       <c r="F71">
-        <v>4795.293</v>
+        <v>4864.79</v>
       </c>
       <c r="G71">
         <v>320.9</v>
@@ -7219,45 +7219,45 @@
         <v>925.225</v>
       </c>
       <c r="M71">
-        <v>307.3782813</v>
+        <v>349.778401</v>
       </c>
       <c r="N71">
-        <v>617.8467187</v>
+        <v>575.446599</v>
       </c>
       <c r="O71">
-        <v>77.2308398375</v>
+        <v>71.930824875</v>
       </c>
       <c r="P71">
-        <v>540.6158788625</v>
+        <v>503.515774125</v>
       </c>
       <c r="Q71">
-        <v>856.5158788625</v>
+        <v>819.415774125</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1447631475931747</v>
+        <v>0.1479220259933216</v>
       </c>
       <c r="T71">
-        <v>1.668660841017241</v>
+        <v>1.721924068956688</v>
       </c>
       <c r="U71">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V71">
         <v>0.125</v>
       </c>
       <c r="W71">
-        <v>0.05608750000000001</v>
+        <v>0.06291250000000001</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y71">
-        <v>3.010053267546851</v>
+        <v>2.645174765951314</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7265,22 +7265,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08841535779799647</v>
+        <v>0.08854451484210882</v>
       </c>
       <c r="C72">
-        <v>1423.501207062079</v>
+        <v>1335.973107347576</v>
       </c>
       <c r="D72">
-        <v>5967.391207062079</v>
+        <v>5949.360107347576</v>
       </c>
       <c r="E72">
-        <v>1074.090000000001</v>
+        <v>1143.587</v>
       </c>
       <c r="F72">
-        <v>4864.79</v>
+        <v>4934.286999999999</v>
       </c>
       <c r="G72">
         <v>320.9</v>
@@ -7301,28 +7301,28 @@
         <v>925.225</v>
       </c>
       <c r="M72">
-        <v>349.778401</v>
+        <v>354.7752353</v>
       </c>
       <c r="N72">
-        <v>575.446599</v>
+        <v>570.4497647000001</v>
       </c>
       <c r="O72">
-        <v>71.930824875</v>
+        <v>71.30622058750001</v>
       </c>
       <c r="P72">
-        <v>503.515774125</v>
+        <v>499.1435441125001</v>
       </c>
       <c r="Q72">
-        <v>819.415774125</v>
+        <v>815.0435441125001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1479220259933216</v>
+        <v>0.1512987580762373</v>
       </c>
       <c r="T72">
-        <v>1.721924068956688</v>
+        <v>1.778860622960925</v>
       </c>
       <c r="U72">
         <v>0.07190000000000001</v>
@@ -7339,7 +7339,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.645174765951314</v>
+        <v>2.607918783332282</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7347,22 +7347,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08854451484210882</v>
+        <v>0.08867367188622115</v>
       </c>
       <c r="C73">
-        <v>1335.973107347576</v>
+        <v>1248.553645099322</v>
       </c>
       <c r="D73">
-        <v>5949.360107347576</v>
+        <v>5931.437645099321</v>
       </c>
       <c r="E73">
-        <v>1143.587</v>
+        <v>1213.083999999999</v>
       </c>
       <c r="F73">
-        <v>4934.286999999999</v>
+        <v>5003.783999999999</v>
       </c>
       <c r="G73">
         <v>320.9</v>
@@ -7383,28 +7383,28 @@
         <v>925.225</v>
       </c>
       <c r="M73">
-        <v>354.7752353</v>
+        <v>359.7720696</v>
       </c>
       <c r="N73">
-        <v>570.4497647000001</v>
+        <v>565.4529304</v>
       </c>
       <c r="O73">
-        <v>71.30622058750001</v>
+        <v>70.6816163</v>
       </c>
       <c r="P73">
-        <v>499.1435441125001</v>
+        <v>494.7713141</v>
       </c>
       <c r="Q73">
-        <v>815.0435441125001</v>
+        <v>810.6713141</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1512987580762373</v>
+        <v>0.1549166853079327</v>
       </c>
       <c r="T73">
-        <v>1.778860622960924</v>
+        <v>1.839864073679749</v>
       </c>
       <c r="U73">
         <v>0.07190000000000001</v>
@@ -7421,7 +7421,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.607918783332282</v>
+        <v>2.571697689119333</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7429,22 +7429,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08867367188622115</v>
+        <v>0.08880282893033348</v>
       </c>
       <c r="C74">
-        <v>1248.553645099322</v>
+        <v>1161.241841454224</v>
       </c>
       <c r="D74">
-        <v>5931.437645099321</v>
+        <v>5913.622841454224</v>
       </c>
       <c r="E74">
-        <v>1213.083999999999</v>
+        <v>1282.581</v>
       </c>
       <c r="F74">
-        <v>5003.783999999999</v>
+        <v>5073.280999999999</v>
       </c>
       <c r="G74">
         <v>320.9</v>
@@ -7465,28 +7465,28 @@
         <v>925.225</v>
       </c>
       <c r="M74">
-        <v>359.7720696</v>
+        <v>364.7689038999999</v>
       </c>
       <c r="N74">
-        <v>565.4529304</v>
+        <v>560.4560961000001</v>
       </c>
       <c r="O74">
-        <v>70.6816163</v>
+        <v>70.05701201250001</v>
       </c>
       <c r="P74">
-        <v>494.7713141</v>
+        <v>490.3990840875001</v>
       </c>
       <c r="Q74">
-        <v>810.6713141</v>
+        <v>806.2990840875</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1549166853079327</v>
+        <v>0.1588026071493832</v>
       </c>
       <c r="T74">
-        <v>1.839864073679749</v>
+        <v>1.905386298525894</v>
       </c>
       <c r="U74">
         <v>0.07190000000000001</v>
@@ -7503,7 +7503,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.571697689119333</v>
+        <v>2.536468953651946</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7511,22 +7511,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08880282893033348</v>
+        <v>0.08893198597444582</v>
       </c>
       <c r="C75">
-        <v>1161.241841454224</v>
+        <v>1074.036729273858</v>
       </c>
       <c r="D75">
-        <v>5913.622841454224</v>
+        <v>5895.914729273858</v>
       </c>
       <c r="E75">
-        <v>1282.581</v>
+        <v>1352.078</v>
       </c>
       <c r="F75">
-        <v>5073.280999999999</v>
+        <v>5142.777999999999</v>
       </c>
       <c r="G75">
         <v>320.9</v>
@@ -7547,28 +7547,28 @@
         <v>925.225</v>
       </c>
       <c r="M75">
-        <v>364.7689038999999</v>
+        <v>369.7657382</v>
       </c>
       <c r="N75">
-        <v>560.4560961000001</v>
+        <v>555.4592618</v>
       </c>
       <c r="O75">
-        <v>70.05701201250001</v>
+        <v>69.432407725</v>
       </c>
       <c r="P75">
-        <v>490.3990840875001</v>
+        <v>486.026854075</v>
       </c>
       <c r="Q75">
-        <v>806.2990840875</v>
+        <v>801.9268540749999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1588026071493832</v>
+        <v>0.1629874460555608</v>
       </c>
       <c r="T75">
-        <v>1.905386298525894</v>
+        <v>1.975948694514049</v>
       </c>
       <c r="U75">
         <v>0.07190000000000001</v>
@@ -7585,7 +7585,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.536468953651946</v>
+        <v>2.502192346170163</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7593,22 +7593,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.08893198597444582</v>
+        <v>0.09162051801855814</v>
       </c>
       <c r="C76">
-        <v>1074.036729273858</v>
+        <v>658.595240549691</v>
       </c>
       <c r="D76">
-        <v>5895.914729273858</v>
+        <v>5549.970240549691</v>
       </c>
       <c r="E76">
-        <v>1352.078</v>
+        <v>1421.575</v>
       </c>
       <c r="F76">
-        <v>5142.777999999999</v>
+        <v>5212.275</v>
       </c>
       <c r="G76">
         <v>320.9</v>
@@ -7629,45 +7629,45 @@
         <v>925.225</v>
       </c>
       <c r="M76">
-        <v>369.7657382</v>
+        <v>395.090445</v>
       </c>
       <c r="N76">
-        <v>555.4592618</v>
+        <v>530.1345550000001</v>
       </c>
       <c r="O76">
-        <v>69.432407725</v>
+        <v>66.26681937500001</v>
       </c>
       <c r="P76">
-        <v>486.026854075</v>
+        <v>463.8677356250001</v>
       </c>
       <c r="Q76">
-        <v>801.9268540749999</v>
+        <v>779.7677356250001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1629874460555608</v>
+        <v>0.1675070720742326</v>
       </c>
       <c r="T76">
-        <v>1.975948694514049</v>
+        <v>2.052156082181258</v>
       </c>
       <c r="U76">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V76">
         <v>0.125</v>
       </c>
       <c r="W76">
-        <v>0.06291250000000001</v>
+        <v>0.06632500000000001</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y76">
-        <v>2.502192346170163</v>
+        <v>2.341805557965341</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7675,22 +7675,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.09162051801855814</v>
+        <v>0.09178380006267048</v>
       </c>
       <c r="C77">
-        <v>658.595240549691</v>
+        <v>569.391072277288</v>
       </c>
       <c r="D77">
-        <v>5549.970240549691</v>
+        <v>5530.263072277287</v>
       </c>
       <c r="E77">
-        <v>1421.575</v>
+        <v>1491.072</v>
       </c>
       <c r="F77">
-        <v>5212.275</v>
+        <v>5281.771999999999</v>
       </c>
       <c r="G77">
         <v>320.9</v>
@@ -7711,28 +7711,28 @@
         <v>925.225</v>
       </c>
       <c r="M77">
-        <v>395.090445</v>
+        <v>400.3583176</v>
       </c>
       <c r="N77">
-        <v>530.1345550000001</v>
+        <v>524.8666824000001</v>
       </c>
       <c r="O77">
-        <v>66.26681937500001</v>
+        <v>65.60833530000001</v>
       </c>
       <c r="P77">
-        <v>463.8677356250001</v>
+        <v>459.2583471</v>
       </c>
       <c r="Q77">
-        <v>779.7677356250001</v>
+        <v>775.1583471</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1675070720742326</v>
+        <v>0.1724033335944603</v>
       </c>
       <c r="T77">
-        <v>2.052156082181258</v>
+        <v>2.134714085487401</v>
       </c>
       <c r="U77">
         <v>0.07580000000000001</v>
@@ -7749,7 +7749,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.341805557965341</v>
+        <v>2.310992326939482</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7757,22 +7757,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.09178380006267048</v>
+        <v>0.09194708210678282</v>
       </c>
       <c r="C78">
-        <v>569.391072277288</v>
+        <v>480.3263636011261</v>
       </c>
       <c r="D78">
-        <v>5530.263072277287</v>
+        <v>5510.695363601126</v>
       </c>
       <c r="E78">
-        <v>1491.072</v>
+        <v>1560.569</v>
       </c>
       <c r="F78">
-        <v>5281.771999999999</v>
+        <v>5351.268999999999</v>
       </c>
       <c r="G78">
         <v>320.9</v>
@@ -7793,28 +7793,28 @@
         <v>925.225</v>
       </c>
       <c r="M78">
-        <v>400.3583176</v>
+        <v>405.6261902</v>
       </c>
       <c r="N78">
-        <v>524.8666824000001</v>
+        <v>519.5988098</v>
       </c>
       <c r="O78">
-        <v>65.60833530000001</v>
+        <v>64.949851225</v>
       </c>
       <c r="P78">
-        <v>459.2583471</v>
+        <v>454.6489585750001</v>
       </c>
       <c r="Q78">
-        <v>775.1583471</v>
+        <v>770.548958575</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1724033335944603</v>
+        <v>0.1777253569860122</v>
       </c>
       <c r="T78">
-        <v>2.134714085487401</v>
+        <v>2.224451045602773</v>
       </c>
       <c r="U78">
         <v>0.07580000000000001</v>
@@ -7831,7 +7831,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.310992326939482</v>
+        <v>2.280979439576631</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7839,22 +7839,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.09194708210678282</v>
+        <v>0.09211036415089516</v>
       </c>
       <c r="C79">
-        <v>480.3263636011261</v>
+        <v>391.3996393925809</v>
       </c>
       <c r="D79">
-        <v>5510.695363601126</v>
+        <v>5491.265639392581</v>
       </c>
       <c r="E79">
-        <v>1560.569</v>
+        <v>1630.066</v>
       </c>
       <c r="F79">
-        <v>5351.268999999999</v>
+        <v>5420.766</v>
       </c>
       <c r="G79">
         <v>320.9</v>
@@ -7875,28 +7875,28 @@
         <v>925.225</v>
       </c>
       <c r="M79">
-        <v>405.6261902</v>
+        <v>410.8940628</v>
       </c>
       <c r="N79">
-        <v>519.5988098</v>
+        <v>514.3309372</v>
       </c>
       <c r="O79">
-        <v>64.949851225</v>
+        <v>64.29136715</v>
       </c>
       <c r="P79">
-        <v>454.6489585750001</v>
+        <v>450.03957005</v>
       </c>
       <c r="Q79">
-        <v>770.548958575</v>
+        <v>765.9395700499999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1777253569860122</v>
+        <v>0.183531200685887</v>
       </c>
       <c r="T79">
-        <v>2.224451045602773</v>
+        <v>2.322345911183179</v>
       </c>
       <c r="U79">
         <v>0.07580000000000001</v>
@@ -7913,7 +7913,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.280979439576631</v>
+        <v>2.251736113428213</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7921,22 +7921,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.09211036415089516</v>
+        <v>0.0922736461950075</v>
       </c>
       <c r="C80">
-        <v>391.3996393925809</v>
+        <v>302.6094452540892</v>
       </c>
       <c r="D80">
-        <v>5491.265639392581</v>
+        <v>5471.972445254089</v>
       </c>
       <c r="E80">
-        <v>1630.066</v>
+        <v>1699.563</v>
       </c>
       <c r="F80">
-        <v>5420.766</v>
+        <v>5490.262999999999</v>
       </c>
       <c r="G80">
         <v>320.9</v>
@@ -7957,28 +7957,28 @@
         <v>925.225</v>
       </c>
       <c r="M80">
-        <v>410.8940628</v>
+        <v>416.1619353999999</v>
       </c>
       <c r="N80">
-        <v>514.3309372</v>
+        <v>509.0630646000001</v>
       </c>
       <c r="O80">
-        <v>64.29136715</v>
+        <v>63.63288307500001</v>
       </c>
       <c r="P80">
-        <v>450.03957005</v>
+        <v>445.4301815250001</v>
       </c>
       <c r="Q80">
-        <v>765.9395700499999</v>
+        <v>761.3301815250001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.183531200685887</v>
+        <v>0.189889981880988</v>
       </c>
       <c r="T80">
-        <v>2.322345911183179</v>
+        <v>2.429564097295053</v>
       </c>
       <c r="U80">
         <v>0.07580000000000001</v>
@@ -7995,7 +7995,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.251736113428213</v>
+        <v>2.223233124650641</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8003,22 +8003,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.0922736461950075</v>
+        <v>0.09243692823911982</v>
       </c>
       <c r="C81">
-        <v>302.6094452540892</v>
+        <v>213.9543471562401</v>
       </c>
       <c r="D81">
-        <v>5471.972445254089</v>
+        <v>5452.81434715624</v>
       </c>
       <c r="E81">
-        <v>1699.563</v>
+        <v>1769.06</v>
       </c>
       <c r="F81">
-        <v>5490.262999999999</v>
+        <v>5559.759999999999</v>
       </c>
       <c r="G81">
         <v>320.9</v>
@@ -8039,28 +8039,28 @@
         <v>925.225</v>
       </c>
       <c r="M81">
-        <v>416.1619353999999</v>
+        <v>421.429808</v>
       </c>
       <c r="N81">
-        <v>509.0630646000001</v>
+        <v>503.795192</v>
       </c>
       <c r="O81">
-        <v>63.63288307500001</v>
+        <v>62.97439900000001</v>
       </c>
       <c r="P81">
-        <v>445.4301815250001</v>
+        <v>440.820793</v>
       </c>
       <c r="Q81">
-        <v>761.3301815250001</v>
+        <v>756.720793</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.189889981880988</v>
+        <v>0.1968846411955991</v>
       </c>
       <c r="T81">
-        <v>2.429564097295053</v>
+        <v>2.547504102018114</v>
       </c>
       <c r="U81">
         <v>0.07580000000000001</v>
@@ -8077,7 +8077,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.223233124650641</v>
+        <v>2.195442710592507</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8085,22 +8085,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.09243692823911982</v>
+        <v>0.09260021028323215</v>
       </c>
       <c r="C82">
-        <v>213.9543471562401</v>
+        <v>125.4329310824578</v>
       </c>
       <c r="D82">
-        <v>5452.81434715624</v>
+        <v>5433.789931082458</v>
       </c>
       <c r="E82">
-        <v>1769.06</v>
+        <v>1838.557</v>
       </c>
       <c r="F82">
-        <v>5559.759999999999</v>
+        <v>5629.257</v>
       </c>
       <c r="G82">
         <v>320.9</v>
@@ -8121,28 +8121,28 @@
         <v>925.225</v>
       </c>
       <c r="M82">
-        <v>421.429808</v>
+        <v>426.6976806</v>
       </c>
       <c r="N82">
-        <v>503.795192</v>
+        <v>498.5273194</v>
       </c>
       <c r="O82">
-        <v>62.97439900000001</v>
+        <v>62.315914925</v>
       </c>
       <c r="P82">
-        <v>440.820793</v>
+        <v>436.211404475</v>
       </c>
       <c r="Q82">
-        <v>756.720793</v>
+        <v>752.111404475</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1968846411955991</v>
+        <v>0.204615580438064</v>
       </c>
       <c r="T82">
-        <v>2.547504102018114</v>
+        <v>2.677858844080445</v>
       </c>
       <c r="U82">
         <v>0.07580000000000001</v>
@@ -8159,7 +8159,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.195442710592507</v>
+        <v>2.168338479597538</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8167,22 +8167,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09260021028323215</v>
+        <v>0.09276349232734449</v>
       </c>
       <c r="C83">
-        <v>125.4329310824578</v>
+        <v>37.04380268110344</v>
       </c>
       <c r="D83">
-        <v>5433.789931082458</v>
+        <v>5414.897802681104</v>
       </c>
       <c r="E83">
-        <v>1838.557</v>
+        <v>1908.054000000001</v>
       </c>
       <c r="F83">
-        <v>5629.257</v>
+        <v>5698.754</v>
       </c>
       <c r="G83">
         <v>320.9</v>
@@ -8203,28 +8203,28 @@
         <v>925.225</v>
       </c>
       <c r="M83">
-        <v>426.6976806</v>
+        <v>431.9655532</v>
       </c>
       <c r="N83">
-        <v>498.5273194</v>
+        <v>493.2594468</v>
       </c>
       <c r="O83">
-        <v>62.315914925</v>
+        <v>61.65743085</v>
       </c>
       <c r="P83">
-        <v>436.211404475</v>
+        <v>431.60201595</v>
       </c>
       <c r="Q83">
-        <v>752.111404475</v>
+        <v>747.50201595</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.204615580438064</v>
+        <v>0.2132055129296916</v>
       </c>
       <c r="T83">
-        <v>2.677858844080445</v>
+        <v>2.822697446371923</v>
       </c>
       <c r="U83">
         <v>0.07580000000000001</v>
@@ -8241,7 +8241,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.168338479597538</v>
+        <v>2.141895327407324</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8249,22 +8249,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09276349232734449</v>
+        <v>0.09292677437145683</v>
       </c>
       <c r="C84">
-        <v>37.04380268110344</v>
+        <v>-51.21441307519126</v>
       </c>
       <c r="D84">
-        <v>5414.897802681104</v>
+        <v>5396.136586924808</v>
       </c>
       <c r="E84">
-        <v>1908.054000000001</v>
+        <v>1977.551</v>
       </c>
       <c r="F84">
-        <v>5698.754</v>
+        <v>5768.250999999999</v>
       </c>
       <c r="G84">
         <v>320.9</v>
@@ -8285,28 +8285,28 @@
         <v>925.225</v>
       </c>
       <c r="M84">
-        <v>431.9655532</v>
+        <v>437.2334258</v>
       </c>
       <c r="N84">
-        <v>493.2594468</v>
+        <v>487.9915742000001</v>
       </c>
       <c r="O84">
-        <v>61.65743085</v>
+        <v>60.99894677500001</v>
       </c>
       <c r="P84">
-        <v>431.60201595</v>
+        <v>426.992627425</v>
       </c>
       <c r="Q84">
-        <v>747.50201595</v>
+        <v>742.892627425</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2132055129296916</v>
+        <v>0.2228060257144519</v>
       </c>
       <c r="T84">
-        <v>2.822697446371923</v>
+        <v>2.984575884227105</v>
       </c>
       <c r="U84">
         <v>0.07580000000000001</v>
@@ -8323,7 +8323,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.141895327407324</v>
+        <v>2.116089359607236</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8331,22 +8331,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.09292677437145683</v>
+        <v>0.09309005641556917</v>
       </c>
       <c r="C85">
-        <v>-51.21441307519126</v>
+        <v>-139.3430722231478</v>
       </c>
       <c r="D85">
-        <v>5396.136586924808</v>
+        <v>5377.504927776852</v>
       </c>
       <c r="E85">
-        <v>1977.551</v>
+        <v>2047.048</v>
       </c>
       <c r="F85">
-        <v>5768.250999999999</v>
+        <v>5837.748</v>
       </c>
       <c r="G85">
         <v>320.9</v>
@@ -8367,28 +8367,28 @@
         <v>925.225</v>
       </c>
       <c r="M85">
-        <v>437.2334258</v>
+        <v>442.5012984</v>
       </c>
       <c r="N85">
-        <v>487.9915742000001</v>
+        <v>482.7237016</v>
       </c>
       <c r="O85">
-        <v>60.99894677500001</v>
+        <v>60.3404627</v>
       </c>
       <c r="P85">
-        <v>426.992627425</v>
+        <v>422.3832389</v>
       </c>
       <c r="Q85">
-        <v>742.892627425</v>
+        <v>738.2832389</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2228060257144519</v>
+        <v>0.2336066025973073</v>
       </c>
       <c r="T85">
-        <v>2.984575884227105</v>
+        <v>3.166689126814185</v>
       </c>
       <c r="U85">
         <v>0.07580000000000001</v>
@@ -8405,7 +8405,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.116089359607236</v>
+        <v>2.090897819611912</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8413,22 +8413,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.09309005641556915</v>
+        <v>0.09325333845968148</v>
       </c>
       <c r="C86">
-        <v>-139.3430722231451</v>
+        <v>-227.343512135546</v>
       </c>
       <c r="D86">
-        <v>5377.504927776854</v>
+        <v>5359.001487864453</v>
       </c>
       <c r="E86">
-        <v>2047.047999999999</v>
+        <v>2116.545</v>
       </c>
       <c r="F86">
-        <v>5837.747999999999</v>
+        <v>5907.244999999999</v>
       </c>
       <c r="G86">
         <v>320.9</v>
@@ -8449,28 +8449,28 @@
         <v>925.225</v>
       </c>
       <c r="M86">
-        <v>442.5012983999999</v>
+        <v>447.769171</v>
       </c>
       <c r="N86">
-        <v>482.7237016000001</v>
+        <v>477.4558290000001</v>
       </c>
       <c r="O86">
-        <v>60.34046270000001</v>
+        <v>59.68197862500001</v>
       </c>
       <c r="P86">
-        <v>422.3832389000001</v>
+        <v>417.7738503750001</v>
       </c>
       <c r="Q86">
-        <v>738.2832389</v>
+        <v>733.673850375</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2336066025973071</v>
+        <v>0.2458472563978765</v>
       </c>
       <c r="T86">
-        <v>3.166689126814183</v>
+        <v>3.373084135079539</v>
       </c>
       <c r="U86">
         <v>0.07580000000000001</v>
@@ -8487,7 +8487,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.090897819611913</v>
+        <v>2.066299021734125</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8495,22 +8495,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.09325333845968148</v>
+        <v>0.09341662050379382</v>
       </c>
       <c r="C87">
-        <v>-227.343512135546</v>
+        <v>-315.217051841254</v>
       </c>
       <c r="D87">
-        <v>5359.001487864453</v>
+        <v>5340.624948158746</v>
       </c>
       <c r="E87">
-        <v>2116.545</v>
+        <v>2186.042</v>
       </c>
       <c r="F87">
-        <v>5907.244999999999</v>
+        <v>5976.741999999999</v>
       </c>
       <c r="G87">
         <v>320.9</v>
@@ -8531,28 +8531,28 @@
         <v>925.225</v>
       </c>
       <c r="M87">
-        <v>447.769171</v>
+        <v>453.0370436</v>
       </c>
       <c r="N87">
-        <v>477.4558290000001</v>
+        <v>472.1879564</v>
       </c>
       <c r="O87">
-        <v>59.68197862500001</v>
+        <v>59.02349455</v>
       </c>
       <c r="P87">
-        <v>417.7738503750001</v>
+        <v>413.16446185</v>
       </c>
       <c r="Q87">
-        <v>733.673850375</v>
+        <v>729.06446185</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2458472563978765</v>
+        <v>0.2598365750270987</v>
       </c>
       <c r="T87">
-        <v>3.373084135079539</v>
+        <v>3.608964144525661</v>
       </c>
       <c r="U87">
         <v>0.07580000000000001</v>
@@ -8569,7 +8569,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.066299021734125</v>
+        <v>2.042272288923263</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8577,22 +8577,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.09341662050379382</v>
+        <v>0.09357990254790616</v>
       </c>
       <c r="C88">
-        <v>-315.217051841254</v>
+        <v>-402.9649923386378</v>
       </c>
       <c r="D88">
-        <v>5340.624948158746</v>
+        <v>5322.374007661361</v>
       </c>
       <c r="E88">
-        <v>2186.042</v>
+        <v>2255.538999999999</v>
       </c>
       <c r="F88">
-        <v>5976.741999999999</v>
+        <v>6046.238999999999</v>
       </c>
       <c r="G88">
         <v>320.9</v>
@@ -8613,28 +8613,28 @@
         <v>925.225</v>
       </c>
       <c r="M88">
-        <v>453.0370436</v>
+        <v>458.3049161999999</v>
       </c>
       <c r="N88">
-        <v>472.1879564</v>
+        <v>466.9200838000001</v>
       </c>
       <c r="O88">
-        <v>59.02349455</v>
+        <v>58.36501047500001</v>
       </c>
       <c r="P88">
-        <v>413.16446185</v>
+        <v>408.5550733250001</v>
       </c>
       <c r="Q88">
-        <v>729.06446185</v>
+        <v>724.4550733250001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2598365750270987</v>
+        <v>0.2759780965223549</v>
       </c>
       <c r="T88">
-        <v>3.608964144525661</v>
+        <v>3.881133386194263</v>
       </c>
       <c r="U88">
         <v>0.07580000000000001</v>
@@ -8651,7 +8651,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.042272288923263</v>
+        <v>2.018797894797708</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8659,22 +8659,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.09357990254790616</v>
+        <v>0.1046771845920185</v>
       </c>
       <c r="C89">
-        <v>-402.9649923386378</v>
+        <v>-1475.633015487007</v>
       </c>
       <c r="D89">
-        <v>5322.374007661361</v>
+        <v>4319.202984512993</v>
       </c>
       <c r="E89">
-        <v>2255.538999999999</v>
+        <v>2325.036</v>
       </c>
       <c r="F89">
-        <v>6046.238999999999</v>
+        <v>6115.735999999999</v>
       </c>
       <c r="G89">
         <v>320.9</v>
@@ -8695,45 +8695,45 @@
         <v>925.225</v>
       </c>
       <c r="M89">
-        <v>458.3049161999999</v>
+        <v>550.4162399999999</v>
       </c>
       <c r="N89">
-        <v>466.9200838000001</v>
+        <v>374.8087600000001</v>
       </c>
       <c r="O89">
-        <v>58.36501047500001</v>
+        <v>46.85109500000002</v>
       </c>
       <c r="P89">
-        <v>408.5550733250001</v>
+        <v>327.9576650000001</v>
       </c>
       <c r="Q89">
-        <v>724.4550733250001</v>
+        <v>643.8576650000001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2759780965223549</v>
+        <v>0.294809871600154</v>
       </c>
       <c r="T89">
-        <v>3.881133386194263</v>
+        <v>4.198664168140965</v>
       </c>
       <c r="U89">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V89">
         <v>0.125</v>
       </c>
       <c r="W89">
-        <v>0.06632500000000001</v>
+        <v>0.07875</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y89">
-        <v>2.018797894797708</v>
+        <v>1.680955125888001</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8741,22 +8741,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1046771845920185</v>
+        <v>0.1049647166361308</v>
       </c>
       <c r="C90">
-        <v>-1475.633015487007</v>
+        <v>-1566.12072301817</v>
       </c>
       <c r="D90">
-        <v>4319.202984512993</v>
+        <v>4298.21227698183</v>
       </c>
       <c r="E90">
-        <v>2325.036</v>
+        <v>2394.533</v>
       </c>
       <c r="F90">
-        <v>6115.735999999999</v>
+        <v>6185.232999999999</v>
       </c>
       <c r="G90">
         <v>320.9</v>
@@ -8777,28 +8777,28 @@
         <v>925.225</v>
       </c>
       <c r="M90">
-        <v>550.4162399999999</v>
+        <v>556.6709699999999</v>
       </c>
       <c r="N90">
-        <v>374.8087600000001</v>
+        <v>368.5540300000001</v>
       </c>
       <c r="O90">
-        <v>46.85109500000002</v>
+        <v>46.06925375000002</v>
       </c>
       <c r="P90">
-        <v>327.9576650000001</v>
+        <v>322.4847762500001</v>
       </c>
       <c r="Q90">
-        <v>643.8576650000001</v>
+        <v>638.3847762500001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.294809871600154</v>
+        <v>0.3170656057830075</v>
       </c>
       <c r="T90">
-        <v>4.198664168140965</v>
+        <v>4.573927819532523</v>
       </c>
       <c r="U90">
         <v>0.09</v>
@@ -8815,7 +8815,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>1.680955125888001</v>
+        <v>1.662067989642068</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8823,22 +8823,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1049647166361308</v>
+        <v>0.1052522486802432</v>
       </c>
       <c r="C91">
-        <v>-1566.12072301817</v>
+        <v>-1656.405393618763</v>
       </c>
       <c r="D91">
-        <v>4298.21227698183</v>
+        <v>4277.424606381237</v>
       </c>
       <c r="E91">
-        <v>2394.533</v>
+        <v>2464.03</v>
       </c>
       <c r="F91">
-        <v>6185.232999999999</v>
+        <v>6254.73</v>
       </c>
       <c r="G91">
         <v>320.9</v>
@@ -8859,28 +8859,28 @@
         <v>925.225</v>
       </c>
       <c r="M91">
-        <v>556.6709699999999</v>
+        <v>562.9256999999999</v>
       </c>
       <c r="N91">
-        <v>368.5540300000001</v>
+        <v>362.2993000000001</v>
       </c>
       <c r="O91">
-        <v>46.06925375000002</v>
+        <v>45.28741250000002</v>
       </c>
       <c r="P91">
-        <v>322.4847762500001</v>
+        <v>317.0118875000001</v>
       </c>
       <c r="Q91">
-        <v>638.3847762500001</v>
+        <v>632.9118875000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3170656057830075</v>
+        <v>0.3437724868024316</v>
       </c>
       <c r="T91">
-        <v>4.573927819532523</v>
+        <v>5.024244201202392</v>
       </c>
       <c r="U91">
         <v>0.09</v>
@@ -8897,7 +8897,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>1.662067989642068</v>
+        <v>1.643600567534934</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8905,22 +8905,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1052522486802432</v>
+        <v>0.1055397807243555</v>
       </c>
       <c r="C92">
-        <v>-1656.405393618763</v>
+        <v>-1746.489958984694</v>
       </c>
       <c r="D92">
-        <v>4277.424606381237</v>
+        <v>4256.837041015306</v>
       </c>
       <c r="E92">
-        <v>2464.03</v>
+        <v>2533.527</v>
       </c>
       <c r="F92">
-        <v>6254.73</v>
+        <v>6324.226999999999</v>
       </c>
       <c r="G92">
         <v>320.9</v>
@@ -8941,28 +8941,28 @@
         <v>925.225</v>
       </c>
       <c r="M92">
-        <v>562.9256999999999</v>
+        <v>569.1804299999999</v>
       </c>
       <c r="N92">
-        <v>362.2993000000001</v>
+        <v>356.0445700000001</v>
       </c>
       <c r="O92">
-        <v>45.28741250000002</v>
+        <v>44.50557125000002</v>
       </c>
       <c r="P92">
-        <v>317.0118875000001</v>
+        <v>311.5389987500001</v>
       </c>
       <c r="Q92">
-        <v>632.9118875000001</v>
+        <v>627.4389987500001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3437724868024316</v>
+        <v>0.3764142302706165</v>
       </c>
       <c r="T92">
-        <v>5.024244201202392</v>
+        <v>5.57463088991001</v>
       </c>
       <c r="U92">
         <v>0.09</v>
@@ -8979,7 +8979,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>1.643600567534934</v>
+        <v>1.625539022836748</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8987,22 +8987,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1055397807243555</v>
+        <v>0.1058273127684678</v>
       </c>
       <c r="C93">
-        <v>-1746.489958984694</v>
+        <v>-1836.377294640353</v>
       </c>
       <c r="D93">
-        <v>4256.837041015306</v>
+        <v>4236.446705359646</v>
       </c>
       <c r="E93">
-        <v>2533.527</v>
+        <v>2603.024</v>
       </c>
       <c r="F93">
-        <v>6324.226999999999</v>
+        <v>6393.723999999999</v>
       </c>
       <c r="G93">
         <v>320.9</v>
@@ -9023,28 +9023,28 @@
         <v>925.225</v>
       </c>
       <c r="M93">
-        <v>569.1804299999999</v>
+        <v>575.4351599999999</v>
       </c>
       <c r="N93">
-        <v>356.0445700000001</v>
+        <v>349.7898400000001</v>
       </c>
       <c r="O93">
-        <v>44.50557125000002</v>
+        <v>43.72373000000002</v>
       </c>
       <c r="P93">
-        <v>311.5389987500001</v>
+        <v>306.0661100000001</v>
       </c>
       <c r="Q93">
-        <v>627.4389987500001</v>
+        <v>621.9661100000001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3764142302706165</v>
+        <v>0.4172164096058479</v>
       </c>
       <c r="T93">
-        <v>5.57463088991001</v>
+        <v>6.262614250794534</v>
       </c>
       <c r="U93">
         <v>0.09</v>
@@ -9061,7 +9061,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>1.625539022836748</v>
+        <v>1.60787012041461</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9069,22 +9069,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1058273127684678</v>
+        <v>0.1061148448125802</v>
       </c>
       <c r="C94">
-        <v>-1836.377294640353</v>
+        <v>-1926.070221277488</v>
       </c>
       <c r="D94">
-        <v>4236.446705359646</v>
+        <v>4216.250778722512</v>
       </c>
       <c r="E94">
-        <v>2603.024</v>
+        <v>2672.521</v>
       </c>
       <c r="F94">
-        <v>6393.723999999999</v>
+        <v>6463.221</v>
       </c>
       <c r="G94">
         <v>320.9</v>
@@ -9105,28 +9105,28 @@
         <v>925.225</v>
       </c>
       <c r="M94">
-        <v>575.4351599999999</v>
+        <v>581.68989</v>
       </c>
       <c r="N94">
-        <v>349.7898400000001</v>
+        <v>343.53511</v>
       </c>
       <c r="O94">
-        <v>43.72373000000002</v>
+        <v>42.94188875</v>
       </c>
       <c r="P94">
-        <v>306.0661100000001</v>
+        <v>300.5932212500001</v>
       </c>
       <c r="Q94">
-        <v>621.9661100000001</v>
+        <v>616.49322125</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4172164096058479</v>
+        <v>0.469676354465431</v>
       </c>
       <c r="T94">
-        <v>6.262614250794534</v>
+        <v>7.147164286217491</v>
       </c>
       <c r="U94">
         <v>0.09</v>
@@ -9143,7 +9143,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>1.60787012041461</v>
+        <v>1.590581194388646</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9151,22 +9151,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1061148448125802</v>
+        <v>0.1064023768566925</v>
       </c>
       <c r="C95">
-        <v>-1926.070221277488</v>
+        <v>-2015.571506056004</v>
       </c>
       <c r="D95">
-        <v>4216.250778722512</v>
+        <v>4196.246493943995</v>
       </c>
       <c r="E95">
-        <v>2672.521</v>
+        <v>2742.018</v>
       </c>
       <c r="F95">
-        <v>6463.221</v>
+        <v>6532.717999999999</v>
       </c>
       <c r="G95">
         <v>320.9</v>
@@ -9187,28 +9187,28 @@
         <v>925.225</v>
       </c>
       <c r="M95">
-        <v>581.68989</v>
+        <v>587.9446199999999</v>
       </c>
       <c r="N95">
-        <v>343.53511</v>
+        <v>337.2803800000002</v>
       </c>
       <c r="O95">
-        <v>42.94188875</v>
+        <v>42.16004750000002</v>
       </c>
       <c r="P95">
-        <v>300.5932212500001</v>
+        <v>295.1203325000001</v>
       </c>
       <c r="Q95">
-        <v>616.49322125</v>
+        <v>611.0203325000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.469676354465431</v>
+        <v>0.5396229476115417</v>
       </c>
       <c r="T95">
-        <v>7.147164286217491</v>
+        <v>8.326564333448101</v>
       </c>
       <c r="U95">
         <v>0.09</v>
@@ -9225,7 +9225,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>1.590581194388646</v>
+        <v>1.573660117852597</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9233,22 +9233,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1064023768566925</v>
+        <v>0.1066899089008048</v>
       </c>
       <c r="C96">
-        <v>-2015.571506056004</v>
+        <v>-2104.883863867896</v>
       </c>
       <c r="D96">
-        <v>4196.246493943995</v>
+        <v>4176.431136132103</v>
       </c>
       <c r="E96">
-        <v>2742.018</v>
+        <v>2811.515</v>
       </c>
       <c r="F96">
-        <v>6532.717999999999</v>
+        <v>6602.214999999999</v>
       </c>
       <c r="G96">
         <v>320.9</v>
@@ -9269,28 +9269,28 @@
         <v>925.225</v>
       </c>
       <c r="M96">
-        <v>587.9446199999999</v>
+        <v>594.1993499999999</v>
       </c>
       <c r="N96">
-        <v>337.2803800000002</v>
+        <v>331.0256500000002</v>
       </c>
       <c r="O96">
-        <v>42.16004750000002</v>
+        <v>41.37820625000002</v>
       </c>
       <c r="P96">
-        <v>295.1203325000001</v>
+        <v>289.6474437500001</v>
       </c>
       <c r="Q96">
-        <v>611.0203325000001</v>
+        <v>605.5474437500002</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5396229476115417</v>
+        <v>0.6375481780160971</v>
       </c>
       <c r="T96">
-        <v>8.326564333448101</v>
+        <v>9.97772439957096</v>
       </c>
       <c r="U96">
         <v>0.09</v>
@@ -9307,7 +9307,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>1.573660117852597</v>
+        <v>1.55709527450678</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9315,22 +9315,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1066899089008048</v>
+        <v>0.1069774409449171</v>
       </c>
       <c r="C97">
-        <v>-2104.883863867896</v>
+        <v>-2194.009958565526</v>
       </c>
       <c r="D97">
-        <v>4176.431136132103</v>
+        <v>4156.802041434474</v>
       </c>
       <c r="E97">
-        <v>2811.515</v>
+        <v>2881.012</v>
       </c>
       <c r="F97">
-        <v>6602.214999999999</v>
+        <v>6671.712</v>
       </c>
       <c r="G97">
         <v>320.9</v>
@@ -9351,28 +9351,28 @@
         <v>925.225</v>
       </c>
       <c r="M97">
-        <v>594.1993499999999</v>
+        <v>600.45408</v>
       </c>
       <c r="N97">
-        <v>331.0256500000002</v>
+        <v>324.77092</v>
       </c>
       <c r="O97">
-        <v>41.37820625000002</v>
+        <v>40.59636500000001</v>
       </c>
       <c r="P97">
-        <v>289.6474437500001</v>
+        <v>284.1745550000001</v>
       </c>
       <c r="Q97">
-        <v>605.5474437500002</v>
+        <v>600.074555</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6375481780160971</v>
+        <v>0.78443602362293</v>
       </c>
       <c r="T97">
-        <v>9.97772439957096</v>
+        <v>12.45446449875524</v>
       </c>
       <c r="U97">
         <v>0.09</v>
@@ -9389,7 +9389,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>1.55709527450678</v>
+        <v>1.540875532064001</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9397,22 +9397,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1069774409449172</v>
+        <v>0.1072649729890295</v>
       </c>
       <c r="C98">
-        <v>-2194.009958565525</v>
+        <v>-2282.952404155444</v>
       </c>
       <c r="D98">
-        <v>4156.802041434474</v>
+        <v>4137.356595844555</v>
       </c>
       <c r="E98">
-        <v>2881.011999999999</v>
+        <v>2950.509</v>
       </c>
       <c r="F98">
-        <v>6671.711999999999</v>
+        <v>6741.208999999999</v>
       </c>
       <c r="G98">
         <v>320.9</v>
@@ -9433,28 +9433,28 @@
         <v>925.225</v>
       </c>
       <c r="M98">
-        <v>600.4540799999999</v>
+        <v>606.7088099999999</v>
       </c>
       <c r="N98">
-        <v>324.7709200000002</v>
+        <v>318.5161900000002</v>
       </c>
       <c r="O98">
-        <v>40.59636500000002</v>
+        <v>39.81452375000002</v>
       </c>
       <c r="P98">
-        <v>284.1745550000002</v>
+        <v>278.7016662500001</v>
       </c>
       <c r="Q98">
-        <v>600.0745550000001</v>
+        <v>594.6016662500001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.7844360236229281</v>
+        <v>1.029249099634315</v>
       </c>
       <c r="T98">
-        <v>12.45446449875521</v>
+        <v>16.58236466406234</v>
       </c>
       <c r="U98">
         <v>0.09</v>
@@ -9471,7 +9471,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>1.540875532064001</v>
+        <v>1.524990217300455</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9479,22 +9479,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1072649729890295</v>
+        <v>0.1075525050331418</v>
       </c>
       <c r="C99">
-        <v>-2282.952404155444</v>
+        <v>-2371.713765958846</v>
       </c>
       <c r="D99">
-        <v>4137.356595844555</v>
+        <v>4118.092234041153</v>
       </c>
       <c r="E99">
-        <v>2950.509</v>
+        <v>3020.006</v>
       </c>
       <c r="F99">
-        <v>6741.208999999999</v>
+        <v>6810.705999999999</v>
       </c>
       <c r="G99">
         <v>320.9</v>
@@ -9515,28 +9515,28 @@
         <v>925.225</v>
       </c>
       <c r="M99">
-        <v>606.7088099999999</v>
+        <v>612.9635399999999</v>
       </c>
       <c r="N99">
-        <v>318.5161900000002</v>
+        <v>312.2614600000002</v>
       </c>
       <c r="O99">
-        <v>39.81452375000002</v>
+        <v>39.03268250000002</v>
       </c>
       <c r="P99">
-        <v>278.7016662500001</v>
+        <v>273.2287775000001</v>
       </c>
       <c r="Q99">
-        <v>594.6016662500001</v>
+        <v>589.1287775000001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.029249099634315</v>
+        <v>1.51887525165709</v>
       </c>
       <c r="T99">
-        <v>16.58236466406234</v>
+        <v>24.83816499467659</v>
       </c>
       <c r="U99">
         <v>0.09</v>
@@ -9553,7 +9553,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>1.524990217300455</v>
+        <v>1.509429092634123</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9561,22 +9561,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1075525050331418</v>
+        <v>0.1589168714670195</v>
       </c>
       <c r="C100">
-        <v>-2371.713765958846</v>
+        <v>-4311.163459792567</v>
       </c>
       <c r="D100">
-        <v>4118.092234041153</v>
+        <v>2248.139540207432</v>
       </c>
       <c r="E100">
-        <v>3020.006</v>
+        <v>3089.502999999999</v>
       </c>
       <c r="F100">
-        <v>6810.705999999999</v>
+        <v>6880.202999999999</v>
       </c>
       <c r="G100">
         <v>320.9</v>
@@ -9597,129 +9597,47 @@
         <v>925.225</v>
       </c>
       <c r="M100">
-        <v>612.9635399999999</v>
+        <v>1010.0138004</v>
       </c>
       <c r="N100">
-        <v>312.2614600000002</v>
+        <v>-84.7888003999999</v>
       </c>
       <c r="O100">
-        <v>39.03268250000002</v>
+        <v>-10.59860004999999</v>
       </c>
       <c r="P100">
-        <v>273.2287775000001</v>
+        <v>-74.19020034999991</v>
       </c>
       <c r="Q100">
-        <v>589.1287775000001</v>
+        <v>241.7097996500001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.51887525165709</v>
+        <v>3.022632721331074</v>
       </c>
       <c r="T100">
-        <v>24.83816499467659</v>
+        <v>50.19367626385544</v>
       </c>
       <c r="U100">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V100">
-        <v>0.125</v>
+        <v>0.1145064799651227</v>
       </c>
       <c r="W100">
-        <v>0.07875</v>
+        <v>0.12999044874112</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y100">
-        <v>1.509429092634123</v>
+        <v>0.9160518397209814</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1589168714670195</v>
-      </c>
-      <c r="C101">
-        <v>-4311.163459792567</v>
-      </c>
-      <c r="D101">
-        <v>2248.139540207432</v>
-      </c>
-      <c r="E101">
-        <v>3089.502999999999</v>
-      </c>
-      <c r="F101">
-        <v>6880.202999999999</v>
-      </c>
-      <c r="G101">
-        <v>320.9</v>
-      </c>
-      <c r="H101">
-        <v>3159</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1241.125</v>
-      </c>
-      <c r="K101">
-        <v>315.9</v>
-      </c>
-      <c r="L101">
-        <v>925.225</v>
-      </c>
-      <c r="M101">
-        <v>1010.0138004</v>
-      </c>
-      <c r="N101">
-        <v>-84.7888003999999</v>
-      </c>
-      <c r="O101">
-        <v>-10.59860004999999</v>
-      </c>
-      <c r="P101">
-        <v>-74.19020034999991</v>
-      </c>
-      <c r="Q101">
-        <v>241.7097996500001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.022632721331074</v>
-      </c>
-      <c r="T101">
-        <v>50.19367626385544</v>
-      </c>
-      <c r="U101">
-        <v>0.1468</v>
-      </c>
-      <c r="V101">
-        <v>0.1145064799651227</v>
-      </c>
-      <c r="W101">
-        <v>0.12999044874112</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ca2/CC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.9160518397209814</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
